--- a/public/modelos/planilha-criancas.xlsx
+++ b/public/modelos/planilha-criancas.xlsx
@@ -230,25 +230,35 @@
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Nome do responsável. Nunca aparece no site.</t>
+        <t>Opcional. Aparece no site. Complete a frase "sonha em...". Ex.: ser professora</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Telefone ou WhatsApp. Nunca aparece no site.</t>
+        <t>Opcional. Aparece no site. O jeitinho dela, contado por ela ou pelos pais (até 400 letras). Sem escola, rua ou sobrenome.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Sim só com o termo de autorização assinado pelo responsável. Sem ele, Não (a criança aparece com avatar).</t>
+        <t>Nome do responsável. Nunca aparece no site.</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
+        <t>Telefone ou WhatsApp. Nunca aparece no site.</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Sim só com o termo de autorização assinado pelo responsável. Sem ele, Não (a criança aparece com avatar).</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
         <t>Uso interno da equipe. Nunca aparece no site.</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>Opcional. Se a criança já tinha um código, ele evita duplicar ao importar de novo.</t>
       </text>
@@ -310,25 +320,35 @@
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Nome do responsável. Nunca aparece no site.</t>
+        <t>Opcional. Aparece no site. Complete a frase "sonha em...". Ex.: ser professora</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Telefone ou WhatsApp. Nunca aparece no site.</t>
+        <t>Opcional. Aparece no site. O jeitinho dela, contado por ela ou pelos pais (até 400 letras). Sem escola, rua ou sobrenome.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Sim só com o termo de autorização assinado pelo responsável. Sem ele, Não (a criança aparece com avatar).</t>
+        <t>Nome do responsável. Nunca aparece no site.</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
+        <t>Telefone ou WhatsApp. Nunca aparece no site.</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Sim só com o termo de autorização assinado pelo responsável. Sem ele, Não (a criança aparece com avatar).</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
         <t>Uso interno da equipe. Nunca aparece no site.</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>Opcional. Se a criança já tinha um código, ele evita duplicar ao importar de novo.</t>
       </text>
@@ -626,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1001"/>
+  <dimension ref="A1:P1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -638,11 +658,13 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -693,25 +715,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Responsável</t>
+          <t>Sonho</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Contato do responsável</t>
+          <t>Sobre a criança</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Autoriza imagem</t>
+          <t>Responsável</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Contato do responsável</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Autoriza imagem</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Observações</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Código no sistema antigo</t>
         </is>
@@ -732,6 +764,8 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -748,6 +782,8 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -764,6 +800,8 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -780,6 +818,8 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -796,6 +836,8 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -812,6 +854,8 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -828,6 +872,8 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -844,6 +890,8 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -860,6 +908,8 @@
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -876,6 +926,8 @@
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -892,6 +944,8 @@
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -908,6 +962,8 @@
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -924,6 +980,8 @@
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -940,6 +998,8 @@
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -956,6 +1016,8 @@
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -972,6 +1034,8 @@
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -988,6 +1052,8 @@
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1004,6 +1070,8 @@
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1020,6 +1088,8 @@
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1036,6 +1106,8 @@
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1052,6 +1124,8 @@
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1068,6 +1142,8 @@
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1084,6 +1160,8 @@
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1100,6 +1178,8 @@
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1116,6 +1196,8 @@
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1132,6 +1214,8 @@
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1148,6 +1232,8 @@
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -1164,6 +1250,8 @@
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1180,6 +1268,8 @@
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -1196,6 +1286,8 @@
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -1212,6 +1304,8 @@
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -1228,6 +1322,8 @@
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1244,6 +1340,8 @@
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -1260,6 +1358,8 @@
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
       <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1276,6 +1376,8 @@
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -1292,6 +1394,8 @@
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
       <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -1308,6 +1412,8 @@
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -1324,6 +1430,8 @@
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -1340,6 +1448,8 @@
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -1356,6 +1466,8 @@
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
       <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -1372,6 +1484,8 @@
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -1388,6 +1502,8 @@
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
       <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -1404,6 +1520,8 @@
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
       <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -1420,6 +1538,8 @@
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
       <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -1436,6 +1556,8 @@
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n"/>
       <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -1452,6 +1574,8 @@
       <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n"/>
       <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
+      <c r="P47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -1468,6 +1592,8 @@
       <c r="L48" s="2" t="n"/>
       <c r="M48" s="2" t="n"/>
       <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
+      <c r="P48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -1484,6 +1610,8 @@
       <c r="L49" s="2" t="n"/>
       <c r="M49" s="2" t="n"/>
       <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
+      <c r="P49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -1500,6 +1628,8 @@
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n"/>
       <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -1516,6 +1646,8 @@
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="2" t="n"/>
       <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -1532,6 +1664,8 @@
       <c r="L52" s="2" t="n"/>
       <c r="M52" s="2" t="n"/>
       <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -1548,6 +1682,8 @@
       <c r="L53" s="2" t="n"/>
       <c r="M53" s="2" t="n"/>
       <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
+      <c r="P53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -1564,6 +1700,8 @@
       <c r="L54" s="2" t="n"/>
       <c r="M54" s="2" t="n"/>
       <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -1580,6 +1718,8 @@
       <c r="L55" s="2" t="n"/>
       <c r="M55" s="2" t="n"/>
       <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -1596,6 +1736,8 @@
       <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n"/>
       <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -1612,6 +1754,8 @@
       <c r="L57" s="2" t="n"/>
       <c r="M57" s="2" t="n"/>
       <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="n"/>
+      <c r="P57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -1628,6 +1772,8 @@
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n"/>
       <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="n"/>
+      <c r="P58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -1644,6 +1790,8 @@
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n"/>
       <c r="N59" s="2" t="n"/>
+      <c r="O59" s="2" t="n"/>
+      <c r="P59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -1660,6 +1808,8 @@
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="2" t="n"/>
       <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
+      <c r="P60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -1676,6 +1826,8 @@
       <c r="L61" s="2" t="n"/>
       <c r="M61" s="2" t="n"/>
       <c r="N61" s="2" t="n"/>
+      <c r="O61" s="2" t="n"/>
+      <c r="P61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -1692,6 +1844,8 @@
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="2" t="n"/>
       <c r="N62" s="2" t="n"/>
+      <c r="O62" s="2" t="n"/>
+      <c r="P62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -1708,6 +1862,8 @@
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="n"/>
       <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="n"/>
+      <c r="P63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -1724,6 +1880,8 @@
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n"/>
       <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -1740,6 +1898,8 @@
       <c r="L65" s="2" t="n"/>
       <c r="M65" s="2" t="n"/>
       <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="n"/>
+      <c r="P65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -1756,6 +1916,8 @@
       <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n"/>
       <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -1772,6 +1934,8 @@
       <c r="L67" s="2" t="n"/>
       <c r="M67" s="2" t="n"/>
       <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="n"/>
+      <c r="P67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -1788,6 +1952,8 @@
       <c r="L68" s="2" t="n"/>
       <c r="M68" s="2" t="n"/>
       <c r="N68" s="2" t="n"/>
+      <c r="O68" s="2" t="n"/>
+      <c r="P68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -1804,6 +1970,8 @@
       <c r="L69" s="2" t="n"/>
       <c r="M69" s="2" t="n"/>
       <c r="N69" s="2" t="n"/>
+      <c r="O69" s="2" t="n"/>
+      <c r="P69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -1820,6 +1988,8 @@
       <c r="L70" s="2" t="n"/>
       <c r="M70" s="2" t="n"/>
       <c r="N70" s="2" t="n"/>
+      <c r="O70" s="2" t="n"/>
+      <c r="P70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -1836,6 +2006,8 @@
       <c r="L71" s="2" t="n"/>
       <c r="M71" s="2" t="n"/>
       <c r="N71" s="2" t="n"/>
+      <c r="O71" s="2" t="n"/>
+      <c r="P71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -1852,6 +2024,8 @@
       <c r="L72" s="2" t="n"/>
       <c r="M72" s="2" t="n"/>
       <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="n"/>
+      <c r="P72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -1868,6 +2042,8 @@
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="n"/>
       <c r="N73" s="2" t="n"/>
+      <c r="O73" s="2" t="n"/>
+      <c r="P73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -1884,6 +2060,8 @@
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="n"/>
       <c r="N74" s="2" t="n"/>
+      <c r="O74" s="2" t="n"/>
+      <c r="P74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -1900,6 +2078,8 @@
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="n"/>
       <c r="N75" s="2" t="n"/>
+      <c r="O75" s="2" t="n"/>
+      <c r="P75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -1916,6 +2096,8 @@
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="2" t="n"/>
       <c r="N76" s="2" t="n"/>
+      <c r="O76" s="2" t="n"/>
+      <c r="P76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
@@ -1932,6 +2114,8 @@
       <c r="L77" s="2" t="n"/>
       <c r="M77" s="2" t="n"/>
       <c r="N77" s="2" t="n"/>
+      <c r="O77" s="2" t="n"/>
+      <c r="P77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -1948,6 +2132,8 @@
       <c r="L78" s="2" t="n"/>
       <c r="M78" s="2" t="n"/>
       <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="n"/>
+      <c r="P78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -1964,6 +2150,8 @@
       <c r="L79" s="2" t="n"/>
       <c r="M79" s="2" t="n"/>
       <c r="N79" s="2" t="n"/>
+      <c r="O79" s="2" t="n"/>
+      <c r="P79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -1980,6 +2168,8 @@
       <c r="L80" s="2" t="n"/>
       <c r="M80" s="2" t="n"/>
       <c r="N80" s="2" t="n"/>
+      <c r="O80" s="2" t="n"/>
+      <c r="P80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -1996,6 +2186,8 @@
       <c r="L81" s="2" t="n"/>
       <c r="M81" s="2" t="n"/>
       <c r="N81" s="2" t="n"/>
+      <c r="O81" s="2" t="n"/>
+      <c r="P81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -2012,6 +2204,8 @@
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="2" t="n"/>
       <c r="N82" s="2" t="n"/>
+      <c r="O82" s="2" t="n"/>
+      <c r="P82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -2028,6 +2222,8 @@
       <c r="L83" s="2" t="n"/>
       <c r="M83" s="2" t="n"/>
       <c r="N83" s="2" t="n"/>
+      <c r="O83" s="2" t="n"/>
+      <c r="P83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -2044,6 +2240,8 @@
       <c r="L84" s="2" t="n"/>
       <c r="M84" s="2" t="n"/>
       <c r="N84" s="2" t="n"/>
+      <c r="O84" s="2" t="n"/>
+      <c r="P84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -2060,6 +2258,8 @@
       <c r="L85" s="2" t="n"/>
       <c r="M85" s="2" t="n"/>
       <c r="N85" s="2" t="n"/>
+      <c r="O85" s="2" t="n"/>
+      <c r="P85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -2076,6 +2276,8 @@
       <c r="L86" s="2" t="n"/>
       <c r="M86" s="2" t="n"/>
       <c r="N86" s="2" t="n"/>
+      <c r="O86" s="2" t="n"/>
+      <c r="P86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -2092,6 +2294,8 @@
       <c r="L87" s="2" t="n"/>
       <c r="M87" s="2" t="n"/>
       <c r="N87" s="2" t="n"/>
+      <c r="O87" s="2" t="n"/>
+      <c r="P87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -2108,6 +2312,8 @@
       <c r="L88" s="2" t="n"/>
       <c r="M88" s="2" t="n"/>
       <c r="N88" s="2" t="n"/>
+      <c r="O88" s="2" t="n"/>
+      <c r="P88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -2124,6 +2330,8 @@
       <c r="L89" s="2" t="n"/>
       <c r="M89" s="2" t="n"/>
       <c r="N89" s="2" t="n"/>
+      <c r="O89" s="2" t="n"/>
+      <c r="P89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -2140,6 +2348,8 @@
       <c r="L90" s="2" t="n"/>
       <c r="M90" s="2" t="n"/>
       <c r="N90" s="2" t="n"/>
+      <c r="O90" s="2" t="n"/>
+      <c r="P90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -2156,6 +2366,8 @@
       <c r="L91" s="2" t="n"/>
       <c r="M91" s="2" t="n"/>
       <c r="N91" s="2" t="n"/>
+      <c r="O91" s="2" t="n"/>
+      <c r="P91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -2172,6 +2384,8 @@
       <c r="L92" s="2" t="n"/>
       <c r="M92" s="2" t="n"/>
       <c r="N92" s="2" t="n"/>
+      <c r="O92" s="2" t="n"/>
+      <c r="P92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
@@ -2188,6 +2402,8 @@
       <c r="L93" s="2" t="n"/>
       <c r="M93" s="2" t="n"/>
       <c r="N93" s="2" t="n"/>
+      <c r="O93" s="2" t="n"/>
+      <c r="P93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -2204,6 +2420,8 @@
       <c r="L94" s="2" t="n"/>
       <c r="M94" s="2" t="n"/>
       <c r="N94" s="2" t="n"/>
+      <c r="O94" s="2" t="n"/>
+      <c r="P94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -2220,6 +2438,8 @@
       <c r="L95" s="2" t="n"/>
       <c r="M95" s="2" t="n"/>
       <c r="N95" s="2" t="n"/>
+      <c r="O95" s="2" t="n"/>
+      <c r="P95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -2236,6 +2456,8 @@
       <c r="L96" s="2" t="n"/>
       <c r="M96" s="2" t="n"/>
       <c r="N96" s="2" t="n"/>
+      <c r="O96" s="2" t="n"/>
+      <c r="P96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -2252,6 +2474,8 @@
       <c r="L97" s="2" t="n"/>
       <c r="M97" s="2" t="n"/>
       <c r="N97" s="2" t="n"/>
+      <c r="O97" s="2" t="n"/>
+      <c r="P97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -2268,6 +2492,8 @@
       <c r="L98" s="2" t="n"/>
       <c r="M98" s="2" t="n"/>
       <c r="N98" s="2" t="n"/>
+      <c r="O98" s="2" t="n"/>
+      <c r="P98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -2284,6 +2510,8 @@
       <c r="L99" s="2" t="n"/>
       <c r="M99" s="2" t="n"/>
       <c r="N99" s="2" t="n"/>
+      <c r="O99" s="2" t="n"/>
+      <c r="P99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -2300,6 +2528,8 @@
       <c r="L100" s="2" t="n"/>
       <c r="M100" s="2" t="n"/>
       <c r="N100" s="2" t="n"/>
+      <c r="O100" s="2" t="n"/>
+      <c r="P100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -2316,6 +2546,8 @@
       <c r="L101" s="2" t="n"/>
       <c r="M101" s="2" t="n"/>
       <c r="N101" s="2" t="n"/>
+      <c r="O101" s="2" t="n"/>
+      <c r="P101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -2332,6 +2564,8 @@
       <c r="L102" s="2" t="n"/>
       <c r="M102" s="2" t="n"/>
       <c r="N102" s="2" t="n"/>
+      <c r="O102" s="2" t="n"/>
+      <c r="P102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
@@ -2348,6 +2582,8 @@
       <c r="L103" s="2" t="n"/>
       <c r="M103" s="2" t="n"/>
       <c r="N103" s="2" t="n"/>
+      <c r="O103" s="2" t="n"/>
+      <c r="P103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -2364,6 +2600,8 @@
       <c r="L104" s="2" t="n"/>
       <c r="M104" s="2" t="n"/>
       <c r="N104" s="2" t="n"/>
+      <c r="O104" s="2" t="n"/>
+      <c r="P104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -2380,6 +2618,8 @@
       <c r="L105" s="2" t="n"/>
       <c r="M105" s="2" t="n"/>
       <c r="N105" s="2" t="n"/>
+      <c r="O105" s="2" t="n"/>
+      <c r="P105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -2396,6 +2636,8 @@
       <c r="L106" s="2" t="n"/>
       <c r="M106" s="2" t="n"/>
       <c r="N106" s="2" t="n"/>
+      <c r="O106" s="2" t="n"/>
+      <c r="P106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -2412,6 +2654,8 @@
       <c r="L107" s="2" t="n"/>
       <c r="M107" s="2" t="n"/>
       <c r="N107" s="2" t="n"/>
+      <c r="O107" s="2" t="n"/>
+      <c r="P107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -2428,6 +2672,8 @@
       <c r="L108" s="2" t="n"/>
       <c r="M108" s="2" t="n"/>
       <c r="N108" s="2" t="n"/>
+      <c r="O108" s="2" t="n"/>
+      <c r="P108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -2444,6 +2690,8 @@
       <c r="L109" s="2" t="n"/>
       <c r="M109" s="2" t="n"/>
       <c r="N109" s="2" t="n"/>
+      <c r="O109" s="2" t="n"/>
+      <c r="P109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -2460,6 +2708,8 @@
       <c r="L110" s="2" t="n"/>
       <c r="M110" s="2" t="n"/>
       <c r="N110" s="2" t="n"/>
+      <c r="O110" s="2" t="n"/>
+      <c r="P110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
@@ -2476,6 +2726,8 @@
       <c r="L111" s="2" t="n"/>
       <c r="M111" s="2" t="n"/>
       <c r="N111" s="2" t="n"/>
+      <c r="O111" s="2" t="n"/>
+      <c r="P111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -2492,6 +2744,8 @@
       <c r="L112" s="2" t="n"/>
       <c r="M112" s="2" t="n"/>
       <c r="N112" s="2" t="n"/>
+      <c r="O112" s="2" t="n"/>
+      <c r="P112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -2508,6 +2762,8 @@
       <c r="L113" s="2" t="n"/>
       <c r="M113" s="2" t="n"/>
       <c r="N113" s="2" t="n"/>
+      <c r="O113" s="2" t="n"/>
+      <c r="P113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -2524,6 +2780,8 @@
       <c r="L114" s="2" t="n"/>
       <c r="M114" s="2" t="n"/>
       <c r="N114" s="2" t="n"/>
+      <c r="O114" s="2" t="n"/>
+      <c r="P114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
@@ -2540,6 +2798,8 @@
       <c r="L115" s="2" t="n"/>
       <c r="M115" s="2" t="n"/>
       <c r="N115" s="2" t="n"/>
+      <c r="O115" s="2" t="n"/>
+      <c r="P115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -2556,6 +2816,8 @@
       <c r="L116" s="2" t="n"/>
       <c r="M116" s="2" t="n"/>
       <c r="N116" s="2" t="n"/>
+      <c r="O116" s="2" t="n"/>
+      <c r="P116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -2572,6 +2834,8 @@
       <c r="L117" s="2" t="n"/>
       <c r="M117" s="2" t="n"/>
       <c r="N117" s="2" t="n"/>
+      <c r="O117" s="2" t="n"/>
+      <c r="P117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -2588,6 +2852,8 @@
       <c r="L118" s="2" t="n"/>
       <c r="M118" s="2" t="n"/>
       <c r="N118" s="2" t="n"/>
+      <c r="O118" s="2" t="n"/>
+      <c r="P118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -2604,6 +2870,8 @@
       <c r="L119" s="2" t="n"/>
       <c r="M119" s="2" t="n"/>
       <c r="N119" s="2" t="n"/>
+      <c r="O119" s="2" t="n"/>
+      <c r="P119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -2620,6 +2888,8 @@
       <c r="L120" s="2" t="n"/>
       <c r="M120" s="2" t="n"/>
       <c r="N120" s="2" t="n"/>
+      <c r="O120" s="2" t="n"/>
+      <c r="P120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -2636,6 +2906,8 @@
       <c r="L121" s="2" t="n"/>
       <c r="M121" s="2" t="n"/>
       <c r="N121" s="2" t="n"/>
+      <c r="O121" s="2" t="n"/>
+      <c r="P121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -2652,6 +2924,8 @@
       <c r="L122" s="2" t="n"/>
       <c r="M122" s="2" t="n"/>
       <c r="N122" s="2" t="n"/>
+      <c r="O122" s="2" t="n"/>
+      <c r="P122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -2668,6 +2942,8 @@
       <c r="L123" s="2" t="n"/>
       <c r="M123" s="2" t="n"/>
       <c r="N123" s="2" t="n"/>
+      <c r="O123" s="2" t="n"/>
+      <c r="P123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -2684,6 +2960,8 @@
       <c r="L124" s="2" t="n"/>
       <c r="M124" s="2" t="n"/>
       <c r="N124" s="2" t="n"/>
+      <c r="O124" s="2" t="n"/>
+      <c r="P124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -2700,6 +2978,8 @@
       <c r="L125" s="2" t="n"/>
       <c r="M125" s="2" t="n"/>
       <c r="N125" s="2" t="n"/>
+      <c r="O125" s="2" t="n"/>
+      <c r="P125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -2716,6 +2996,8 @@
       <c r="L126" s="2" t="n"/>
       <c r="M126" s="2" t="n"/>
       <c r="N126" s="2" t="n"/>
+      <c r="O126" s="2" t="n"/>
+      <c r="P126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -2732,6 +3014,8 @@
       <c r="L127" s="2" t="n"/>
       <c r="M127" s="2" t="n"/>
       <c r="N127" s="2" t="n"/>
+      <c r="O127" s="2" t="n"/>
+      <c r="P127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -2748,6 +3032,8 @@
       <c r="L128" s="2" t="n"/>
       <c r="M128" s="2" t="n"/>
       <c r="N128" s="2" t="n"/>
+      <c r="O128" s="2" t="n"/>
+      <c r="P128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -2764,6 +3050,8 @@
       <c r="L129" s="2" t="n"/>
       <c r="M129" s="2" t="n"/>
       <c r="N129" s="2" t="n"/>
+      <c r="O129" s="2" t="n"/>
+      <c r="P129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -2780,6 +3068,8 @@
       <c r="L130" s="2" t="n"/>
       <c r="M130" s="2" t="n"/>
       <c r="N130" s="2" t="n"/>
+      <c r="O130" s="2" t="n"/>
+      <c r="P130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -2796,6 +3086,8 @@
       <c r="L131" s="2" t="n"/>
       <c r="M131" s="2" t="n"/>
       <c r="N131" s="2" t="n"/>
+      <c r="O131" s="2" t="n"/>
+      <c r="P131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -2812,6 +3104,8 @@
       <c r="L132" s="2" t="n"/>
       <c r="M132" s="2" t="n"/>
       <c r="N132" s="2" t="n"/>
+      <c r="O132" s="2" t="n"/>
+      <c r="P132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -2828,6 +3122,8 @@
       <c r="L133" s="2" t="n"/>
       <c r="M133" s="2" t="n"/>
       <c r="N133" s="2" t="n"/>
+      <c r="O133" s="2" t="n"/>
+      <c r="P133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -2844,6 +3140,8 @@
       <c r="L134" s="2" t="n"/>
       <c r="M134" s="2" t="n"/>
       <c r="N134" s="2" t="n"/>
+      <c r="O134" s="2" t="n"/>
+      <c r="P134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -2860,6 +3158,8 @@
       <c r="L135" s="2" t="n"/>
       <c r="M135" s="2" t="n"/>
       <c r="N135" s="2" t="n"/>
+      <c r="O135" s="2" t="n"/>
+      <c r="P135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -2876,6 +3176,8 @@
       <c r="L136" s="2" t="n"/>
       <c r="M136" s="2" t="n"/>
       <c r="N136" s="2" t="n"/>
+      <c r="O136" s="2" t="n"/>
+      <c r="P136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -2892,6 +3194,8 @@
       <c r="L137" s="2" t="n"/>
       <c r="M137" s="2" t="n"/>
       <c r="N137" s="2" t="n"/>
+      <c r="O137" s="2" t="n"/>
+      <c r="P137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -2908,6 +3212,8 @@
       <c r="L138" s="2" t="n"/>
       <c r="M138" s="2" t="n"/>
       <c r="N138" s="2" t="n"/>
+      <c r="O138" s="2" t="n"/>
+      <c r="P138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -2924,6 +3230,8 @@
       <c r="L139" s="2" t="n"/>
       <c r="M139" s="2" t="n"/>
       <c r="N139" s="2" t="n"/>
+      <c r="O139" s="2" t="n"/>
+      <c r="P139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -2940,6 +3248,8 @@
       <c r="L140" s="2" t="n"/>
       <c r="M140" s="2" t="n"/>
       <c r="N140" s="2" t="n"/>
+      <c r="O140" s="2" t="n"/>
+      <c r="P140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -2956,6 +3266,8 @@
       <c r="L141" s="2" t="n"/>
       <c r="M141" s="2" t="n"/>
       <c r="N141" s="2" t="n"/>
+      <c r="O141" s="2" t="n"/>
+      <c r="P141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -2972,6 +3284,8 @@
       <c r="L142" s="2" t="n"/>
       <c r="M142" s="2" t="n"/>
       <c r="N142" s="2" t="n"/>
+      <c r="O142" s="2" t="n"/>
+      <c r="P142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -2988,6 +3302,8 @@
       <c r="L143" s="2" t="n"/>
       <c r="M143" s="2" t="n"/>
       <c r="N143" s="2" t="n"/>
+      <c r="O143" s="2" t="n"/>
+      <c r="P143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -3004,6 +3320,8 @@
       <c r="L144" s="2" t="n"/>
       <c r="M144" s="2" t="n"/>
       <c r="N144" s="2" t="n"/>
+      <c r="O144" s="2" t="n"/>
+      <c r="P144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -3020,6 +3338,8 @@
       <c r="L145" s="2" t="n"/>
       <c r="M145" s="2" t="n"/>
       <c r="N145" s="2" t="n"/>
+      <c r="O145" s="2" t="n"/>
+      <c r="P145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -3036,6 +3356,8 @@
       <c r="L146" s="2" t="n"/>
       <c r="M146" s="2" t="n"/>
       <c r="N146" s="2" t="n"/>
+      <c r="O146" s="2" t="n"/>
+      <c r="P146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -3052,6 +3374,8 @@
       <c r="L147" s="2" t="n"/>
       <c r="M147" s="2" t="n"/>
       <c r="N147" s="2" t="n"/>
+      <c r="O147" s="2" t="n"/>
+      <c r="P147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -3068,6 +3392,8 @@
       <c r="L148" s="2" t="n"/>
       <c r="M148" s="2" t="n"/>
       <c r="N148" s="2" t="n"/>
+      <c r="O148" s="2" t="n"/>
+      <c r="P148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -3084,6 +3410,8 @@
       <c r="L149" s="2" t="n"/>
       <c r="M149" s="2" t="n"/>
       <c r="N149" s="2" t="n"/>
+      <c r="O149" s="2" t="n"/>
+      <c r="P149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -3100,6 +3428,8 @@
       <c r="L150" s="2" t="n"/>
       <c r="M150" s="2" t="n"/>
       <c r="N150" s="2" t="n"/>
+      <c r="O150" s="2" t="n"/>
+      <c r="P150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -3116,6 +3446,8 @@
       <c r="L151" s="2" t="n"/>
       <c r="M151" s="2" t="n"/>
       <c r="N151" s="2" t="n"/>
+      <c r="O151" s="2" t="n"/>
+      <c r="P151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -3132,6 +3464,8 @@
       <c r="L152" s="2" t="n"/>
       <c r="M152" s="2" t="n"/>
       <c r="N152" s="2" t="n"/>
+      <c r="O152" s="2" t="n"/>
+      <c r="P152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -3148,6 +3482,8 @@
       <c r="L153" s="2" t="n"/>
       <c r="M153" s="2" t="n"/>
       <c r="N153" s="2" t="n"/>
+      <c r="O153" s="2" t="n"/>
+      <c r="P153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -3164,6 +3500,8 @@
       <c r="L154" s="2" t="n"/>
       <c r="M154" s="2" t="n"/>
       <c r="N154" s="2" t="n"/>
+      <c r="O154" s="2" t="n"/>
+      <c r="P154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -3180,6 +3518,8 @@
       <c r="L155" s="2" t="n"/>
       <c r="M155" s="2" t="n"/>
       <c r="N155" s="2" t="n"/>
+      <c r="O155" s="2" t="n"/>
+      <c r="P155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -3196,6 +3536,8 @@
       <c r="L156" s="2" t="n"/>
       <c r="M156" s="2" t="n"/>
       <c r="N156" s="2" t="n"/>
+      <c r="O156" s="2" t="n"/>
+      <c r="P156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -3212,6 +3554,8 @@
       <c r="L157" s="2" t="n"/>
       <c r="M157" s="2" t="n"/>
       <c r="N157" s="2" t="n"/>
+      <c r="O157" s="2" t="n"/>
+      <c r="P157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -3228,6 +3572,8 @@
       <c r="L158" s="2" t="n"/>
       <c r="M158" s="2" t="n"/>
       <c r="N158" s="2" t="n"/>
+      <c r="O158" s="2" t="n"/>
+      <c r="P158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -3244,6 +3590,8 @@
       <c r="L159" s="2" t="n"/>
       <c r="M159" s="2" t="n"/>
       <c r="N159" s="2" t="n"/>
+      <c r="O159" s="2" t="n"/>
+      <c r="P159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -3260,6 +3608,8 @@
       <c r="L160" s="2" t="n"/>
       <c r="M160" s="2" t="n"/>
       <c r="N160" s="2" t="n"/>
+      <c r="O160" s="2" t="n"/>
+      <c r="P160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -3276,6 +3626,8 @@
       <c r="L161" s="2" t="n"/>
       <c r="M161" s="2" t="n"/>
       <c r="N161" s="2" t="n"/>
+      <c r="O161" s="2" t="n"/>
+      <c r="P161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -3292,6 +3644,8 @@
       <c r="L162" s="2" t="n"/>
       <c r="M162" s="2" t="n"/>
       <c r="N162" s="2" t="n"/>
+      <c r="O162" s="2" t="n"/>
+      <c r="P162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -3308,6 +3662,8 @@
       <c r="L163" s="2" t="n"/>
       <c r="M163" s="2" t="n"/>
       <c r="N163" s="2" t="n"/>
+      <c r="O163" s="2" t="n"/>
+      <c r="P163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -3324,6 +3680,8 @@
       <c r="L164" s="2" t="n"/>
       <c r="M164" s="2" t="n"/>
       <c r="N164" s="2" t="n"/>
+      <c r="O164" s="2" t="n"/>
+      <c r="P164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -3340,6 +3698,8 @@
       <c r="L165" s="2" t="n"/>
       <c r="M165" s="2" t="n"/>
       <c r="N165" s="2" t="n"/>
+      <c r="O165" s="2" t="n"/>
+      <c r="P165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -3356,6 +3716,8 @@
       <c r="L166" s="2" t="n"/>
       <c r="M166" s="2" t="n"/>
       <c r="N166" s="2" t="n"/>
+      <c r="O166" s="2" t="n"/>
+      <c r="P166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -3372,6 +3734,8 @@
       <c r="L167" s="2" t="n"/>
       <c r="M167" s="2" t="n"/>
       <c r="N167" s="2" t="n"/>
+      <c r="O167" s="2" t="n"/>
+      <c r="P167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -3388,6 +3752,8 @@
       <c r="L168" s="2" t="n"/>
       <c r="M168" s="2" t="n"/>
       <c r="N168" s="2" t="n"/>
+      <c r="O168" s="2" t="n"/>
+      <c r="P168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -3404,6 +3770,8 @@
       <c r="L169" s="2" t="n"/>
       <c r="M169" s="2" t="n"/>
       <c r="N169" s="2" t="n"/>
+      <c r="O169" s="2" t="n"/>
+      <c r="P169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -3420,6 +3788,8 @@
       <c r="L170" s="2" t="n"/>
       <c r="M170" s="2" t="n"/>
       <c r="N170" s="2" t="n"/>
+      <c r="O170" s="2" t="n"/>
+      <c r="P170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -3436,6 +3806,8 @@
       <c r="L171" s="2" t="n"/>
       <c r="M171" s="2" t="n"/>
       <c r="N171" s="2" t="n"/>
+      <c r="O171" s="2" t="n"/>
+      <c r="P171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -3452,6 +3824,8 @@
       <c r="L172" s="2" t="n"/>
       <c r="M172" s="2" t="n"/>
       <c r="N172" s="2" t="n"/>
+      <c r="O172" s="2" t="n"/>
+      <c r="P172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -3468,6 +3842,8 @@
       <c r="L173" s="2" t="n"/>
       <c r="M173" s="2" t="n"/>
       <c r="N173" s="2" t="n"/>
+      <c r="O173" s="2" t="n"/>
+      <c r="P173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -3484,6 +3860,8 @@
       <c r="L174" s="2" t="n"/>
       <c r="M174" s="2" t="n"/>
       <c r="N174" s="2" t="n"/>
+      <c r="O174" s="2" t="n"/>
+      <c r="P174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -3500,6 +3878,8 @@
       <c r="L175" s="2" t="n"/>
       <c r="M175" s="2" t="n"/>
       <c r="N175" s="2" t="n"/>
+      <c r="O175" s="2" t="n"/>
+      <c r="P175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -3516,6 +3896,8 @@
       <c r="L176" s="2" t="n"/>
       <c r="M176" s="2" t="n"/>
       <c r="N176" s="2" t="n"/>
+      <c r="O176" s="2" t="n"/>
+      <c r="P176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -3532,6 +3914,8 @@
       <c r="L177" s="2" t="n"/>
       <c r="M177" s="2" t="n"/>
       <c r="N177" s="2" t="n"/>
+      <c r="O177" s="2" t="n"/>
+      <c r="P177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -3548,6 +3932,8 @@
       <c r="L178" s="2" t="n"/>
       <c r="M178" s="2" t="n"/>
       <c r="N178" s="2" t="n"/>
+      <c r="O178" s="2" t="n"/>
+      <c r="P178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -3564,6 +3950,8 @@
       <c r="L179" s="2" t="n"/>
       <c r="M179" s="2" t="n"/>
       <c r="N179" s="2" t="n"/>
+      <c r="O179" s="2" t="n"/>
+      <c r="P179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -3580,6 +3968,8 @@
       <c r="L180" s="2" t="n"/>
       <c r="M180" s="2" t="n"/>
       <c r="N180" s="2" t="n"/>
+      <c r="O180" s="2" t="n"/>
+      <c r="P180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -3596,6 +3986,8 @@
       <c r="L181" s="2" t="n"/>
       <c r="M181" s="2" t="n"/>
       <c r="N181" s="2" t="n"/>
+      <c r="O181" s="2" t="n"/>
+      <c r="P181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -3612,6 +4004,8 @@
       <c r="L182" s="2" t="n"/>
       <c r="M182" s="2" t="n"/>
       <c r="N182" s="2" t="n"/>
+      <c r="O182" s="2" t="n"/>
+      <c r="P182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
@@ -3628,6 +4022,8 @@
       <c r="L183" s="2" t="n"/>
       <c r="M183" s="2" t="n"/>
       <c r="N183" s="2" t="n"/>
+      <c r="O183" s="2" t="n"/>
+      <c r="P183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -3644,6 +4040,8 @@
       <c r="L184" s="2" t="n"/>
       <c r="M184" s="2" t="n"/>
       <c r="N184" s="2" t="n"/>
+      <c r="O184" s="2" t="n"/>
+      <c r="P184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -3660,6 +4058,8 @@
       <c r="L185" s="2" t="n"/>
       <c r="M185" s="2" t="n"/>
       <c r="N185" s="2" t="n"/>
+      <c r="O185" s="2" t="n"/>
+      <c r="P185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -3676,6 +4076,8 @@
       <c r="L186" s="2" t="n"/>
       <c r="M186" s="2" t="n"/>
       <c r="N186" s="2" t="n"/>
+      <c r="O186" s="2" t="n"/>
+      <c r="P186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
@@ -3692,6 +4094,8 @@
       <c r="L187" s="2" t="n"/>
       <c r="M187" s="2" t="n"/>
       <c r="N187" s="2" t="n"/>
+      <c r="O187" s="2" t="n"/>
+      <c r="P187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -3708,6 +4112,8 @@
       <c r="L188" s="2" t="n"/>
       <c r="M188" s="2" t="n"/>
       <c r="N188" s="2" t="n"/>
+      <c r="O188" s="2" t="n"/>
+      <c r="P188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
@@ -3724,6 +4130,8 @@
       <c r="L189" s="2" t="n"/>
       <c r="M189" s="2" t="n"/>
       <c r="N189" s="2" t="n"/>
+      <c r="O189" s="2" t="n"/>
+      <c r="P189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -3740,6 +4148,8 @@
       <c r="L190" s="2" t="n"/>
       <c r="M190" s="2" t="n"/>
       <c r="N190" s="2" t="n"/>
+      <c r="O190" s="2" t="n"/>
+      <c r="P190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
@@ -3756,6 +4166,8 @@
       <c r="L191" s="2" t="n"/>
       <c r="M191" s="2" t="n"/>
       <c r="N191" s="2" t="n"/>
+      <c r="O191" s="2" t="n"/>
+      <c r="P191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -3772,6 +4184,8 @@
       <c r="L192" s="2" t="n"/>
       <c r="M192" s="2" t="n"/>
       <c r="N192" s="2" t="n"/>
+      <c r="O192" s="2" t="n"/>
+      <c r="P192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -3788,6 +4202,8 @@
       <c r="L193" s="2" t="n"/>
       <c r="M193" s="2" t="n"/>
       <c r="N193" s="2" t="n"/>
+      <c r="O193" s="2" t="n"/>
+      <c r="P193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -3804,6 +4220,8 @@
       <c r="L194" s="2" t="n"/>
       <c r="M194" s="2" t="n"/>
       <c r="N194" s="2" t="n"/>
+      <c r="O194" s="2" t="n"/>
+      <c r="P194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -3820,6 +4238,8 @@
       <c r="L195" s="2" t="n"/>
       <c r="M195" s="2" t="n"/>
       <c r="N195" s="2" t="n"/>
+      <c r="O195" s="2" t="n"/>
+      <c r="P195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -3836,6 +4256,8 @@
       <c r="L196" s="2" t="n"/>
       <c r="M196" s="2" t="n"/>
       <c r="N196" s="2" t="n"/>
+      <c r="O196" s="2" t="n"/>
+      <c r="P196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -3852,6 +4274,8 @@
       <c r="L197" s="2" t="n"/>
       <c r="M197" s="2" t="n"/>
       <c r="N197" s="2" t="n"/>
+      <c r="O197" s="2" t="n"/>
+      <c r="P197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -3868,6 +4292,8 @@
       <c r="L198" s="2" t="n"/>
       <c r="M198" s="2" t="n"/>
       <c r="N198" s="2" t="n"/>
+      <c r="O198" s="2" t="n"/>
+      <c r="P198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -3884,6 +4310,8 @@
       <c r="L199" s="2" t="n"/>
       <c r="M199" s="2" t="n"/>
       <c r="N199" s="2" t="n"/>
+      <c r="O199" s="2" t="n"/>
+      <c r="P199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -3900,6 +4328,8 @@
       <c r="L200" s="2" t="n"/>
       <c r="M200" s="2" t="n"/>
       <c r="N200" s="2" t="n"/>
+      <c r="O200" s="2" t="n"/>
+      <c r="P200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -3916,6 +4346,8 @@
       <c r="L201" s="2" t="n"/>
       <c r="M201" s="2" t="n"/>
       <c r="N201" s="2" t="n"/>
+      <c r="O201" s="2" t="n"/>
+      <c r="P201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -3932,6 +4364,8 @@
       <c r="L202" s="2" t="n"/>
       <c r="M202" s="2" t="n"/>
       <c r="N202" s="2" t="n"/>
+      <c r="O202" s="2" t="n"/>
+      <c r="P202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -3948,6 +4382,8 @@
       <c r="L203" s="2" t="n"/>
       <c r="M203" s="2" t="n"/>
       <c r="N203" s="2" t="n"/>
+      <c r="O203" s="2" t="n"/>
+      <c r="P203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -3964,6 +4400,8 @@
       <c r="L204" s="2" t="n"/>
       <c r="M204" s="2" t="n"/>
       <c r="N204" s="2" t="n"/>
+      <c r="O204" s="2" t="n"/>
+      <c r="P204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
@@ -3980,6 +4418,8 @@
       <c r="L205" s="2" t="n"/>
       <c r="M205" s="2" t="n"/>
       <c r="N205" s="2" t="n"/>
+      <c r="O205" s="2" t="n"/>
+      <c r="P205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -3996,6 +4436,8 @@
       <c r="L206" s="2" t="n"/>
       <c r="M206" s="2" t="n"/>
       <c r="N206" s="2" t="n"/>
+      <c r="O206" s="2" t="n"/>
+      <c r="P206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
@@ -4012,6 +4454,8 @@
       <c r="L207" s="2" t="n"/>
       <c r="M207" s="2" t="n"/>
       <c r="N207" s="2" t="n"/>
+      <c r="O207" s="2" t="n"/>
+      <c r="P207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
@@ -4028,6 +4472,8 @@
       <c r="L208" s="2" t="n"/>
       <c r="M208" s="2" t="n"/>
       <c r="N208" s="2" t="n"/>
+      <c r="O208" s="2" t="n"/>
+      <c r="P208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n"/>
@@ -4044,6 +4490,8 @@
       <c r="L209" s="2" t="n"/>
       <c r="M209" s="2" t="n"/>
       <c r="N209" s="2" t="n"/>
+      <c r="O209" s="2" t="n"/>
+      <c r="P209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
@@ -4060,6 +4508,8 @@
       <c r="L210" s="2" t="n"/>
       <c r="M210" s="2" t="n"/>
       <c r="N210" s="2" t="n"/>
+      <c r="O210" s="2" t="n"/>
+      <c r="P210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n"/>
@@ -4076,6 +4526,8 @@
       <c r="L211" s="2" t="n"/>
       <c r="M211" s="2" t="n"/>
       <c r="N211" s="2" t="n"/>
+      <c r="O211" s="2" t="n"/>
+      <c r="P211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
@@ -4092,6 +4544,8 @@
       <c r="L212" s="2" t="n"/>
       <c r="M212" s="2" t="n"/>
       <c r="N212" s="2" t="n"/>
+      <c r="O212" s="2" t="n"/>
+      <c r="P212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n"/>
@@ -4108,6 +4562,8 @@
       <c r="L213" s="2" t="n"/>
       <c r="M213" s="2" t="n"/>
       <c r="N213" s="2" t="n"/>
+      <c r="O213" s="2" t="n"/>
+      <c r="P213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -4124,6 +4580,8 @@
       <c r="L214" s="2" t="n"/>
       <c r="M214" s="2" t="n"/>
       <c r="N214" s="2" t="n"/>
+      <c r="O214" s="2" t="n"/>
+      <c r="P214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n"/>
@@ -4140,6 +4598,8 @@
       <c r="L215" s="2" t="n"/>
       <c r="M215" s="2" t="n"/>
       <c r="N215" s="2" t="n"/>
+      <c r="O215" s="2" t="n"/>
+      <c r="P215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
@@ -4156,6 +4616,8 @@
       <c r="L216" s="2" t="n"/>
       <c r="M216" s="2" t="n"/>
       <c r="N216" s="2" t="n"/>
+      <c r="O216" s="2" t="n"/>
+      <c r="P216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
@@ -4172,6 +4634,8 @@
       <c r="L217" s="2" t="n"/>
       <c r="M217" s="2" t="n"/>
       <c r="N217" s="2" t="n"/>
+      <c r="O217" s="2" t="n"/>
+      <c r="P217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -4188,6 +4652,8 @@
       <c r="L218" s="2" t="n"/>
       <c r="M218" s="2" t="n"/>
       <c r="N218" s="2" t="n"/>
+      <c r="O218" s="2" t="n"/>
+      <c r="P218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
@@ -4204,6 +4670,8 @@
       <c r="L219" s="2" t="n"/>
       <c r="M219" s="2" t="n"/>
       <c r="N219" s="2" t="n"/>
+      <c r="O219" s="2" t="n"/>
+      <c r="P219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -4220,6 +4688,8 @@
       <c r="L220" s="2" t="n"/>
       <c r="M220" s="2" t="n"/>
       <c r="N220" s="2" t="n"/>
+      <c r="O220" s="2" t="n"/>
+      <c r="P220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
@@ -4236,6 +4706,8 @@
       <c r="L221" s="2" t="n"/>
       <c r="M221" s="2" t="n"/>
       <c r="N221" s="2" t="n"/>
+      <c r="O221" s="2" t="n"/>
+      <c r="P221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
@@ -4252,6 +4724,8 @@
       <c r="L222" s="2" t="n"/>
       <c r="M222" s="2" t="n"/>
       <c r="N222" s="2" t="n"/>
+      <c r="O222" s="2" t="n"/>
+      <c r="P222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n"/>
@@ -4268,6 +4742,8 @@
       <c r="L223" s="2" t="n"/>
       <c r="M223" s="2" t="n"/>
       <c r="N223" s="2" t="n"/>
+      <c r="O223" s="2" t="n"/>
+      <c r="P223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -4284,6 +4760,8 @@
       <c r="L224" s="2" t="n"/>
       <c r="M224" s="2" t="n"/>
       <c r="N224" s="2" t="n"/>
+      <c r="O224" s="2" t="n"/>
+      <c r="P224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
@@ -4300,6 +4778,8 @@
       <c r="L225" s="2" t="n"/>
       <c r="M225" s="2" t="n"/>
       <c r="N225" s="2" t="n"/>
+      <c r="O225" s="2" t="n"/>
+      <c r="P225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
@@ -4316,6 +4796,8 @@
       <c r="L226" s="2" t="n"/>
       <c r="M226" s="2" t="n"/>
       <c r="N226" s="2" t="n"/>
+      <c r="O226" s="2" t="n"/>
+      <c r="P226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
@@ -4332,6 +4814,8 @@
       <c r="L227" s="2" t="n"/>
       <c r="M227" s="2" t="n"/>
       <c r="N227" s="2" t="n"/>
+      <c r="O227" s="2" t="n"/>
+      <c r="P227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -4348,6 +4832,8 @@
       <c r="L228" s="2" t="n"/>
       <c r="M228" s="2" t="n"/>
       <c r="N228" s="2" t="n"/>
+      <c r="O228" s="2" t="n"/>
+      <c r="P228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -4364,6 +4850,8 @@
       <c r="L229" s="2" t="n"/>
       <c r="M229" s="2" t="n"/>
       <c r="N229" s="2" t="n"/>
+      <c r="O229" s="2" t="n"/>
+      <c r="P229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -4380,6 +4868,8 @@
       <c r="L230" s="2" t="n"/>
       <c r="M230" s="2" t="n"/>
       <c r="N230" s="2" t="n"/>
+      <c r="O230" s="2" t="n"/>
+      <c r="P230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
@@ -4396,6 +4886,8 @@
       <c r="L231" s="2" t="n"/>
       <c r="M231" s="2" t="n"/>
       <c r="N231" s="2" t="n"/>
+      <c r="O231" s="2" t="n"/>
+      <c r="P231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -4412,6 +4904,8 @@
       <c r="L232" s="2" t="n"/>
       <c r="M232" s="2" t="n"/>
       <c r="N232" s="2" t="n"/>
+      <c r="O232" s="2" t="n"/>
+      <c r="P232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
@@ -4428,6 +4922,8 @@
       <c r="L233" s="2" t="n"/>
       <c r="M233" s="2" t="n"/>
       <c r="N233" s="2" t="n"/>
+      <c r="O233" s="2" t="n"/>
+      <c r="P233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -4444,6 +4940,8 @@
       <c r="L234" s="2" t="n"/>
       <c r="M234" s="2" t="n"/>
       <c r="N234" s="2" t="n"/>
+      <c r="O234" s="2" t="n"/>
+      <c r="P234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
@@ -4460,6 +4958,8 @@
       <c r="L235" s="2" t="n"/>
       <c r="M235" s="2" t="n"/>
       <c r="N235" s="2" t="n"/>
+      <c r="O235" s="2" t="n"/>
+      <c r="P235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -4476,6 +4976,8 @@
       <c r="L236" s="2" t="n"/>
       <c r="M236" s="2" t="n"/>
       <c r="N236" s="2" t="n"/>
+      <c r="O236" s="2" t="n"/>
+      <c r="P236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
@@ -4492,6 +4994,8 @@
       <c r="L237" s="2" t="n"/>
       <c r="M237" s="2" t="n"/>
       <c r="N237" s="2" t="n"/>
+      <c r="O237" s="2" t="n"/>
+      <c r="P237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -4508,6 +5012,8 @@
       <c r="L238" s="2" t="n"/>
       <c r="M238" s="2" t="n"/>
       <c r="N238" s="2" t="n"/>
+      <c r="O238" s="2" t="n"/>
+      <c r="P238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
@@ -4524,6 +5030,8 @@
       <c r="L239" s="2" t="n"/>
       <c r="M239" s="2" t="n"/>
       <c r="N239" s="2" t="n"/>
+      <c r="O239" s="2" t="n"/>
+      <c r="P239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -4540,6 +5048,8 @@
       <c r="L240" s="2" t="n"/>
       <c r="M240" s="2" t="n"/>
       <c r="N240" s="2" t="n"/>
+      <c r="O240" s="2" t="n"/>
+      <c r="P240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
@@ -4556,6 +5066,8 @@
       <c r="L241" s="2" t="n"/>
       <c r="M241" s="2" t="n"/>
       <c r="N241" s="2" t="n"/>
+      <c r="O241" s="2" t="n"/>
+      <c r="P241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
@@ -4572,6 +5084,8 @@
       <c r="L242" s="2" t="n"/>
       <c r="M242" s="2" t="n"/>
       <c r="N242" s="2" t="n"/>
+      <c r="O242" s="2" t="n"/>
+      <c r="P242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n"/>
@@ -4588,6 +5102,8 @@
       <c r="L243" s="2" t="n"/>
       <c r="M243" s="2" t="n"/>
       <c r="N243" s="2" t="n"/>
+      <c r="O243" s="2" t="n"/>
+      <c r="P243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
@@ -4604,6 +5120,8 @@
       <c r="L244" s="2" t="n"/>
       <c r="M244" s="2" t="n"/>
       <c r="N244" s="2" t="n"/>
+      <c r="O244" s="2" t="n"/>
+      <c r="P244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
@@ -4620,6 +5138,8 @@
       <c r="L245" s="2" t="n"/>
       <c r="M245" s="2" t="n"/>
       <c r="N245" s="2" t="n"/>
+      <c r="O245" s="2" t="n"/>
+      <c r="P245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
@@ -4636,6 +5156,8 @@
       <c r="L246" s="2" t="n"/>
       <c r="M246" s="2" t="n"/>
       <c r="N246" s="2" t="n"/>
+      <c r="O246" s="2" t="n"/>
+      <c r="P246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n"/>
@@ -4652,6 +5174,8 @@
       <c r="L247" s="2" t="n"/>
       <c r="M247" s="2" t="n"/>
       <c r="N247" s="2" t="n"/>
+      <c r="O247" s="2" t="n"/>
+      <c r="P247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
@@ -4668,6 +5192,8 @@
       <c r="L248" s="2" t="n"/>
       <c r="M248" s="2" t="n"/>
       <c r="N248" s="2" t="n"/>
+      <c r="O248" s="2" t="n"/>
+      <c r="P248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n"/>
@@ -4684,6 +5210,8 @@
       <c r="L249" s="2" t="n"/>
       <c r="M249" s="2" t="n"/>
       <c r="N249" s="2" t="n"/>
+      <c r="O249" s="2" t="n"/>
+      <c r="P249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
@@ -4700,6 +5228,8 @@
       <c r="L250" s="2" t="n"/>
       <c r="M250" s="2" t="n"/>
       <c r="N250" s="2" t="n"/>
+      <c r="O250" s="2" t="n"/>
+      <c r="P250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
@@ -4716,6 +5246,8 @@
       <c r="L251" s="2" t="n"/>
       <c r="M251" s="2" t="n"/>
       <c r="N251" s="2" t="n"/>
+      <c r="O251" s="2" t="n"/>
+      <c r="P251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
@@ -4732,6 +5264,8 @@
       <c r="L252" s="2" t="n"/>
       <c r="M252" s="2" t="n"/>
       <c r="N252" s="2" t="n"/>
+      <c r="O252" s="2" t="n"/>
+      <c r="P252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n"/>
@@ -4748,6 +5282,8 @@
       <c r="L253" s="2" t="n"/>
       <c r="M253" s="2" t="n"/>
       <c r="N253" s="2" t="n"/>
+      <c r="O253" s="2" t="n"/>
+      <c r="P253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
@@ -4764,6 +5300,8 @@
       <c r="L254" s="2" t="n"/>
       <c r="M254" s="2" t="n"/>
       <c r="N254" s="2" t="n"/>
+      <c r="O254" s="2" t="n"/>
+      <c r="P254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n"/>
@@ -4780,6 +5318,8 @@
       <c r="L255" s="2" t="n"/>
       <c r="M255" s="2" t="n"/>
       <c r="N255" s="2" t="n"/>
+      <c r="O255" s="2" t="n"/>
+      <c r="P255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
@@ -4796,6 +5336,8 @@
       <c r="L256" s="2" t="n"/>
       <c r="M256" s="2" t="n"/>
       <c r="N256" s="2" t="n"/>
+      <c r="O256" s="2" t="n"/>
+      <c r="P256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n"/>
@@ -4812,6 +5354,8 @@
       <c r="L257" s="2" t="n"/>
       <c r="M257" s="2" t="n"/>
       <c r="N257" s="2" t="n"/>
+      <c r="O257" s="2" t="n"/>
+      <c r="P257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
@@ -4828,6 +5372,8 @@
       <c r="L258" s="2" t="n"/>
       <c r="M258" s="2" t="n"/>
       <c r="N258" s="2" t="n"/>
+      <c r="O258" s="2" t="n"/>
+      <c r="P258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n"/>
@@ -4844,6 +5390,8 @@
       <c r="L259" s="2" t="n"/>
       <c r="M259" s="2" t="n"/>
       <c r="N259" s="2" t="n"/>
+      <c r="O259" s="2" t="n"/>
+      <c r="P259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
@@ -4860,6 +5408,8 @@
       <c r="L260" s="2" t="n"/>
       <c r="M260" s="2" t="n"/>
       <c r="N260" s="2" t="n"/>
+      <c r="O260" s="2" t="n"/>
+      <c r="P260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n"/>
@@ -4876,6 +5426,8 @@
       <c r="L261" s="2" t="n"/>
       <c r="M261" s="2" t="n"/>
       <c r="N261" s="2" t="n"/>
+      <c r="O261" s="2" t="n"/>
+      <c r="P261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
@@ -4892,6 +5444,8 @@
       <c r="L262" s="2" t="n"/>
       <c r="M262" s="2" t="n"/>
       <c r="N262" s="2" t="n"/>
+      <c r="O262" s="2" t="n"/>
+      <c r="P262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n"/>
@@ -4908,6 +5462,8 @@
       <c r="L263" s="2" t="n"/>
       <c r="M263" s="2" t="n"/>
       <c r="N263" s="2" t="n"/>
+      <c r="O263" s="2" t="n"/>
+      <c r="P263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
@@ -4924,6 +5480,8 @@
       <c r="L264" s="2" t="n"/>
       <c r="M264" s="2" t="n"/>
       <c r="N264" s="2" t="n"/>
+      <c r="O264" s="2" t="n"/>
+      <c r="P264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n"/>
@@ -4940,6 +5498,8 @@
       <c r="L265" s="2" t="n"/>
       <c r="M265" s="2" t="n"/>
       <c r="N265" s="2" t="n"/>
+      <c r="O265" s="2" t="n"/>
+      <c r="P265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
@@ -4956,6 +5516,8 @@
       <c r="L266" s="2" t="n"/>
       <c r="M266" s="2" t="n"/>
       <c r="N266" s="2" t="n"/>
+      <c r="O266" s="2" t="n"/>
+      <c r="P266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n"/>
@@ -4972,6 +5534,8 @@
       <c r="L267" s="2" t="n"/>
       <c r="M267" s="2" t="n"/>
       <c r="N267" s="2" t="n"/>
+      <c r="O267" s="2" t="n"/>
+      <c r="P267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
@@ -4988,6 +5552,8 @@
       <c r="L268" s="2" t="n"/>
       <c r="M268" s="2" t="n"/>
       <c r="N268" s="2" t="n"/>
+      <c r="O268" s="2" t="n"/>
+      <c r="P268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n"/>
@@ -5004,6 +5570,8 @@
       <c r="L269" s="2" t="n"/>
       <c r="M269" s="2" t="n"/>
       <c r="N269" s="2" t="n"/>
+      <c r="O269" s="2" t="n"/>
+      <c r="P269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
@@ -5020,6 +5588,8 @@
       <c r="L270" s="2" t="n"/>
       <c r="M270" s="2" t="n"/>
       <c r="N270" s="2" t="n"/>
+      <c r="O270" s="2" t="n"/>
+      <c r="P270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n"/>
@@ -5036,6 +5606,8 @@
       <c r="L271" s="2" t="n"/>
       <c r="M271" s="2" t="n"/>
       <c r="N271" s="2" t="n"/>
+      <c r="O271" s="2" t="n"/>
+      <c r="P271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
@@ -5052,6 +5624,8 @@
       <c r="L272" s="2" t="n"/>
       <c r="M272" s="2" t="n"/>
       <c r="N272" s="2" t="n"/>
+      <c r="O272" s="2" t="n"/>
+      <c r="P272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n"/>
@@ -5068,6 +5642,8 @@
       <c r="L273" s="2" t="n"/>
       <c r="M273" s="2" t="n"/>
       <c r="N273" s="2" t="n"/>
+      <c r="O273" s="2" t="n"/>
+      <c r="P273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
@@ -5084,6 +5660,8 @@
       <c r="L274" s="2" t="n"/>
       <c r="M274" s="2" t="n"/>
       <c r="N274" s="2" t="n"/>
+      <c r="O274" s="2" t="n"/>
+      <c r="P274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n"/>
@@ -5100,6 +5678,8 @@
       <c r="L275" s="2" t="n"/>
       <c r="M275" s="2" t="n"/>
       <c r="N275" s="2" t="n"/>
+      <c r="O275" s="2" t="n"/>
+      <c r="P275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
@@ -5116,6 +5696,8 @@
       <c r="L276" s="2" t="n"/>
       <c r="M276" s="2" t="n"/>
       <c r="N276" s="2" t="n"/>
+      <c r="O276" s="2" t="n"/>
+      <c r="P276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n"/>
@@ -5132,6 +5714,8 @@
       <c r="L277" s="2" t="n"/>
       <c r="M277" s="2" t="n"/>
       <c r="N277" s="2" t="n"/>
+      <c r="O277" s="2" t="n"/>
+      <c r="P277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
@@ -5148,6 +5732,8 @@
       <c r="L278" s="2" t="n"/>
       <c r="M278" s="2" t="n"/>
       <c r="N278" s="2" t="n"/>
+      <c r="O278" s="2" t="n"/>
+      <c r="P278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n"/>
@@ -5164,6 +5750,8 @@
       <c r="L279" s="2" t="n"/>
       <c r="M279" s="2" t="n"/>
       <c r="N279" s="2" t="n"/>
+      <c r="O279" s="2" t="n"/>
+      <c r="P279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
@@ -5180,6 +5768,8 @@
       <c r="L280" s="2" t="n"/>
       <c r="M280" s="2" t="n"/>
       <c r="N280" s="2" t="n"/>
+      <c r="O280" s="2" t="n"/>
+      <c r="P280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n"/>
@@ -5196,6 +5786,8 @@
       <c r="L281" s="2" t="n"/>
       <c r="M281" s="2" t="n"/>
       <c r="N281" s="2" t="n"/>
+      <c r="O281" s="2" t="n"/>
+      <c r="P281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
@@ -5212,6 +5804,8 @@
       <c r="L282" s="2" t="n"/>
       <c r="M282" s="2" t="n"/>
       <c r="N282" s="2" t="n"/>
+      <c r="O282" s="2" t="n"/>
+      <c r="P282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n"/>
@@ -5228,6 +5822,8 @@
       <c r="L283" s="2" t="n"/>
       <c r="M283" s="2" t="n"/>
       <c r="N283" s="2" t="n"/>
+      <c r="O283" s="2" t="n"/>
+      <c r="P283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
@@ -5244,6 +5840,8 @@
       <c r="L284" s="2" t="n"/>
       <c r="M284" s="2" t="n"/>
       <c r="N284" s="2" t="n"/>
+      <c r="O284" s="2" t="n"/>
+      <c r="P284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n"/>
@@ -5260,6 +5858,8 @@
       <c r="L285" s="2" t="n"/>
       <c r="M285" s="2" t="n"/>
       <c r="N285" s="2" t="n"/>
+      <c r="O285" s="2" t="n"/>
+      <c r="P285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
@@ -5276,6 +5876,8 @@
       <c r="L286" s="2" t="n"/>
       <c r="M286" s="2" t="n"/>
       <c r="N286" s="2" t="n"/>
+      <c r="O286" s="2" t="n"/>
+      <c r="P286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n"/>
@@ -5292,6 +5894,8 @@
       <c r="L287" s="2" t="n"/>
       <c r="M287" s="2" t="n"/>
       <c r="N287" s="2" t="n"/>
+      <c r="O287" s="2" t="n"/>
+      <c r="P287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
@@ -5308,6 +5912,8 @@
       <c r="L288" s="2" t="n"/>
       <c r="M288" s="2" t="n"/>
       <c r="N288" s="2" t="n"/>
+      <c r="O288" s="2" t="n"/>
+      <c r="P288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n"/>
@@ -5324,6 +5930,8 @@
       <c r="L289" s="2" t="n"/>
       <c r="M289" s="2" t="n"/>
       <c r="N289" s="2" t="n"/>
+      <c r="O289" s="2" t="n"/>
+      <c r="P289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
@@ -5340,6 +5948,8 @@
       <c r="L290" s="2" t="n"/>
       <c r="M290" s="2" t="n"/>
       <c r="N290" s="2" t="n"/>
+      <c r="O290" s="2" t="n"/>
+      <c r="P290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n"/>
@@ -5356,6 +5966,8 @@
       <c r="L291" s="2" t="n"/>
       <c r="M291" s="2" t="n"/>
       <c r="N291" s="2" t="n"/>
+      <c r="O291" s="2" t="n"/>
+      <c r="P291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
@@ -5372,6 +5984,8 @@
       <c r="L292" s="2" t="n"/>
       <c r="M292" s="2" t="n"/>
       <c r="N292" s="2" t="n"/>
+      <c r="O292" s="2" t="n"/>
+      <c r="P292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n"/>
@@ -5388,6 +6002,8 @@
       <c r="L293" s="2" t="n"/>
       <c r="M293" s="2" t="n"/>
       <c r="N293" s="2" t="n"/>
+      <c r="O293" s="2" t="n"/>
+      <c r="P293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
@@ -5404,6 +6020,8 @@
       <c r="L294" s="2" t="n"/>
       <c r="M294" s="2" t="n"/>
       <c r="N294" s="2" t="n"/>
+      <c r="O294" s="2" t="n"/>
+      <c r="P294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n"/>
@@ -5420,6 +6038,8 @@
       <c r="L295" s="2" t="n"/>
       <c r="M295" s="2" t="n"/>
       <c r="N295" s="2" t="n"/>
+      <c r="O295" s="2" t="n"/>
+      <c r="P295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
@@ -5436,6 +6056,8 @@
       <c r="L296" s="2" t="n"/>
       <c r="M296" s="2" t="n"/>
       <c r="N296" s="2" t="n"/>
+      <c r="O296" s="2" t="n"/>
+      <c r="P296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n"/>
@@ -5452,6 +6074,8 @@
       <c r="L297" s="2" t="n"/>
       <c r="M297" s="2" t="n"/>
       <c r="N297" s="2" t="n"/>
+      <c r="O297" s="2" t="n"/>
+      <c r="P297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
@@ -5468,6 +6092,8 @@
       <c r="L298" s="2" t="n"/>
       <c r="M298" s="2" t="n"/>
       <c r="N298" s="2" t="n"/>
+      <c r="O298" s="2" t="n"/>
+      <c r="P298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n"/>
@@ -5484,6 +6110,8 @@
       <c r="L299" s="2" t="n"/>
       <c r="M299" s="2" t="n"/>
       <c r="N299" s="2" t="n"/>
+      <c r="O299" s="2" t="n"/>
+      <c r="P299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
@@ -5500,6 +6128,8 @@
       <c r="L300" s="2" t="n"/>
       <c r="M300" s="2" t="n"/>
       <c r="N300" s="2" t="n"/>
+      <c r="O300" s="2" t="n"/>
+      <c r="P300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n"/>
@@ -5516,6 +6146,8 @@
       <c r="L301" s="2" t="n"/>
       <c r="M301" s="2" t="n"/>
       <c r="N301" s="2" t="n"/>
+      <c r="O301" s="2" t="n"/>
+      <c r="P301" s="2" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n"/>
@@ -5532,6 +6164,8 @@
       <c r="L302" s="2" t="n"/>
       <c r="M302" s="2" t="n"/>
       <c r="N302" s="2" t="n"/>
+      <c r="O302" s="2" t="n"/>
+      <c r="P302" s="2" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n"/>
@@ -5548,6 +6182,8 @@
       <c r="L303" s="2" t="n"/>
       <c r="M303" s="2" t="n"/>
       <c r="N303" s="2" t="n"/>
+      <c r="O303" s="2" t="n"/>
+      <c r="P303" s="2" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n"/>
@@ -5564,6 +6200,8 @@
       <c r="L304" s="2" t="n"/>
       <c r="M304" s="2" t="n"/>
       <c r="N304" s="2" t="n"/>
+      <c r="O304" s="2" t="n"/>
+      <c r="P304" s="2" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n"/>
@@ -5580,6 +6218,8 @@
       <c r="L305" s="2" t="n"/>
       <c r="M305" s="2" t="n"/>
       <c r="N305" s="2" t="n"/>
+      <c r="O305" s="2" t="n"/>
+      <c r="P305" s="2" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n"/>
@@ -5596,6 +6236,8 @@
       <c r="L306" s="2" t="n"/>
       <c r="M306" s="2" t="n"/>
       <c r="N306" s="2" t="n"/>
+      <c r="O306" s="2" t="n"/>
+      <c r="P306" s="2" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n"/>
@@ -5612,6 +6254,8 @@
       <c r="L307" s="2" t="n"/>
       <c r="M307" s="2" t="n"/>
       <c r="N307" s="2" t="n"/>
+      <c r="O307" s="2" t="n"/>
+      <c r="P307" s="2" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n"/>
@@ -5628,6 +6272,8 @@
       <c r="L308" s="2" t="n"/>
       <c r="M308" s="2" t="n"/>
       <c r="N308" s="2" t="n"/>
+      <c r="O308" s="2" t="n"/>
+      <c r="P308" s="2" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n"/>
@@ -5644,6 +6290,8 @@
       <c r="L309" s="2" t="n"/>
       <c r="M309" s="2" t="n"/>
       <c r="N309" s="2" t="n"/>
+      <c r="O309" s="2" t="n"/>
+      <c r="P309" s="2" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n"/>
@@ -5660,6 +6308,8 @@
       <c r="L310" s="2" t="n"/>
       <c r="M310" s="2" t="n"/>
       <c r="N310" s="2" t="n"/>
+      <c r="O310" s="2" t="n"/>
+      <c r="P310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n"/>
@@ -5676,6 +6326,8 @@
       <c r="L311" s="2" t="n"/>
       <c r="M311" s="2" t="n"/>
       <c r="N311" s="2" t="n"/>
+      <c r="O311" s="2" t="n"/>
+      <c r="P311" s="2" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n"/>
@@ -5692,6 +6344,8 @@
       <c r="L312" s="2" t="n"/>
       <c r="M312" s="2" t="n"/>
       <c r="N312" s="2" t="n"/>
+      <c r="O312" s="2" t="n"/>
+      <c r="P312" s="2" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n"/>
@@ -5708,6 +6362,8 @@
       <c r="L313" s="2" t="n"/>
       <c r="M313" s="2" t="n"/>
       <c r="N313" s="2" t="n"/>
+      <c r="O313" s="2" t="n"/>
+      <c r="P313" s="2" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n"/>
@@ -5724,6 +6380,8 @@
       <c r="L314" s="2" t="n"/>
       <c r="M314" s="2" t="n"/>
       <c r="N314" s="2" t="n"/>
+      <c r="O314" s="2" t="n"/>
+      <c r="P314" s="2" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n"/>
@@ -5740,6 +6398,8 @@
       <c r="L315" s="2" t="n"/>
       <c r="M315" s="2" t="n"/>
       <c r="N315" s="2" t="n"/>
+      <c r="O315" s="2" t="n"/>
+      <c r="P315" s="2" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n"/>
@@ -5756,6 +6416,8 @@
       <c r="L316" s="2" t="n"/>
       <c r="M316" s="2" t="n"/>
       <c r="N316" s="2" t="n"/>
+      <c r="O316" s="2" t="n"/>
+      <c r="P316" s="2" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n"/>
@@ -5772,6 +6434,8 @@
       <c r="L317" s="2" t="n"/>
       <c r="M317" s="2" t="n"/>
       <c r="N317" s="2" t="n"/>
+      <c r="O317" s="2" t="n"/>
+      <c r="P317" s="2" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n"/>
@@ -5788,6 +6452,8 @@
       <c r="L318" s="2" t="n"/>
       <c r="M318" s="2" t="n"/>
       <c r="N318" s="2" t="n"/>
+      <c r="O318" s="2" t="n"/>
+      <c r="P318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n"/>
@@ -5804,6 +6470,8 @@
       <c r="L319" s="2" t="n"/>
       <c r="M319" s="2" t="n"/>
       <c r="N319" s="2" t="n"/>
+      <c r="O319" s="2" t="n"/>
+      <c r="P319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n"/>
@@ -5820,6 +6488,8 @@
       <c r="L320" s="2" t="n"/>
       <c r="M320" s="2" t="n"/>
       <c r="N320" s="2" t="n"/>
+      <c r="O320" s="2" t="n"/>
+      <c r="P320" s="2" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n"/>
@@ -5836,6 +6506,8 @@
       <c r="L321" s="2" t="n"/>
       <c r="M321" s="2" t="n"/>
       <c r="N321" s="2" t="n"/>
+      <c r="O321" s="2" t="n"/>
+      <c r="P321" s="2" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n"/>
@@ -5852,6 +6524,8 @@
       <c r="L322" s="2" t="n"/>
       <c r="M322" s="2" t="n"/>
       <c r="N322" s="2" t="n"/>
+      <c r="O322" s="2" t="n"/>
+      <c r="P322" s="2" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n"/>
@@ -5868,6 +6542,8 @@
       <c r="L323" s="2" t="n"/>
       <c r="M323" s="2" t="n"/>
       <c r="N323" s="2" t="n"/>
+      <c r="O323" s="2" t="n"/>
+      <c r="P323" s="2" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n"/>
@@ -5884,6 +6560,8 @@
       <c r="L324" s="2" t="n"/>
       <c r="M324" s="2" t="n"/>
       <c r="N324" s="2" t="n"/>
+      <c r="O324" s="2" t="n"/>
+      <c r="P324" s="2" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n"/>
@@ -5900,6 +6578,8 @@
       <c r="L325" s="2" t="n"/>
       <c r="M325" s="2" t="n"/>
       <c r="N325" s="2" t="n"/>
+      <c r="O325" s="2" t="n"/>
+      <c r="P325" s="2" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n"/>
@@ -5916,6 +6596,8 @@
       <c r="L326" s="2" t="n"/>
       <c r="M326" s="2" t="n"/>
       <c r="N326" s="2" t="n"/>
+      <c r="O326" s="2" t="n"/>
+      <c r="P326" s="2" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n"/>
@@ -5932,6 +6614,8 @@
       <c r="L327" s="2" t="n"/>
       <c r="M327" s="2" t="n"/>
       <c r="N327" s="2" t="n"/>
+      <c r="O327" s="2" t="n"/>
+      <c r="P327" s="2" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n"/>
@@ -5948,6 +6632,8 @@
       <c r="L328" s="2" t="n"/>
       <c r="M328" s="2" t="n"/>
       <c r="N328" s="2" t="n"/>
+      <c r="O328" s="2" t="n"/>
+      <c r="P328" s="2" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n"/>
@@ -5964,6 +6650,8 @@
       <c r="L329" s="2" t="n"/>
       <c r="M329" s="2" t="n"/>
       <c r="N329" s="2" t="n"/>
+      <c r="O329" s="2" t="n"/>
+      <c r="P329" s="2" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n"/>
@@ -5980,6 +6668,8 @@
       <c r="L330" s="2" t="n"/>
       <c r="M330" s="2" t="n"/>
       <c r="N330" s="2" t="n"/>
+      <c r="O330" s="2" t="n"/>
+      <c r="P330" s="2" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n"/>
@@ -5996,6 +6686,8 @@
       <c r="L331" s="2" t="n"/>
       <c r="M331" s="2" t="n"/>
       <c r="N331" s="2" t="n"/>
+      <c r="O331" s="2" t="n"/>
+      <c r="P331" s="2" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n"/>
@@ -6012,6 +6704,8 @@
       <c r="L332" s="2" t="n"/>
       <c r="M332" s="2" t="n"/>
       <c r="N332" s="2" t="n"/>
+      <c r="O332" s="2" t="n"/>
+      <c r="P332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n"/>
@@ -6028,6 +6722,8 @@
       <c r="L333" s="2" t="n"/>
       <c r="M333" s="2" t="n"/>
       <c r="N333" s="2" t="n"/>
+      <c r="O333" s="2" t="n"/>
+      <c r="P333" s="2" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n"/>
@@ -6044,6 +6740,8 @@
       <c r="L334" s="2" t="n"/>
       <c r="M334" s="2" t="n"/>
       <c r="N334" s="2" t="n"/>
+      <c r="O334" s="2" t="n"/>
+      <c r="P334" s="2" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n"/>
@@ -6060,6 +6758,8 @@
       <c r="L335" s="2" t="n"/>
       <c r="M335" s="2" t="n"/>
       <c r="N335" s="2" t="n"/>
+      <c r="O335" s="2" t="n"/>
+      <c r="P335" s="2" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n"/>
@@ -6076,6 +6776,8 @@
       <c r="L336" s="2" t="n"/>
       <c r="M336" s="2" t="n"/>
       <c r="N336" s="2" t="n"/>
+      <c r="O336" s="2" t="n"/>
+      <c r="P336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n"/>
@@ -6092,6 +6794,8 @@
       <c r="L337" s="2" t="n"/>
       <c r="M337" s="2" t="n"/>
       <c r="N337" s="2" t="n"/>
+      <c r="O337" s="2" t="n"/>
+      <c r="P337" s="2" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n"/>
@@ -6108,6 +6812,8 @@
       <c r="L338" s="2" t="n"/>
       <c r="M338" s="2" t="n"/>
       <c r="N338" s="2" t="n"/>
+      <c r="O338" s="2" t="n"/>
+      <c r="P338" s="2" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n"/>
@@ -6124,6 +6830,8 @@
       <c r="L339" s="2" t="n"/>
       <c r="M339" s="2" t="n"/>
       <c r="N339" s="2" t="n"/>
+      <c r="O339" s="2" t="n"/>
+      <c r="P339" s="2" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n"/>
@@ -6140,6 +6848,8 @@
       <c r="L340" s="2" t="n"/>
       <c r="M340" s="2" t="n"/>
       <c r="N340" s="2" t="n"/>
+      <c r="O340" s="2" t="n"/>
+      <c r="P340" s="2" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n"/>
@@ -6156,6 +6866,8 @@
       <c r="L341" s="2" t="n"/>
       <c r="M341" s="2" t="n"/>
       <c r="N341" s="2" t="n"/>
+      <c r="O341" s="2" t="n"/>
+      <c r="P341" s="2" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n"/>
@@ -6172,6 +6884,8 @@
       <c r="L342" s="2" t="n"/>
       <c r="M342" s="2" t="n"/>
       <c r="N342" s="2" t="n"/>
+      <c r="O342" s="2" t="n"/>
+      <c r="P342" s="2" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n"/>
@@ -6188,6 +6902,8 @@
       <c r="L343" s="2" t="n"/>
       <c r="M343" s="2" t="n"/>
       <c r="N343" s="2" t="n"/>
+      <c r="O343" s="2" t="n"/>
+      <c r="P343" s="2" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n"/>
@@ -6204,6 +6920,8 @@
       <c r="L344" s="2" t="n"/>
       <c r="M344" s="2" t="n"/>
       <c r="N344" s="2" t="n"/>
+      <c r="O344" s="2" t="n"/>
+      <c r="P344" s="2" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n"/>
@@ -6220,6 +6938,8 @@
       <c r="L345" s="2" t="n"/>
       <c r="M345" s="2" t="n"/>
       <c r="N345" s="2" t="n"/>
+      <c r="O345" s="2" t="n"/>
+      <c r="P345" s="2" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n"/>
@@ -6236,6 +6956,8 @@
       <c r="L346" s="2" t="n"/>
       <c r="M346" s="2" t="n"/>
       <c r="N346" s="2" t="n"/>
+      <c r="O346" s="2" t="n"/>
+      <c r="P346" s="2" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n"/>
@@ -6252,6 +6974,8 @@
       <c r="L347" s="2" t="n"/>
       <c r="M347" s="2" t="n"/>
       <c r="N347" s="2" t="n"/>
+      <c r="O347" s="2" t="n"/>
+      <c r="P347" s="2" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n"/>
@@ -6268,6 +6992,8 @@
       <c r="L348" s="2" t="n"/>
       <c r="M348" s="2" t="n"/>
       <c r="N348" s="2" t="n"/>
+      <c r="O348" s="2" t="n"/>
+      <c r="P348" s="2" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n"/>
@@ -6284,6 +7010,8 @@
       <c r="L349" s="2" t="n"/>
       <c r="M349" s="2" t="n"/>
       <c r="N349" s="2" t="n"/>
+      <c r="O349" s="2" t="n"/>
+      <c r="P349" s="2" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n"/>
@@ -6300,6 +7028,8 @@
       <c r="L350" s="2" t="n"/>
       <c r="M350" s="2" t="n"/>
       <c r="N350" s="2" t="n"/>
+      <c r="O350" s="2" t="n"/>
+      <c r="P350" s="2" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n"/>
@@ -6316,6 +7046,8 @@
       <c r="L351" s="2" t="n"/>
       <c r="M351" s="2" t="n"/>
       <c r="N351" s="2" t="n"/>
+      <c r="O351" s="2" t="n"/>
+      <c r="P351" s="2" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n"/>
@@ -6332,6 +7064,8 @@
       <c r="L352" s="2" t="n"/>
       <c r="M352" s="2" t="n"/>
       <c r="N352" s="2" t="n"/>
+      <c r="O352" s="2" t="n"/>
+      <c r="P352" s="2" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n"/>
@@ -6348,6 +7082,8 @@
       <c r="L353" s="2" t="n"/>
       <c r="M353" s="2" t="n"/>
       <c r="N353" s="2" t="n"/>
+      <c r="O353" s="2" t="n"/>
+      <c r="P353" s="2" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n"/>
@@ -6364,6 +7100,8 @@
       <c r="L354" s="2" t="n"/>
       <c r="M354" s="2" t="n"/>
       <c r="N354" s="2" t="n"/>
+      <c r="O354" s="2" t="n"/>
+      <c r="P354" s="2" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n"/>
@@ -6380,6 +7118,8 @@
       <c r="L355" s="2" t="n"/>
       <c r="M355" s="2" t="n"/>
       <c r="N355" s="2" t="n"/>
+      <c r="O355" s="2" t="n"/>
+      <c r="P355" s="2" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n"/>
@@ -6396,6 +7136,8 @@
       <c r="L356" s="2" t="n"/>
       <c r="M356" s="2" t="n"/>
       <c r="N356" s="2" t="n"/>
+      <c r="O356" s="2" t="n"/>
+      <c r="P356" s="2" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n"/>
@@ -6412,6 +7154,8 @@
       <c r="L357" s="2" t="n"/>
       <c r="M357" s="2" t="n"/>
       <c r="N357" s="2" t="n"/>
+      <c r="O357" s="2" t="n"/>
+      <c r="P357" s="2" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n"/>
@@ -6428,6 +7172,8 @@
       <c r="L358" s="2" t="n"/>
       <c r="M358" s="2" t="n"/>
       <c r="N358" s="2" t="n"/>
+      <c r="O358" s="2" t="n"/>
+      <c r="P358" s="2" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n"/>
@@ -6444,6 +7190,8 @@
       <c r="L359" s="2" t="n"/>
       <c r="M359" s="2" t="n"/>
       <c r="N359" s="2" t="n"/>
+      <c r="O359" s="2" t="n"/>
+      <c r="P359" s="2" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n"/>
@@ -6460,6 +7208,8 @@
       <c r="L360" s="2" t="n"/>
       <c r="M360" s="2" t="n"/>
       <c r="N360" s="2" t="n"/>
+      <c r="O360" s="2" t="n"/>
+      <c r="P360" s="2" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n"/>
@@ -6476,6 +7226,8 @@
       <c r="L361" s="2" t="n"/>
       <c r="M361" s="2" t="n"/>
       <c r="N361" s="2" t="n"/>
+      <c r="O361" s="2" t="n"/>
+      <c r="P361" s="2" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n"/>
@@ -6492,6 +7244,8 @@
       <c r="L362" s="2" t="n"/>
       <c r="M362" s="2" t="n"/>
       <c r="N362" s="2" t="n"/>
+      <c r="O362" s="2" t="n"/>
+      <c r="P362" s="2" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n"/>
@@ -6508,6 +7262,8 @@
       <c r="L363" s="2" t="n"/>
       <c r="M363" s="2" t="n"/>
       <c r="N363" s="2" t="n"/>
+      <c r="O363" s="2" t="n"/>
+      <c r="P363" s="2" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n"/>
@@ -6524,6 +7280,8 @@
       <c r="L364" s="2" t="n"/>
       <c r="M364" s="2" t="n"/>
       <c r="N364" s="2" t="n"/>
+      <c r="O364" s="2" t="n"/>
+      <c r="P364" s="2" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n"/>
@@ -6540,6 +7298,8 @@
       <c r="L365" s="2" t="n"/>
       <c r="M365" s="2" t="n"/>
       <c r="N365" s="2" t="n"/>
+      <c r="O365" s="2" t="n"/>
+      <c r="P365" s="2" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n"/>
@@ -6556,6 +7316,8 @@
       <c r="L366" s="2" t="n"/>
       <c r="M366" s="2" t="n"/>
       <c r="N366" s="2" t="n"/>
+      <c r="O366" s="2" t="n"/>
+      <c r="P366" s="2" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n"/>
@@ -6572,6 +7334,8 @@
       <c r="L367" s="2" t="n"/>
       <c r="M367" s="2" t="n"/>
       <c r="N367" s="2" t="n"/>
+      <c r="O367" s="2" t="n"/>
+      <c r="P367" s="2" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n"/>
@@ -6588,6 +7352,8 @@
       <c r="L368" s="2" t="n"/>
       <c r="M368" s="2" t="n"/>
       <c r="N368" s="2" t="n"/>
+      <c r="O368" s="2" t="n"/>
+      <c r="P368" s="2" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n"/>
@@ -6604,6 +7370,8 @@
       <c r="L369" s="2" t="n"/>
       <c r="M369" s="2" t="n"/>
       <c r="N369" s="2" t="n"/>
+      <c r="O369" s="2" t="n"/>
+      <c r="P369" s="2" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n"/>
@@ -6620,6 +7388,8 @@
       <c r="L370" s="2" t="n"/>
       <c r="M370" s="2" t="n"/>
       <c r="N370" s="2" t="n"/>
+      <c r="O370" s="2" t="n"/>
+      <c r="P370" s="2" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n"/>
@@ -6636,6 +7406,8 @@
       <c r="L371" s="2" t="n"/>
       <c r="M371" s="2" t="n"/>
       <c r="N371" s="2" t="n"/>
+      <c r="O371" s="2" t="n"/>
+      <c r="P371" s="2" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n"/>
@@ -6652,6 +7424,8 @@
       <c r="L372" s="2" t="n"/>
       <c r="M372" s="2" t="n"/>
       <c r="N372" s="2" t="n"/>
+      <c r="O372" s="2" t="n"/>
+      <c r="P372" s="2" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n"/>
@@ -6668,6 +7442,8 @@
       <c r="L373" s="2" t="n"/>
       <c r="M373" s="2" t="n"/>
       <c r="N373" s="2" t="n"/>
+      <c r="O373" s="2" t="n"/>
+      <c r="P373" s="2" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n"/>
@@ -6684,6 +7460,8 @@
       <c r="L374" s="2" t="n"/>
       <c r="M374" s="2" t="n"/>
       <c r="N374" s="2" t="n"/>
+      <c r="O374" s="2" t="n"/>
+      <c r="P374" s="2" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n"/>
@@ -6700,6 +7478,8 @@
       <c r="L375" s="2" t="n"/>
       <c r="M375" s="2" t="n"/>
       <c r="N375" s="2" t="n"/>
+      <c r="O375" s="2" t="n"/>
+      <c r="P375" s="2" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n"/>
@@ -6716,6 +7496,8 @@
       <c r="L376" s="2" t="n"/>
       <c r="M376" s="2" t="n"/>
       <c r="N376" s="2" t="n"/>
+      <c r="O376" s="2" t="n"/>
+      <c r="P376" s="2" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n"/>
@@ -6732,6 +7514,8 @@
       <c r="L377" s="2" t="n"/>
       <c r="M377" s="2" t="n"/>
       <c r="N377" s="2" t="n"/>
+      <c r="O377" s="2" t="n"/>
+      <c r="P377" s="2" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n"/>
@@ -6748,6 +7532,8 @@
       <c r="L378" s="2" t="n"/>
       <c r="M378" s="2" t="n"/>
       <c r="N378" s="2" t="n"/>
+      <c r="O378" s="2" t="n"/>
+      <c r="P378" s="2" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n"/>
@@ -6764,6 +7550,8 @@
       <c r="L379" s="2" t="n"/>
       <c r="M379" s="2" t="n"/>
       <c r="N379" s="2" t="n"/>
+      <c r="O379" s="2" t="n"/>
+      <c r="P379" s="2" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n"/>
@@ -6780,6 +7568,8 @@
       <c r="L380" s="2" t="n"/>
       <c r="M380" s="2" t="n"/>
       <c r="N380" s="2" t="n"/>
+      <c r="O380" s="2" t="n"/>
+      <c r="P380" s="2" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n"/>
@@ -6796,6 +7586,8 @@
       <c r="L381" s="2" t="n"/>
       <c r="M381" s="2" t="n"/>
       <c r="N381" s="2" t="n"/>
+      <c r="O381" s="2" t="n"/>
+      <c r="P381" s="2" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n"/>
@@ -6812,6 +7604,8 @@
       <c r="L382" s="2" t="n"/>
       <c r="M382" s="2" t="n"/>
       <c r="N382" s="2" t="n"/>
+      <c r="O382" s="2" t="n"/>
+      <c r="P382" s="2" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n"/>
@@ -6828,6 +7622,8 @@
       <c r="L383" s="2" t="n"/>
       <c r="M383" s="2" t="n"/>
       <c r="N383" s="2" t="n"/>
+      <c r="O383" s="2" t="n"/>
+      <c r="P383" s="2" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n"/>
@@ -6844,6 +7640,8 @@
       <c r="L384" s="2" t="n"/>
       <c r="M384" s="2" t="n"/>
       <c r="N384" s="2" t="n"/>
+      <c r="O384" s="2" t="n"/>
+      <c r="P384" s="2" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n"/>
@@ -6860,6 +7658,8 @@
       <c r="L385" s="2" t="n"/>
       <c r="M385" s="2" t="n"/>
       <c r="N385" s="2" t="n"/>
+      <c r="O385" s="2" t="n"/>
+      <c r="P385" s="2" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n"/>
@@ -6876,6 +7676,8 @@
       <c r="L386" s="2" t="n"/>
       <c r="M386" s="2" t="n"/>
       <c r="N386" s="2" t="n"/>
+      <c r="O386" s="2" t="n"/>
+      <c r="P386" s="2" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n"/>
@@ -6892,6 +7694,8 @@
       <c r="L387" s="2" t="n"/>
       <c r="M387" s="2" t="n"/>
       <c r="N387" s="2" t="n"/>
+      <c r="O387" s="2" t="n"/>
+      <c r="P387" s="2" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n"/>
@@ -6908,6 +7712,8 @@
       <c r="L388" s="2" t="n"/>
       <c r="M388" s="2" t="n"/>
       <c r="N388" s="2" t="n"/>
+      <c r="O388" s="2" t="n"/>
+      <c r="P388" s="2" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n"/>
@@ -6924,6 +7730,8 @@
       <c r="L389" s="2" t="n"/>
       <c r="M389" s="2" t="n"/>
       <c r="N389" s="2" t="n"/>
+      <c r="O389" s="2" t="n"/>
+      <c r="P389" s="2" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n"/>
@@ -6940,6 +7748,8 @@
       <c r="L390" s="2" t="n"/>
       <c r="M390" s="2" t="n"/>
       <c r="N390" s="2" t="n"/>
+      <c r="O390" s="2" t="n"/>
+      <c r="P390" s="2" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n"/>
@@ -6956,6 +7766,8 @@
       <c r="L391" s="2" t="n"/>
       <c r="M391" s="2" t="n"/>
       <c r="N391" s="2" t="n"/>
+      <c r="O391" s="2" t="n"/>
+      <c r="P391" s="2" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n"/>
@@ -6972,6 +7784,8 @@
       <c r="L392" s="2" t="n"/>
       <c r="M392" s="2" t="n"/>
       <c r="N392" s="2" t="n"/>
+      <c r="O392" s="2" t="n"/>
+      <c r="P392" s="2" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n"/>
@@ -6988,6 +7802,8 @@
       <c r="L393" s="2" t="n"/>
       <c r="M393" s="2" t="n"/>
       <c r="N393" s="2" t="n"/>
+      <c r="O393" s="2" t="n"/>
+      <c r="P393" s="2" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n"/>
@@ -7004,6 +7820,8 @@
       <c r="L394" s="2" t="n"/>
       <c r="M394" s="2" t="n"/>
       <c r="N394" s="2" t="n"/>
+      <c r="O394" s="2" t="n"/>
+      <c r="P394" s="2" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n"/>
@@ -7020,6 +7838,8 @@
       <c r="L395" s="2" t="n"/>
       <c r="M395" s="2" t="n"/>
       <c r="N395" s="2" t="n"/>
+      <c r="O395" s="2" t="n"/>
+      <c r="P395" s="2" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n"/>
@@ -7036,6 +7856,8 @@
       <c r="L396" s="2" t="n"/>
       <c r="M396" s="2" t="n"/>
       <c r="N396" s="2" t="n"/>
+      <c r="O396" s="2" t="n"/>
+      <c r="P396" s="2" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n"/>
@@ -7052,6 +7874,8 @@
       <c r="L397" s="2" t="n"/>
       <c r="M397" s="2" t="n"/>
       <c r="N397" s="2" t="n"/>
+      <c r="O397" s="2" t="n"/>
+      <c r="P397" s="2" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n"/>
@@ -7068,6 +7892,8 @@
       <c r="L398" s="2" t="n"/>
       <c r="M398" s="2" t="n"/>
       <c r="N398" s="2" t="n"/>
+      <c r="O398" s="2" t="n"/>
+      <c r="P398" s="2" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n"/>
@@ -7084,6 +7910,8 @@
       <c r="L399" s="2" t="n"/>
       <c r="M399" s="2" t="n"/>
       <c r="N399" s="2" t="n"/>
+      <c r="O399" s="2" t="n"/>
+      <c r="P399" s="2" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n"/>
@@ -7100,6 +7928,8 @@
       <c r="L400" s="2" t="n"/>
       <c r="M400" s="2" t="n"/>
       <c r="N400" s="2" t="n"/>
+      <c r="O400" s="2" t="n"/>
+      <c r="P400" s="2" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n"/>
@@ -7116,6 +7946,8 @@
       <c r="L401" s="2" t="n"/>
       <c r="M401" s="2" t="n"/>
       <c r="N401" s="2" t="n"/>
+      <c r="O401" s="2" t="n"/>
+      <c r="P401" s="2" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n"/>
@@ -7132,6 +7964,8 @@
       <c r="L402" s="2" t="n"/>
       <c r="M402" s="2" t="n"/>
       <c r="N402" s="2" t="n"/>
+      <c r="O402" s="2" t="n"/>
+      <c r="P402" s="2" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n"/>
@@ -7148,6 +7982,8 @@
       <c r="L403" s="2" t="n"/>
       <c r="M403" s="2" t="n"/>
       <c r="N403" s="2" t="n"/>
+      <c r="O403" s="2" t="n"/>
+      <c r="P403" s="2" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n"/>
@@ -7164,6 +8000,8 @@
       <c r="L404" s="2" t="n"/>
       <c r="M404" s="2" t="n"/>
       <c r="N404" s="2" t="n"/>
+      <c r="O404" s="2" t="n"/>
+      <c r="P404" s="2" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n"/>
@@ -7180,6 +8018,8 @@
       <c r="L405" s="2" t="n"/>
       <c r="M405" s="2" t="n"/>
       <c r="N405" s="2" t="n"/>
+      <c r="O405" s="2" t="n"/>
+      <c r="P405" s="2" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n"/>
@@ -7196,6 +8036,8 @@
       <c r="L406" s="2" t="n"/>
       <c r="M406" s="2" t="n"/>
       <c r="N406" s="2" t="n"/>
+      <c r="O406" s="2" t="n"/>
+      <c r="P406" s="2" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n"/>
@@ -7212,6 +8054,8 @@
       <c r="L407" s="2" t="n"/>
       <c r="M407" s="2" t="n"/>
       <c r="N407" s="2" t="n"/>
+      <c r="O407" s="2" t="n"/>
+      <c r="P407" s="2" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n"/>
@@ -7228,6 +8072,8 @@
       <c r="L408" s="2" t="n"/>
       <c r="M408" s="2" t="n"/>
       <c r="N408" s="2" t="n"/>
+      <c r="O408" s="2" t="n"/>
+      <c r="P408" s="2" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n"/>
@@ -7244,6 +8090,8 @@
       <c r="L409" s="2" t="n"/>
       <c r="M409" s="2" t="n"/>
       <c r="N409" s="2" t="n"/>
+      <c r="O409" s="2" t="n"/>
+      <c r="P409" s="2" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n"/>
@@ -7260,6 +8108,8 @@
       <c r="L410" s="2" t="n"/>
       <c r="M410" s="2" t="n"/>
       <c r="N410" s="2" t="n"/>
+      <c r="O410" s="2" t="n"/>
+      <c r="P410" s="2" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n"/>
@@ -7276,6 +8126,8 @@
       <c r="L411" s="2" t="n"/>
       <c r="M411" s="2" t="n"/>
       <c r="N411" s="2" t="n"/>
+      <c r="O411" s="2" t="n"/>
+      <c r="P411" s="2" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n"/>
@@ -7292,6 +8144,8 @@
       <c r="L412" s="2" t="n"/>
       <c r="M412" s="2" t="n"/>
       <c r="N412" s="2" t="n"/>
+      <c r="O412" s="2" t="n"/>
+      <c r="P412" s="2" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n"/>
@@ -7308,6 +8162,8 @@
       <c r="L413" s="2" t="n"/>
       <c r="M413" s="2" t="n"/>
       <c r="N413" s="2" t="n"/>
+      <c r="O413" s="2" t="n"/>
+      <c r="P413" s="2" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n"/>
@@ -7324,6 +8180,8 @@
       <c r="L414" s="2" t="n"/>
       <c r="M414" s="2" t="n"/>
       <c r="N414" s="2" t="n"/>
+      <c r="O414" s="2" t="n"/>
+      <c r="P414" s="2" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n"/>
@@ -7340,6 +8198,8 @@
       <c r="L415" s="2" t="n"/>
       <c r="M415" s="2" t="n"/>
       <c r="N415" s="2" t="n"/>
+      <c r="O415" s="2" t="n"/>
+      <c r="P415" s="2" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n"/>
@@ -7356,6 +8216,8 @@
       <c r="L416" s="2" t="n"/>
       <c r="M416" s="2" t="n"/>
       <c r="N416" s="2" t="n"/>
+      <c r="O416" s="2" t="n"/>
+      <c r="P416" s="2" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n"/>
@@ -7372,6 +8234,8 @@
       <c r="L417" s="2" t="n"/>
       <c r="M417" s="2" t="n"/>
       <c r="N417" s="2" t="n"/>
+      <c r="O417" s="2" t="n"/>
+      <c r="P417" s="2" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n"/>
@@ -7388,6 +8252,8 @@
       <c r="L418" s="2" t="n"/>
       <c r="M418" s="2" t="n"/>
       <c r="N418" s="2" t="n"/>
+      <c r="O418" s="2" t="n"/>
+      <c r="P418" s="2" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n"/>
@@ -7404,6 +8270,8 @@
       <c r="L419" s="2" t="n"/>
       <c r="M419" s="2" t="n"/>
       <c r="N419" s="2" t="n"/>
+      <c r="O419" s="2" t="n"/>
+      <c r="P419" s="2" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n"/>
@@ -7420,6 +8288,8 @@
       <c r="L420" s="2" t="n"/>
       <c r="M420" s="2" t="n"/>
       <c r="N420" s="2" t="n"/>
+      <c r="O420" s="2" t="n"/>
+      <c r="P420" s="2" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n"/>
@@ -7436,6 +8306,8 @@
       <c r="L421" s="2" t="n"/>
       <c r="M421" s="2" t="n"/>
       <c r="N421" s="2" t="n"/>
+      <c r="O421" s="2" t="n"/>
+      <c r="P421" s="2" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n"/>
@@ -7452,6 +8324,8 @@
       <c r="L422" s="2" t="n"/>
       <c r="M422" s="2" t="n"/>
       <c r="N422" s="2" t="n"/>
+      <c r="O422" s="2" t="n"/>
+      <c r="P422" s="2" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n"/>
@@ -7468,6 +8342,8 @@
       <c r="L423" s="2" t="n"/>
       <c r="M423" s="2" t="n"/>
       <c r="N423" s="2" t="n"/>
+      <c r="O423" s="2" t="n"/>
+      <c r="P423" s="2" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n"/>
@@ -7484,6 +8360,8 @@
       <c r="L424" s="2" t="n"/>
       <c r="M424" s="2" t="n"/>
       <c r="N424" s="2" t="n"/>
+      <c r="O424" s="2" t="n"/>
+      <c r="P424" s="2" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n"/>
@@ -7500,6 +8378,8 @@
       <c r="L425" s="2" t="n"/>
       <c r="M425" s="2" t="n"/>
       <c r="N425" s="2" t="n"/>
+      <c r="O425" s="2" t="n"/>
+      <c r="P425" s="2" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n"/>
@@ -7516,6 +8396,8 @@
       <c r="L426" s="2" t="n"/>
       <c r="M426" s="2" t="n"/>
       <c r="N426" s="2" t="n"/>
+      <c r="O426" s="2" t="n"/>
+      <c r="P426" s="2" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n"/>
@@ -7532,6 +8414,8 @@
       <c r="L427" s="2" t="n"/>
       <c r="M427" s="2" t="n"/>
       <c r="N427" s="2" t="n"/>
+      <c r="O427" s="2" t="n"/>
+      <c r="P427" s="2" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n"/>
@@ -7548,6 +8432,8 @@
       <c r="L428" s="2" t="n"/>
       <c r="M428" s="2" t="n"/>
       <c r="N428" s="2" t="n"/>
+      <c r="O428" s="2" t="n"/>
+      <c r="P428" s="2" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n"/>
@@ -7564,6 +8450,8 @@
       <c r="L429" s="2" t="n"/>
       <c r="M429" s="2" t="n"/>
       <c r="N429" s="2" t="n"/>
+      <c r="O429" s="2" t="n"/>
+      <c r="P429" s="2" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n"/>
@@ -7580,6 +8468,8 @@
       <c r="L430" s="2" t="n"/>
       <c r="M430" s="2" t="n"/>
       <c r="N430" s="2" t="n"/>
+      <c r="O430" s="2" t="n"/>
+      <c r="P430" s="2" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n"/>
@@ -7596,6 +8486,8 @@
       <c r="L431" s="2" t="n"/>
       <c r="M431" s="2" t="n"/>
       <c r="N431" s="2" t="n"/>
+      <c r="O431" s="2" t="n"/>
+      <c r="P431" s="2" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n"/>
@@ -7612,6 +8504,8 @@
       <c r="L432" s="2" t="n"/>
       <c r="M432" s="2" t="n"/>
       <c r="N432" s="2" t="n"/>
+      <c r="O432" s="2" t="n"/>
+      <c r="P432" s="2" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n"/>
@@ -7628,6 +8522,8 @@
       <c r="L433" s="2" t="n"/>
       <c r="M433" s="2" t="n"/>
       <c r="N433" s="2" t="n"/>
+      <c r="O433" s="2" t="n"/>
+      <c r="P433" s="2" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n"/>
@@ -7644,6 +8540,8 @@
       <c r="L434" s="2" t="n"/>
       <c r="M434" s="2" t="n"/>
       <c r="N434" s="2" t="n"/>
+      <c r="O434" s="2" t="n"/>
+      <c r="P434" s="2" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n"/>
@@ -7660,6 +8558,8 @@
       <c r="L435" s="2" t="n"/>
       <c r="M435" s="2" t="n"/>
       <c r="N435" s="2" t="n"/>
+      <c r="O435" s="2" t="n"/>
+      <c r="P435" s="2" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n"/>
@@ -7676,6 +8576,8 @@
       <c r="L436" s="2" t="n"/>
       <c r="M436" s="2" t="n"/>
       <c r="N436" s="2" t="n"/>
+      <c r="O436" s="2" t="n"/>
+      <c r="P436" s="2" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n"/>
@@ -7692,6 +8594,8 @@
       <c r="L437" s="2" t="n"/>
       <c r="M437" s="2" t="n"/>
       <c r="N437" s="2" t="n"/>
+      <c r="O437" s="2" t="n"/>
+      <c r="P437" s="2" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n"/>
@@ -7708,6 +8612,8 @@
       <c r="L438" s="2" t="n"/>
       <c r="M438" s="2" t="n"/>
       <c r="N438" s="2" t="n"/>
+      <c r="O438" s="2" t="n"/>
+      <c r="P438" s="2" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n"/>
@@ -7724,6 +8630,8 @@
       <c r="L439" s="2" t="n"/>
       <c r="M439" s="2" t="n"/>
       <c r="N439" s="2" t="n"/>
+      <c r="O439" s="2" t="n"/>
+      <c r="P439" s="2" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n"/>
@@ -7740,6 +8648,8 @@
       <c r="L440" s="2" t="n"/>
       <c r="M440" s="2" t="n"/>
       <c r="N440" s="2" t="n"/>
+      <c r="O440" s="2" t="n"/>
+      <c r="P440" s="2" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n"/>
@@ -7756,6 +8666,8 @@
       <c r="L441" s="2" t="n"/>
       <c r="M441" s="2" t="n"/>
       <c r="N441" s="2" t="n"/>
+      <c r="O441" s="2" t="n"/>
+      <c r="P441" s="2" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n"/>
@@ -7772,6 +8684,8 @@
       <c r="L442" s="2" t="n"/>
       <c r="M442" s="2" t="n"/>
       <c r="N442" s="2" t="n"/>
+      <c r="O442" s="2" t="n"/>
+      <c r="P442" s="2" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n"/>
@@ -7788,6 +8702,8 @@
       <c r="L443" s="2" t="n"/>
       <c r="M443" s="2" t="n"/>
       <c r="N443" s="2" t="n"/>
+      <c r="O443" s="2" t="n"/>
+      <c r="P443" s="2" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n"/>
@@ -7804,6 +8720,8 @@
       <c r="L444" s="2" t="n"/>
       <c r="M444" s="2" t="n"/>
       <c r="N444" s="2" t="n"/>
+      <c r="O444" s="2" t="n"/>
+      <c r="P444" s="2" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n"/>
@@ -7820,6 +8738,8 @@
       <c r="L445" s="2" t="n"/>
       <c r="M445" s="2" t="n"/>
       <c r="N445" s="2" t="n"/>
+      <c r="O445" s="2" t="n"/>
+      <c r="P445" s="2" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n"/>
@@ -7836,6 +8756,8 @@
       <c r="L446" s="2" t="n"/>
       <c r="M446" s="2" t="n"/>
       <c r="N446" s="2" t="n"/>
+      <c r="O446" s="2" t="n"/>
+      <c r="P446" s="2" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n"/>
@@ -7852,6 +8774,8 @@
       <c r="L447" s="2" t="n"/>
       <c r="M447" s="2" t="n"/>
       <c r="N447" s="2" t="n"/>
+      <c r="O447" s="2" t="n"/>
+      <c r="P447" s="2" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n"/>
@@ -7868,6 +8792,8 @@
       <c r="L448" s="2" t="n"/>
       <c r="M448" s="2" t="n"/>
       <c r="N448" s="2" t="n"/>
+      <c r="O448" s="2" t="n"/>
+      <c r="P448" s="2" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n"/>
@@ -7884,6 +8810,8 @@
       <c r="L449" s="2" t="n"/>
       <c r="M449" s="2" t="n"/>
       <c r="N449" s="2" t="n"/>
+      <c r="O449" s="2" t="n"/>
+      <c r="P449" s="2" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n"/>
@@ -7900,6 +8828,8 @@
       <c r="L450" s="2" t="n"/>
       <c r="M450" s="2" t="n"/>
       <c r="N450" s="2" t="n"/>
+      <c r="O450" s="2" t="n"/>
+      <c r="P450" s="2" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n"/>
@@ -7916,6 +8846,8 @@
       <c r="L451" s="2" t="n"/>
       <c r="M451" s="2" t="n"/>
       <c r="N451" s="2" t="n"/>
+      <c r="O451" s="2" t="n"/>
+      <c r="P451" s="2" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n"/>
@@ -7932,6 +8864,8 @@
       <c r="L452" s="2" t="n"/>
       <c r="M452" s="2" t="n"/>
       <c r="N452" s="2" t="n"/>
+      <c r="O452" s="2" t="n"/>
+      <c r="P452" s="2" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n"/>
@@ -7948,6 +8882,8 @@
       <c r="L453" s="2" t="n"/>
       <c r="M453" s="2" t="n"/>
       <c r="N453" s="2" t="n"/>
+      <c r="O453" s="2" t="n"/>
+      <c r="P453" s="2" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n"/>
@@ -7964,6 +8900,8 @@
       <c r="L454" s="2" t="n"/>
       <c r="M454" s="2" t="n"/>
       <c r="N454" s="2" t="n"/>
+      <c r="O454" s="2" t="n"/>
+      <c r="P454" s="2" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n"/>
@@ -7980,6 +8918,8 @@
       <c r="L455" s="2" t="n"/>
       <c r="M455" s="2" t="n"/>
       <c r="N455" s="2" t="n"/>
+      <c r="O455" s="2" t="n"/>
+      <c r="P455" s="2" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n"/>
@@ -7996,6 +8936,8 @@
       <c r="L456" s="2" t="n"/>
       <c r="M456" s="2" t="n"/>
       <c r="N456" s="2" t="n"/>
+      <c r="O456" s="2" t="n"/>
+      <c r="P456" s="2" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n"/>
@@ -8012,6 +8954,8 @@
       <c r="L457" s="2" t="n"/>
       <c r="M457" s="2" t="n"/>
       <c r="N457" s="2" t="n"/>
+      <c r="O457" s="2" t="n"/>
+      <c r="P457" s="2" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n"/>
@@ -8028,6 +8972,8 @@
       <c r="L458" s="2" t="n"/>
       <c r="M458" s="2" t="n"/>
       <c r="N458" s="2" t="n"/>
+      <c r="O458" s="2" t="n"/>
+      <c r="P458" s="2" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n"/>
@@ -8044,6 +8990,8 @@
       <c r="L459" s="2" t="n"/>
       <c r="M459" s="2" t="n"/>
       <c r="N459" s="2" t="n"/>
+      <c r="O459" s="2" t="n"/>
+      <c r="P459" s="2" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n"/>
@@ -8060,6 +9008,8 @@
       <c r="L460" s="2" t="n"/>
       <c r="M460" s="2" t="n"/>
       <c r="N460" s="2" t="n"/>
+      <c r="O460" s="2" t="n"/>
+      <c r="P460" s="2" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n"/>
@@ -8076,6 +9026,8 @@
       <c r="L461" s="2" t="n"/>
       <c r="M461" s="2" t="n"/>
       <c r="N461" s="2" t="n"/>
+      <c r="O461" s="2" t="n"/>
+      <c r="P461" s="2" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n"/>
@@ -8092,6 +9044,8 @@
       <c r="L462" s="2" t="n"/>
       <c r="M462" s="2" t="n"/>
       <c r="N462" s="2" t="n"/>
+      <c r="O462" s="2" t="n"/>
+      <c r="P462" s="2" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n"/>
@@ -8108,6 +9062,8 @@
       <c r="L463" s="2" t="n"/>
       <c r="M463" s="2" t="n"/>
       <c r="N463" s="2" t="n"/>
+      <c r="O463" s="2" t="n"/>
+      <c r="P463" s="2" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n"/>
@@ -8124,6 +9080,8 @@
       <c r="L464" s="2" t="n"/>
       <c r="M464" s="2" t="n"/>
       <c r="N464" s="2" t="n"/>
+      <c r="O464" s="2" t="n"/>
+      <c r="P464" s="2" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n"/>
@@ -8140,6 +9098,8 @@
       <c r="L465" s="2" t="n"/>
       <c r="M465" s="2" t="n"/>
       <c r="N465" s="2" t="n"/>
+      <c r="O465" s="2" t="n"/>
+      <c r="P465" s="2" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n"/>
@@ -8156,6 +9116,8 @@
       <c r="L466" s="2" t="n"/>
       <c r="M466" s="2" t="n"/>
       <c r="N466" s="2" t="n"/>
+      <c r="O466" s="2" t="n"/>
+      <c r="P466" s="2" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n"/>
@@ -8172,6 +9134,8 @@
       <c r="L467" s="2" t="n"/>
       <c r="M467" s="2" t="n"/>
       <c r="N467" s="2" t="n"/>
+      <c r="O467" s="2" t="n"/>
+      <c r="P467" s="2" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n"/>
@@ -8188,6 +9152,8 @@
       <c r="L468" s="2" t="n"/>
       <c r="M468" s="2" t="n"/>
       <c r="N468" s="2" t="n"/>
+      <c r="O468" s="2" t="n"/>
+      <c r="P468" s="2" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n"/>
@@ -8204,6 +9170,8 @@
       <c r="L469" s="2" t="n"/>
       <c r="M469" s="2" t="n"/>
       <c r="N469" s="2" t="n"/>
+      <c r="O469" s="2" t="n"/>
+      <c r="P469" s="2" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n"/>
@@ -8220,6 +9188,8 @@
       <c r="L470" s="2" t="n"/>
       <c r="M470" s="2" t="n"/>
       <c r="N470" s="2" t="n"/>
+      <c r="O470" s="2" t="n"/>
+      <c r="P470" s="2" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n"/>
@@ -8236,6 +9206,8 @@
       <c r="L471" s="2" t="n"/>
       <c r="M471" s="2" t="n"/>
       <c r="N471" s="2" t="n"/>
+      <c r="O471" s="2" t="n"/>
+      <c r="P471" s="2" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n"/>
@@ -8252,6 +9224,8 @@
       <c r="L472" s="2" t="n"/>
       <c r="M472" s="2" t="n"/>
       <c r="N472" s="2" t="n"/>
+      <c r="O472" s="2" t="n"/>
+      <c r="P472" s="2" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n"/>
@@ -8268,6 +9242,8 @@
       <c r="L473" s="2" t="n"/>
       <c r="M473" s="2" t="n"/>
       <c r="N473" s="2" t="n"/>
+      <c r="O473" s="2" t="n"/>
+      <c r="P473" s="2" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n"/>
@@ -8284,6 +9260,8 @@
       <c r="L474" s="2" t="n"/>
       <c r="M474" s="2" t="n"/>
       <c r="N474" s="2" t="n"/>
+      <c r="O474" s="2" t="n"/>
+      <c r="P474" s="2" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n"/>
@@ -8300,6 +9278,8 @@
       <c r="L475" s="2" t="n"/>
       <c r="M475" s="2" t="n"/>
       <c r="N475" s="2" t="n"/>
+      <c r="O475" s="2" t="n"/>
+      <c r="P475" s="2" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n"/>
@@ -8316,6 +9296,8 @@
       <c r="L476" s="2" t="n"/>
       <c r="M476" s="2" t="n"/>
       <c r="N476" s="2" t="n"/>
+      <c r="O476" s="2" t="n"/>
+      <c r="P476" s="2" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n"/>
@@ -8332,6 +9314,8 @@
       <c r="L477" s="2" t="n"/>
       <c r="M477" s="2" t="n"/>
       <c r="N477" s="2" t="n"/>
+      <c r="O477" s="2" t="n"/>
+      <c r="P477" s="2" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n"/>
@@ -8348,6 +9332,8 @@
       <c r="L478" s="2" t="n"/>
       <c r="M478" s="2" t="n"/>
       <c r="N478" s="2" t="n"/>
+      <c r="O478" s="2" t="n"/>
+      <c r="P478" s="2" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n"/>
@@ -8364,6 +9350,8 @@
       <c r="L479" s="2" t="n"/>
       <c r="M479" s="2" t="n"/>
       <c r="N479" s="2" t="n"/>
+      <c r="O479" s="2" t="n"/>
+      <c r="P479" s="2" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n"/>
@@ -8380,6 +9368,8 @@
       <c r="L480" s="2" t="n"/>
       <c r="M480" s="2" t="n"/>
       <c r="N480" s="2" t="n"/>
+      <c r="O480" s="2" t="n"/>
+      <c r="P480" s="2" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n"/>
@@ -8396,6 +9386,8 @@
       <c r="L481" s="2" t="n"/>
       <c r="M481" s="2" t="n"/>
       <c r="N481" s="2" t="n"/>
+      <c r="O481" s="2" t="n"/>
+      <c r="P481" s="2" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n"/>
@@ -8412,6 +9404,8 @@
       <c r="L482" s="2" t="n"/>
       <c r="M482" s="2" t="n"/>
       <c r="N482" s="2" t="n"/>
+      <c r="O482" s="2" t="n"/>
+      <c r="P482" s="2" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n"/>
@@ -8428,6 +9422,8 @@
       <c r="L483" s="2" t="n"/>
       <c r="M483" s="2" t="n"/>
       <c r="N483" s="2" t="n"/>
+      <c r="O483" s="2" t="n"/>
+      <c r="P483" s="2" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n"/>
@@ -8444,6 +9440,8 @@
       <c r="L484" s="2" t="n"/>
       <c r="M484" s="2" t="n"/>
       <c r="N484" s="2" t="n"/>
+      <c r="O484" s="2" t="n"/>
+      <c r="P484" s="2" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n"/>
@@ -8460,6 +9458,8 @@
       <c r="L485" s="2" t="n"/>
       <c r="M485" s="2" t="n"/>
       <c r="N485" s="2" t="n"/>
+      <c r="O485" s="2" t="n"/>
+      <c r="P485" s="2" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n"/>
@@ -8476,6 +9476,8 @@
       <c r="L486" s="2" t="n"/>
       <c r="M486" s="2" t="n"/>
       <c r="N486" s="2" t="n"/>
+      <c r="O486" s="2" t="n"/>
+      <c r="P486" s="2" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n"/>
@@ -8492,6 +9494,8 @@
       <c r="L487" s="2" t="n"/>
       <c r="M487" s="2" t="n"/>
       <c r="N487" s="2" t="n"/>
+      <c r="O487" s="2" t="n"/>
+      <c r="P487" s="2" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n"/>
@@ -8508,6 +9512,8 @@
       <c r="L488" s="2" t="n"/>
       <c r="M488" s="2" t="n"/>
       <c r="N488" s="2" t="n"/>
+      <c r="O488" s="2" t="n"/>
+      <c r="P488" s="2" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n"/>
@@ -8524,6 +9530,8 @@
       <c r="L489" s="2" t="n"/>
       <c r="M489" s="2" t="n"/>
       <c r="N489" s="2" t="n"/>
+      <c r="O489" s="2" t="n"/>
+      <c r="P489" s="2" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n"/>
@@ -8540,6 +9548,8 @@
       <c r="L490" s="2" t="n"/>
       <c r="M490" s="2" t="n"/>
       <c r="N490" s="2" t="n"/>
+      <c r="O490" s="2" t="n"/>
+      <c r="P490" s="2" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n"/>
@@ -8556,6 +9566,8 @@
       <c r="L491" s="2" t="n"/>
       <c r="M491" s="2" t="n"/>
       <c r="N491" s="2" t="n"/>
+      <c r="O491" s="2" t="n"/>
+      <c r="P491" s="2" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n"/>
@@ -8572,6 +9584,8 @@
       <c r="L492" s="2" t="n"/>
       <c r="M492" s="2" t="n"/>
       <c r="N492" s="2" t="n"/>
+      <c r="O492" s="2" t="n"/>
+      <c r="P492" s="2" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n"/>
@@ -8588,6 +9602,8 @@
       <c r="L493" s="2" t="n"/>
       <c r="M493" s="2" t="n"/>
       <c r="N493" s="2" t="n"/>
+      <c r="O493" s="2" t="n"/>
+      <c r="P493" s="2" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n"/>
@@ -8604,6 +9620,8 @@
       <c r="L494" s="2" t="n"/>
       <c r="M494" s="2" t="n"/>
       <c r="N494" s="2" t="n"/>
+      <c r="O494" s="2" t="n"/>
+      <c r="P494" s="2" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n"/>
@@ -8620,6 +9638,8 @@
       <c r="L495" s="2" t="n"/>
       <c r="M495" s="2" t="n"/>
       <c r="N495" s="2" t="n"/>
+      <c r="O495" s="2" t="n"/>
+      <c r="P495" s="2" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n"/>
@@ -8636,6 +9656,8 @@
       <c r="L496" s="2" t="n"/>
       <c r="M496" s="2" t="n"/>
       <c r="N496" s="2" t="n"/>
+      <c r="O496" s="2" t="n"/>
+      <c r="P496" s="2" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n"/>
@@ -8652,6 +9674,8 @@
       <c r="L497" s="2" t="n"/>
       <c r="M497" s="2" t="n"/>
       <c r="N497" s="2" t="n"/>
+      <c r="O497" s="2" t="n"/>
+      <c r="P497" s="2" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n"/>
@@ -8668,6 +9692,8 @@
       <c r="L498" s="2" t="n"/>
       <c r="M498" s="2" t="n"/>
       <c r="N498" s="2" t="n"/>
+      <c r="O498" s="2" t="n"/>
+      <c r="P498" s="2" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n"/>
@@ -8684,6 +9710,8 @@
       <c r="L499" s="2" t="n"/>
       <c r="M499" s="2" t="n"/>
       <c r="N499" s="2" t="n"/>
+      <c r="O499" s="2" t="n"/>
+      <c r="P499" s="2" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n"/>
@@ -8700,6 +9728,8 @@
       <c r="L500" s="2" t="n"/>
       <c r="M500" s="2" t="n"/>
       <c r="N500" s="2" t="n"/>
+      <c r="O500" s="2" t="n"/>
+      <c r="P500" s="2" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n"/>
@@ -8716,6 +9746,8 @@
       <c r="L501" s="2" t="n"/>
       <c r="M501" s="2" t="n"/>
       <c r="N501" s="2" t="n"/>
+      <c r="O501" s="2" t="n"/>
+      <c r="P501" s="2" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n"/>
@@ -8732,6 +9764,8 @@
       <c r="L502" s="2" t="n"/>
       <c r="M502" s="2" t="n"/>
       <c r="N502" s="2" t="n"/>
+      <c r="O502" s="2" t="n"/>
+      <c r="P502" s="2" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n"/>
@@ -8748,6 +9782,8 @@
       <c r="L503" s="2" t="n"/>
       <c r="M503" s="2" t="n"/>
       <c r="N503" s="2" t="n"/>
+      <c r="O503" s="2" t="n"/>
+      <c r="P503" s="2" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n"/>
@@ -8764,6 +9800,8 @@
       <c r="L504" s="2" t="n"/>
       <c r="M504" s="2" t="n"/>
       <c r="N504" s="2" t="n"/>
+      <c r="O504" s="2" t="n"/>
+      <c r="P504" s="2" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n"/>
@@ -8780,6 +9818,8 @@
       <c r="L505" s="2" t="n"/>
       <c r="M505" s="2" t="n"/>
       <c r="N505" s="2" t="n"/>
+      <c r="O505" s="2" t="n"/>
+      <c r="P505" s="2" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n"/>
@@ -8796,6 +9836,8 @@
       <c r="L506" s="2" t="n"/>
       <c r="M506" s="2" t="n"/>
       <c r="N506" s="2" t="n"/>
+      <c r="O506" s="2" t="n"/>
+      <c r="P506" s="2" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n"/>
@@ -8812,6 +9854,8 @@
       <c r="L507" s="2" t="n"/>
       <c r="M507" s="2" t="n"/>
       <c r="N507" s="2" t="n"/>
+      <c r="O507" s="2" t="n"/>
+      <c r="P507" s="2" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n"/>
@@ -8828,6 +9872,8 @@
       <c r="L508" s="2" t="n"/>
       <c r="M508" s="2" t="n"/>
       <c r="N508" s="2" t="n"/>
+      <c r="O508" s="2" t="n"/>
+      <c r="P508" s="2" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n"/>
@@ -8844,6 +9890,8 @@
       <c r="L509" s="2" t="n"/>
       <c r="M509" s="2" t="n"/>
       <c r="N509" s="2" t="n"/>
+      <c r="O509" s="2" t="n"/>
+      <c r="P509" s="2" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n"/>
@@ -8860,6 +9908,8 @@
       <c r="L510" s="2" t="n"/>
       <c r="M510" s="2" t="n"/>
       <c r="N510" s="2" t="n"/>
+      <c r="O510" s="2" t="n"/>
+      <c r="P510" s="2" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n"/>
@@ -8876,6 +9926,8 @@
       <c r="L511" s="2" t="n"/>
       <c r="M511" s="2" t="n"/>
       <c r="N511" s="2" t="n"/>
+      <c r="O511" s="2" t="n"/>
+      <c r="P511" s="2" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n"/>
@@ -8892,6 +9944,8 @@
       <c r="L512" s="2" t="n"/>
       <c r="M512" s="2" t="n"/>
       <c r="N512" s="2" t="n"/>
+      <c r="O512" s="2" t="n"/>
+      <c r="P512" s="2" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n"/>
@@ -8908,6 +9962,8 @@
       <c r="L513" s="2" t="n"/>
       <c r="M513" s="2" t="n"/>
       <c r="N513" s="2" t="n"/>
+      <c r="O513" s="2" t="n"/>
+      <c r="P513" s="2" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n"/>
@@ -8924,6 +9980,8 @@
       <c r="L514" s="2" t="n"/>
       <c r="M514" s="2" t="n"/>
       <c r="N514" s="2" t="n"/>
+      <c r="O514" s="2" t="n"/>
+      <c r="P514" s="2" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n"/>
@@ -8940,6 +9998,8 @@
       <c r="L515" s="2" t="n"/>
       <c r="M515" s="2" t="n"/>
       <c r="N515" s="2" t="n"/>
+      <c r="O515" s="2" t="n"/>
+      <c r="P515" s="2" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n"/>
@@ -8956,6 +10016,8 @@
       <c r="L516" s="2" t="n"/>
       <c r="M516" s="2" t="n"/>
       <c r="N516" s="2" t="n"/>
+      <c r="O516" s="2" t="n"/>
+      <c r="P516" s="2" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n"/>
@@ -8972,6 +10034,8 @@
       <c r="L517" s="2" t="n"/>
       <c r="M517" s="2" t="n"/>
       <c r="N517" s="2" t="n"/>
+      <c r="O517" s="2" t="n"/>
+      <c r="P517" s="2" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n"/>
@@ -8988,6 +10052,8 @@
       <c r="L518" s="2" t="n"/>
       <c r="M518" s="2" t="n"/>
       <c r="N518" s="2" t="n"/>
+      <c r="O518" s="2" t="n"/>
+      <c r="P518" s="2" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n"/>
@@ -9004,6 +10070,8 @@
       <c r="L519" s="2" t="n"/>
       <c r="M519" s="2" t="n"/>
       <c r="N519" s="2" t="n"/>
+      <c r="O519" s="2" t="n"/>
+      <c r="P519" s="2" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n"/>
@@ -9020,6 +10088,8 @@
       <c r="L520" s="2" t="n"/>
       <c r="M520" s="2" t="n"/>
       <c r="N520" s="2" t="n"/>
+      <c r="O520" s="2" t="n"/>
+      <c r="P520" s="2" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n"/>
@@ -9036,6 +10106,8 @@
       <c r="L521" s="2" t="n"/>
       <c r="M521" s="2" t="n"/>
       <c r="N521" s="2" t="n"/>
+      <c r="O521" s="2" t="n"/>
+      <c r="P521" s="2" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n"/>
@@ -9052,6 +10124,8 @@
       <c r="L522" s="2" t="n"/>
       <c r="M522" s="2" t="n"/>
       <c r="N522" s="2" t="n"/>
+      <c r="O522" s="2" t="n"/>
+      <c r="P522" s="2" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n"/>
@@ -9068,6 +10142,8 @@
       <c r="L523" s="2" t="n"/>
       <c r="M523" s="2" t="n"/>
       <c r="N523" s="2" t="n"/>
+      <c r="O523" s="2" t="n"/>
+      <c r="P523" s="2" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n"/>
@@ -9084,6 +10160,8 @@
       <c r="L524" s="2" t="n"/>
       <c r="M524" s="2" t="n"/>
       <c r="N524" s="2" t="n"/>
+      <c r="O524" s="2" t="n"/>
+      <c r="P524" s="2" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n"/>
@@ -9100,6 +10178,8 @@
       <c r="L525" s="2" t="n"/>
       <c r="M525" s="2" t="n"/>
       <c r="N525" s="2" t="n"/>
+      <c r="O525" s="2" t="n"/>
+      <c r="P525" s="2" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n"/>
@@ -9116,6 +10196,8 @@
       <c r="L526" s="2" t="n"/>
       <c r="M526" s="2" t="n"/>
       <c r="N526" s="2" t="n"/>
+      <c r="O526" s="2" t="n"/>
+      <c r="P526" s="2" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n"/>
@@ -9132,6 +10214,8 @@
       <c r="L527" s="2" t="n"/>
       <c r="M527" s="2" t="n"/>
       <c r="N527" s="2" t="n"/>
+      <c r="O527" s="2" t="n"/>
+      <c r="P527" s="2" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n"/>
@@ -9148,6 +10232,8 @@
       <c r="L528" s="2" t="n"/>
       <c r="M528" s="2" t="n"/>
       <c r="N528" s="2" t="n"/>
+      <c r="O528" s="2" t="n"/>
+      <c r="P528" s="2" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n"/>
@@ -9164,6 +10250,8 @@
       <c r="L529" s="2" t="n"/>
       <c r="M529" s="2" t="n"/>
       <c r="N529" s="2" t="n"/>
+      <c r="O529" s="2" t="n"/>
+      <c r="P529" s="2" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n"/>
@@ -9180,6 +10268,8 @@
       <c r="L530" s="2" t="n"/>
       <c r="M530" s="2" t="n"/>
       <c r="N530" s="2" t="n"/>
+      <c r="O530" s="2" t="n"/>
+      <c r="P530" s="2" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n"/>
@@ -9196,6 +10286,8 @@
       <c r="L531" s="2" t="n"/>
       <c r="M531" s="2" t="n"/>
       <c r="N531" s="2" t="n"/>
+      <c r="O531" s="2" t="n"/>
+      <c r="P531" s="2" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n"/>
@@ -9212,6 +10304,8 @@
       <c r="L532" s="2" t="n"/>
       <c r="M532" s="2" t="n"/>
       <c r="N532" s="2" t="n"/>
+      <c r="O532" s="2" t="n"/>
+      <c r="P532" s="2" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n"/>
@@ -9228,6 +10322,8 @@
       <c r="L533" s="2" t="n"/>
       <c r="M533" s="2" t="n"/>
       <c r="N533" s="2" t="n"/>
+      <c r="O533" s="2" t="n"/>
+      <c r="P533" s="2" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n"/>
@@ -9244,6 +10340,8 @@
       <c r="L534" s="2" t="n"/>
       <c r="M534" s="2" t="n"/>
       <c r="N534" s="2" t="n"/>
+      <c r="O534" s="2" t="n"/>
+      <c r="P534" s="2" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n"/>
@@ -9260,6 +10358,8 @@
       <c r="L535" s="2" t="n"/>
       <c r="M535" s="2" t="n"/>
       <c r="N535" s="2" t="n"/>
+      <c r="O535" s="2" t="n"/>
+      <c r="P535" s="2" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n"/>
@@ -9276,6 +10376,8 @@
       <c r="L536" s="2" t="n"/>
       <c r="M536" s="2" t="n"/>
       <c r="N536" s="2" t="n"/>
+      <c r="O536" s="2" t="n"/>
+      <c r="P536" s="2" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n"/>
@@ -9292,6 +10394,8 @@
       <c r="L537" s="2" t="n"/>
       <c r="M537" s="2" t="n"/>
       <c r="N537" s="2" t="n"/>
+      <c r="O537" s="2" t="n"/>
+      <c r="P537" s="2" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n"/>
@@ -9308,6 +10412,8 @@
       <c r="L538" s="2" t="n"/>
       <c r="M538" s="2" t="n"/>
       <c r="N538" s="2" t="n"/>
+      <c r="O538" s="2" t="n"/>
+      <c r="P538" s="2" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n"/>
@@ -9324,6 +10430,8 @@
       <c r="L539" s="2" t="n"/>
       <c r="M539" s="2" t="n"/>
       <c r="N539" s="2" t="n"/>
+      <c r="O539" s="2" t="n"/>
+      <c r="P539" s="2" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n"/>
@@ -9340,6 +10448,8 @@
       <c r="L540" s="2" t="n"/>
       <c r="M540" s="2" t="n"/>
       <c r="N540" s="2" t="n"/>
+      <c r="O540" s="2" t="n"/>
+      <c r="P540" s="2" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n"/>
@@ -9356,6 +10466,8 @@
       <c r="L541" s="2" t="n"/>
       <c r="M541" s="2" t="n"/>
       <c r="N541" s="2" t="n"/>
+      <c r="O541" s="2" t="n"/>
+      <c r="P541" s="2" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n"/>
@@ -9372,6 +10484,8 @@
       <c r="L542" s="2" t="n"/>
       <c r="M542" s="2" t="n"/>
       <c r="N542" s="2" t="n"/>
+      <c r="O542" s="2" t="n"/>
+      <c r="P542" s="2" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="n"/>
@@ -9388,6 +10502,8 @@
       <c r="L543" s="2" t="n"/>
       <c r="M543" s="2" t="n"/>
       <c r="N543" s="2" t="n"/>
+      <c r="O543" s="2" t="n"/>
+      <c r="P543" s="2" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n"/>
@@ -9404,6 +10520,8 @@
       <c r="L544" s="2" t="n"/>
       <c r="M544" s="2" t="n"/>
       <c r="N544" s="2" t="n"/>
+      <c r="O544" s="2" t="n"/>
+      <c r="P544" s="2" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n"/>
@@ -9420,6 +10538,8 @@
       <c r="L545" s="2" t="n"/>
       <c r="M545" s="2" t="n"/>
       <c r="N545" s="2" t="n"/>
+      <c r="O545" s="2" t="n"/>
+      <c r="P545" s="2" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n"/>
@@ -9436,6 +10556,8 @@
       <c r="L546" s="2" t="n"/>
       <c r="M546" s="2" t="n"/>
       <c r="N546" s="2" t="n"/>
+      <c r="O546" s="2" t="n"/>
+      <c r="P546" s="2" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n"/>
@@ -9452,6 +10574,8 @@
       <c r="L547" s="2" t="n"/>
       <c r="M547" s="2" t="n"/>
       <c r="N547" s="2" t="n"/>
+      <c r="O547" s="2" t="n"/>
+      <c r="P547" s="2" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n"/>
@@ -9468,6 +10592,8 @@
       <c r="L548" s="2" t="n"/>
       <c r="M548" s="2" t="n"/>
       <c r="N548" s="2" t="n"/>
+      <c r="O548" s="2" t="n"/>
+      <c r="P548" s="2" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n"/>
@@ -9484,6 +10610,8 @@
       <c r="L549" s="2" t="n"/>
       <c r="M549" s="2" t="n"/>
       <c r="N549" s="2" t="n"/>
+      <c r="O549" s="2" t="n"/>
+      <c r="P549" s="2" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n"/>
@@ -9500,6 +10628,8 @@
       <c r="L550" s="2" t="n"/>
       <c r="M550" s="2" t="n"/>
       <c r="N550" s="2" t="n"/>
+      <c r="O550" s="2" t="n"/>
+      <c r="P550" s="2" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n"/>
@@ -9516,6 +10646,8 @@
       <c r="L551" s="2" t="n"/>
       <c r="M551" s="2" t="n"/>
       <c r="N551" s="2" t="n"/>
+      <c r="O551" s="2" t="n"/>
+      <c r="P551" s="2" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n"/>
@@ -9532,6 +10664,8 @@
       <c r="L552" s="2" t="n"/>
       <c r="M552" s="2" t="n"/>
       <c r="N552" s="2" t="n"/>
+      <c r="O552" s="2" t="n"/>
+      <c r="P552" s="2" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n"/>
@@ -9548,6 +10682,8 @@
       <c r="L553" s="2" t="n"/>
       <c r="M553" s="2" t="n"/>
       <c r="N553" s="2" t="n"/>
+      <c r="O553" s="2" t="n"/>
+      <c r="P553" s="2" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n"/>
@@ -9564,6 +10700,8 @@
       <c r="L554" s="2" t="n"/>
       <c r="M554" s="2" t="n"/>
       <c r="N554" s="2" t="n"/>
+      <c r="O554" s="2" t="n"/>
+      <c r="P554" s="2" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n"/>
@@ -9580,6 +10718,8 @@
       <c r="L555" s="2" t="n"/>
       <c r="M555" s="2" t="n"/>
       <c r="N555" s="2" t="n"/>
+      <c r="O555" s="2" t="n"/>
+      <c r="P555" s="2" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n"/>
@@ -9596,6 +10736,8 @@
       <c r="L556" s="2" t="n"/>
       <c r="M556" s="2" t="n"/>
       <c r="N556" s="2" t="n"/>
+      <c r="O556" s="2" t="n"/>
+      <c r="P556" s="2" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n"/>
@@ -9612,6 +10754,8 @@
       <c r="L557" s="2" t="n"/>
       <c r="M557" s="2" t="n"/>
       <c r="N557" s="2" t="n"/>
+      <c r="O557" s="2" t="n"/>
+      <c r="P557" s="2" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n"/>
@@ -9628,6 +10772,8 @@
       <c r="L558" s="2" t="n"/>
       <c r="M558" s="2" t="n"/>
       <c r="N558" s="2" t="n"/>
+      <c r="O558" s="2" t="n"/>
+      <c r="P558" s="2" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n"/>
@@ -9644,6 +10790,8 @@
       <c r="L559" s="2" t="n"/>
       <c r="M559" s="2" t="n"/>
       <c r="N559" s="2" t="n"/>
+      <c r="O559" s="2" t="n"/>
+      <c r="P559" s="2" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n"/>
@@ -9660,6 +10808,8 @@
       <c r="L560" s="2" t="n"/>
       <c r="M560" s="2" t="n"/>
       <c r="N560" s="2" t="n"/>
+      <c r="O560" s="2" t="n"/>
+      <c r="P560" s="2" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n"/>
@@ -9676,6 +10826,8 @@
       <c r="L561" s="2" t="n"/>
       <c r="M561" s="2" t="n"/>
       <c r="N561" s="2" t="n"/>
+      <c r="O561" s="2" t="n"/>
+      <c r="P561" s="2" t="n"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n"/>
@@ -9692,6 +10844,8 @@
       <c r="L562" s="2" t="n"/>
       <c r="M562" s="2" t="n"/>
       <c r="N562" s="2" t="n"/>
+      <c r="O562" s="2" t="n"/>
+      <c r="P562" s="2" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n"/>
@@ -9708,6 +10862,8 @@
       <c r="L563" s="2" t="n"/>
       <c r="M563" s="2" t="n"/>
       <c r="N563" s="2" t="n"/>
+      <c r="O563" s="2" t="n"/>
+      <c r="P563" s="2" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n"/>
@@ -9724,6 +10880,8 @@
       <c r="L564" s="2" t="n"/>
       <c r="M564" s="2" t="n"/>
       <c r="N564" s="2" t="n"/>
+      <c r="O564" s="2" t="n"/>
+      <c r="P564" s="2" t="n"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n"/>
@@ -9740,6 +10898,8 @@
       <c r="L565" s="2" t="n"/>
       <c r="M565" s="2" t="n"/>
       <c r="N565" s="2" t="n"/>
+      <c r="O565" s="2" t="n"/>
+      <c r="P565" s="2" t="n"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n"/>
@@ -9756,6 +10916,8 @@
       <c r="L566" s="2" t="n"/>
       <c r="M566" s="2" t="n"/>
       <c r="N566" s="2" t="n"/>
+      <c r="O566" s="2" t="n"/>
+      <c r="P566" s="2" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n"/>
@@ -9772,6 +10934,8 @@
       <c r="L567" s="2" t="n"/>
       <c r="M567" s="2" t="n"/>
       <c r="N567" s="2" t="n"/>
+      <c r="O567" s="2" t="n"/>
+      <c r="P567" s="2" t="n"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n"/>
@@ -9788,6 +10952,8 @@
       <c r="L568" s="2" t="n"/>
       <c r="M568" s="2" t="n"/>
       <c r="N568" s="2" t="n"/>
+      <c r="O568" s="2" t="n"/>
+      <c r="P568" s="2" t="n"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n"/>
@@ -9804,6 +10970,8 @@
       <c r="L569" s="2" t="n"/>
       <c r="M569" s="2" t="n"/>
       <c r="N569" s="2" t="n"/>
+      <c r="O569" s="2" t="n"/>
+      <c r="P569" s="2" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n"/>
@@ -9820,6 +10988,8 @@
       <c r="L570" s="2" t="n"/>
       <c r="M570" s="2" t="n"/>
       <c r="N570" s="2" t="n"/>
+      <c r="O570" s="2" t="n"/>
+      <c r="P570" s="2" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n"/>
@@ -9836,6 +11006,8 @@
       <c r="L571" s="2" t="n"/>
       <c r="M571" s="2" t="n"/>
       <c r="N571" s="2" t="n"/>
+      <c r="O571" s="2" t="n"/>
+      <c r="P571" s="2" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n"/>
@@ -9852,6 +11024,8 @@
       <c r="L572" s="2" t="n"/>
       <c r="M572" s="2" t="n"/>
       <c r="N572" s="2" t="n"/>
+      <c r="O572" s="2" t="n"/>
+      <c r="P572" s="2" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n"/>
@@ -9868,6 +11042,8 @@
       <c r="L573" s="2" t="n"/>
       <c r="M573" s="2" t="n"/>
       <c r="N573" s="2" t="n"/>
+      <c r="O573" s="2" t="n"/>
+      <c r="P573" s="2" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n"/>
@@ -9884,6 +11060,8 @@
       <c r="L574" s="2" t="n"/>
       <c r="M574" s="2" t="n"/>
       <c r="N574" s="2" t="n"/>
+      <c r="O574" s="2" t="n"/>
+      <c r="P574" s="2" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n"/>
@@ -9900,6 +11078,8 @@
       <c r="L575" s="2" t="n"/>
       <c r="M575" s="2" t="n"/>
       <c r="N575" s="2" t="n"/>
+      <c r="O575" s="2" t="n"/>
+      <c r="P575" s="2" t="n"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n"/>
@@ -9916,6 +11096,8 @@
       <c r="L576" s="2" t="n"/>
       <c r="M576" s="2" t="n"/>
       <c r="N576" s="2" t="n"/>
+      <c r="O576" s="2" t="n"/>
+      <c r="P576" s="2" t="n"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n"/>
@@ -9932,6 +11114,8 @@
       <c r="L577" s="2" t="n"/>
       <c r="M577" s="2" t="n"/>
       <c r="N577" s="2" t="n"/>
+      <c r="O577" s="2" t="n"/>
+      <c r="P577" s="2" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n"/>
@@ -9948,6 +11132,8 @@
       <c r="L578" s="2" t="n"/>
       <c r="M578" s="2" t="n"/>
       <c r="N578" s="2" t="n"/>
+      <c r="O578" s="2" t="n"/>
+      <c r="P578" s="2" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n"/>
@@ -9964,6 +11150,8 @@
       <c r="L579" s="2" t="n"/>
       <c r="M579" s="2" t="n"/>
       <c r="N579" s="2" t="n"/>
+      <c r="O579" s="2" t="n"/>
+      <c r="P579" s="2" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n"/>
@@ -9980,6 +11168,8 @@
       <c r="L580" s="2" t="n"/>
       <c r="M580" s="2" t="n"/>
       <c r="N580" s="2" t="n"/>
+      <c r="O580" s="2" t="n"/>
+      <c r="P580" s="2" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n"/>
@@ -9996,6 +11186,8 @@
       <c r="L581" s="2" t="n"/>
       <c r="M581" s="2" t="n"/>
       <c r="N581" s="2" t="n"/>
+      <c r="O581" s="2" t="n"/>
+      <c r="P581" s="2" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n"/>
@@ -10012,6 +11204,8 @@
       <c r="L582" s="2" t="n"/>
       <c r="M582" s="2" t="n"/>
       <c r="N582" s="2" t="n"/>
+      <c r="O582" s="2" t="n"/>
+      <c r="P582" s="2" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n"/>
@@ -10028,6 +11222,8 @@
       <c r="L583" s="2" t="n"/>
       <c r="M583" s="2" t="n"/>
       <c r="N583" s="2" t="n"/>
+      <c r="O583" s="2" t="n"/>
+      <c r="P583" s="2" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n"/>
@@ -10044,6 +11240,8 @@
       <c r="L584" s="2" t="n"/>
       <c r="M584" s="2" t="n"/>
       <c r="N584" s="2" t="n"/>
+      <c r="O584" s="2" t="n"/>
+      <c r="P584" s="2" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="n"/>
@@ -10060,6 +11258,8 @@
       <c r="L585" s="2" t="n"/>
       <c r="M585" s="2" t="n"/>
       <c r="N585" s="2" t="n"/>
+      <c r="O585" s="2" t="n"/>
+      <c r="P585" s="2" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n"/>
@@ -10076,6 +11276,8 @@
       <c r="L586" s="2" t="n"/>
       <c r="M586" s="2" t="n"/>
       <c r="N586" s="2" t="n"/>
+      <c r="O586" s="2" t="n"/>
+      <c r="P586" s="2" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="n"/>
@@ -10092,6 +11294,8 @@
       <c r="L587" s="2" t="n"/>
       <c r="M587" s="2" t="n"/>
       <c r="N587" s="2" t="n"/>
+      <c r="O587" s="2" t="n"/>
+      <c r="P587" s="2" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n"/>
@@ -10108,6 +11312,8 @@
       <c r="L588" s="2" t="n"/>
       <c r="M588" s="2" t="n"/>
       <c r="N588" s="2" t="n"/>
+      <c r="O588" s="2" t="n"/>
+      <c r="P588" s="2" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="n"/>
@@ -10124,6 +11330,8 @@
       <c r="L589" s="2" t="n"/>
       <c r="M589" s="2" t="n"/>
       <c r="N589" s="2" t="n"/>
+      <c r="O589" s="2" t="n"/>
+      <c r="P589" s="2" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n"/>
@@ -10140,6 +11348,8 @@
       <c r="L590" s="2" t="n"/>
       <c r="M590" s="2" t="n"/>
       <c r="N590" s="2" t="n"/>
+      <c r="O590" s="2" t="n"/>
+      <c r="P590" s="2" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n"/>
@@ -10156,6 +11366,8 @@
       <c r="L591" s="2" t="n"/>
       <c r="M591" s="2" t="n"/>
       <c r="N591" s="2" t="n"/>
+      <c r="O591" s="2" t="n"/>
+      <c r="P591" s="2" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n"/>
@@ -10172,6 +11384,8 @@
       <c r="L592" s="2" t="n"/>
       <c r="M592" s="2" t="n"/>
       <c r="N592" s="2" t="n"/>
+      <c r="O592" s="2" t="n"/>
+      <c r="P592" s="2" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="n"/>
@@ -10188,6 +11402,8 @@
       <c r="L593" s="2" t="n"/>
       <c r="M593" s="2" t="n"/>
       <c r="N593" s="2" t="n"/>
+      <c r="O593" s="2" t="n"/>
+      <c r="P593" s="2" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n"/>
@@ -10204,6 +11420,8 @@
       <c r="L594" s="2" t="n"/>
       <c r="M594" s="2" t="n"/>
       <c r="N594" s="2" t="n"/>
+      <c r="O594" s="2" t="n"/>
+      <c r="P594" s="2" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="n"/>
@@ -10220,6 +11438,8 @@
       <c r="L595" s="2" t="n"/>
       <c r="M595" s="2" t="n"/>
       <c r="N595" s="2" t="n"/>
+      <c r="O595" s="2" t="n"/>
+      <c r="P595" s="2" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n"/>
@@ -10236,6 +11456,8 @@
       <c r="L596" s="2" t="n"/>
       <c r="M596" s="2" t="n"/>
       <c r="N596" s="2" t="n"/>
+      <c r="O596" s="2" t="n"/>
+      <c r="P596" s="2" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n"/>
@@ -10252,6 +11474,8 @@
       <c r="L597" s="2" t="n"/>
       <c r="M597" s="2" t="n"/>
       <c r="N597" s="2" t="n"/>
+      <c r="O597" s="2" t="n"/>
+      <c r="P597" s="2" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n"/>
@@ -10268,6 +11492,8 @@
       <c r="L598" s="2" t="n"/>
       <c r="M598" s="2" t="n"/>
       <c r="N598" s="2" t="n"/>
+      <c r="O598" s="2" t="n"/>
+      <c r="P598" s="2" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n"/>
@@ -10284,6 +11510,8 @@
       <c r="L599" s="2" t="n"/>
       <c r="M599" s="2" t="n"/>
       <c r="N599" s="2" t="n"/>
+      <c r="O599" s="2" t="n"/>
+      <c r="P599" s="2" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n"/>
@@ -10300,6 +11528,8 @@
       <c r="L600" s="2" t="n"/>
       <c r="M600" s="2" t="n"/>
       <c r="N600" s="2" t="n"/>
+      <c r="O600" s="2" t="n"/>
+      <c r="P600" s="2" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n"/>
@@ -10316,6 +11546,8 @@
       <c r="L601" s="2" t="n"/>
       <c r="M601" s="2" t="n"/>
       <c r="N601" s="2" t="n"/>
+      <c r="O601" s="2" t="n"/>
+      <c r="P601" s="2" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n"/>
@@ -10332,6 +11564,8 @@
       <c r="L602" s="2" t="n"/>
       <c r="M602" s="2" t="n"/>
       <c r="N602" s="2" t="n"/>
+      <c r="O602" s="2" t="n"/>
+      <c r="P602" s="2" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="n"/>
@@ -10348,6 +11582,8 @@
       <c r="L603" s="2" t="n"/>
       <c r="M603" s="2" t="n"/>
       <c r="N603" s="2" t="n"/>
+      <c r="O603" s="2" t="n"/>
+      <c r="P603" s="2" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n"/>
@@ -10364,6 +11600,8 @@
       <c r="L604" s="2" t="n"/>
       <c r="M604" s="2" t="n"/>
       <c r="N604" s="2" t="n"/>
+      <c r="O604" s="2" t="n"/>
+      <c r="P604" s="2" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n"/>
@@ -10380,6 +11618,8 @@
       <c r="L605" s="2" t="n"/>
       <c r="M605" s="2" t="n"/>
       <c r="N605" s="2" t="n"/>
+      <c r="O605" s="2" t="n"/>
+      <c r="P605" s="2" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n"/>
@@ -10396,6 +11636,8 @@
       <c r="L606" s="2" t="n"/>
       <c r="M606" s="2" t="n"/>
       <c r="N606" s="2" t="n"/>
+      <c r="O606" s="2" t="n"/>
+      <c r="P606" s="2" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="n"/>
@@ -10412,6 +11654,8 @@
       <c r="L607" s="2" t="n"/>
       <c r="M607" s="2" t="n"/>
       <c r="N607" s="2" t="n"/>
+      <c r="O607" s="2" t="n"/>
+      <c r="P607" s="2" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n"/>
@@ -10428,6 +11672,8 @@
       <c r="L608" s="2" t="n"/>
       <c r="M608" s="2" t="n"/>
       <c r="N608" s="2" t="n"/>
+      <c r="O608" s="2" t="n"/>
+      <c r="P608" s="2" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="n"/>
@@ -10444,6 +11690,8 @@
       <c r="L609" s="2" t="n"/>
       <c r="M609" s="2" t="n"/>
       <c r="N609" s="2" t="n"/>
+      <c r="O609" s="2" t="n"/>
+      <c r="P609" s="2" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n"/>
@@ -10460,6 +11708,8 @@
       <c r="L610" s="2" t="n"/>
       <c r="M610" s="2" t="n"/>
       <c r="N610" s="2" t="n"/>
+      <c r="O610" s="2" t="n"/>
+      <c r="P610" s="2" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="n"/>
@@ -10476,6 +11726,8 @@
       <c r="L611" s="2" t="n"/>
       <c r="M611" s="2" t="n"/>
       <c r="N611" s="2" t="n"/>
+      <c r="O611" s="2" t="n"/>
+      <c r="P611" s="2" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n"/>
@@ -10492,6 +11744,8 @@
       <c r="L612" s="2" t="n"/>
       <c r="M612" s="2" t="n"/>
       <c r="N612" s="2" t="n"/>
+      <c r="O612" s="2" t="n"/>
+      <c r="P612" s="2" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="n"/>
@@ -10508,6 +11762,8 @@
       <c r="L613" s="2" t="n"/>
       <c r="M613" s="2" t="n"/>
       <c r="N613" s="2" t="n"/>
+      <c r="O613" s="2" t="n"/>
+      <c r="P613" s="2" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n"/>
@@ -10524,6 +11780,8 @@
       <c r="L614" s="2" t="n"/>
       <c r="M614" s="2" t="n"/>
       <c r="N614" s="2" t="n"/>
+      <c r="O614" s="2" t="n"/>
+      <c r="P614" s="2" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="n"/>
@@ -10540,6 +11798,8 @@
       <c r="L615" s="2" t="n"/>
       <c r="M615" s="2" t="n"/>
       <c r="N615" s="2" t="n"/>
+      <c r="O615" s="2" t="n"/>
+      <c r="P615" s="2" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n"/>
@@ -10556,6 +11816,8 @@
       <c r="L616" s="2" t="n"/>
       <c r="M616" s="2" t="n"/>
       <c r="N616" s="2" t="n"/>
+      <c r="O616" s="2" t="n"/>
+      <c r="P616" s="2" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="n"/>
@@ -10572,6 +11834,8 @@
       <c r="L617" s="2" t="n"/>
       <c r="M617" s="2" t="n"/>
       <c r="N617" s="2" t="n"/>
+      <c r="O617" s="2" t="n"/>
+      <c r="P617" s="2" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="n"/>
@@ -10588,6 +11852,8 @@
       <c r="L618" s="2" t="n"/>
       <c r="M618" s="2" t="n"/>
       <c r="N618" s="2" t="n"/>
+      <c r="O618" s="2" t="n"/>
+      <c r="P618" s="2" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="n"/>
@@ -10604,6 +11870,8 @@
       <c r="L619" s="2" t="n"/>
       <c r="M619" s="2" t="n"/>
       <c r="N619" s="2" t="n"/>
+      <c r="O619" s="2" t="n"/>
+      <c r="P619" s="2" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="n"/>
@@ -10620,6 +11888,8 @@
       <c r="L620" s="2" t="n"/>
       <c r="M620" s="2" t="n"/>
       <c r="N620" s="2" t="n"/>
+      <c r="O620" s="2" t="n"/>
+      <c r="P620" s="2" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="n"/>
@@ -10636,6 +11906,8 @@
       <c r="L621" s="2" t="n"/>
       <c r="M621" s="2" t="n"/>
       <c r="N621" s="2" t="n"/>
+      <c r="O621" s="2" t="n"/>
+      <c r="P621" s="2" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="n"/>
@@ -10652,6 +11924,8 @@
       <c r="L622" s="2" t="n"/>
       <c r="M622" s="2" t="n"/>
       <c r="N622" s="2" t="n"/>
+      <c r="O622" s="2" t="n"/>
+      <c r="P622" s="2" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="n"/>
@@ -10668,6 +11942,8 @@
       <c r="L623" s="2" t="n"/>
       <c r="M623" s="2" t="n"/>
       <c r="N623" s="2" t="n"/>
+      <c r="O623" s="2" t="n"/>
+      <c r="P623" s="2" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n"/>
@@ -10684,6 +11960,8 @@
       <c r="L624" s="2" t="n"/>
       <c r="M624" s="2" t="n"/>
       <c r="N624" s="2" t="n"/>
+      <c r="O624" s="2" t="n"/>
+      <c r="P624" s="2" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="n"/>
@@ -10700,6 +11978,8 @@
       <c r="L625" s="2" t="n"/>
       <c r="M625" s="2" t="n"/>
       <c r="N625" s="2" t="n"/>
+      <c r="O625" s="2" t="n"/>
+      <c r="P625" s="2" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="n"/>
@@ -10716,6 +11996,8 @@
       <c r="L626" s="2" t="n"/>
       <c r="M626" s="2" t="n"/>
       <c r="N626" s="2" t="n"/>
+      <c r="O626" s="2" t="n"/>
+      <c r="P626" s="2" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="n"/>
@@ -10732,6 +12014,8 @@
       <c r="L627" s="2" t="n"/>
       <c r="M627" s="2" t="n"/>
       <c r="N627" s="2" t="n"/>
+      <c r="O627" s="2" t="n"/>
+      <c r="P627" s="2" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n"/>
@@ -10748,6 +12032,8 @@
       <c r="L628" s="2" t="n"/>
       <c r="M628" s="2" t="n"/>
       <c r="N628" s="2" t="n"/>
+      <c r="O628" s="2" t="n"/>
+      <c r="P628" s="2" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="n"/>
@@ -10764,6 +12050,8 @@
       <c r="L629" s="2" t="n"/>
       <c r="M629" s="2" t="n"/>
       <c r="N629" s="2" t="n"/>
+      <c r="O629" s="2" t="n"/>
+      <c r="P629" s="2" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="n"/>
@@ -10780,6 +12068,8 @@
       <c r="L630" s="2" t="n"/>
       <c r="M630" s="2" t="n"/>
       <c r="N630" s="2" t="n"/>
+      <c r="O630" s="2" t="n"/>
+      <c r="P630" s="2" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="n"/>
@@ -10796,6 +12086,8 @@
       <c r="L631" s="2" t="n"/>
       <c r="M631" s="2" t="n"/>
       <c r="N631" s="2" t="n"/>
+      <c r="O631" s="2" t="n"/>
+      <c r="P631" s="2" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="n"/>
@@ -10812,6 +12104,8 @@
       <c r="L632" s="2" t="n"/>
       <c r="M632" s="2" t="n"/>
       <c r="N632" s="2" t="n"/>
+      <c r="O632" s="2" t="n"/>
+      <c r="P632" s="2" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="n"/>
@@ -10828,6 +12122,8 @@
       <c r="L633" s="2" t="n"/>
       <c r="M633" s="2" t="n"/>
       <c r="N633" s="2" t="n"/>
+      <c r="O633" s="2" t="n"/>
+      <c r="P633" s="2" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n"/>
@@ -10844,6 +12140,8 @@
       <c r="L634" s="2" t="n"/>
       <c r="M634" s="2" t="n"/>
       <c r="N634" s="2" t="n"/>
+      <c r="O634" s="2" t="n"/>
+      <c r="P634" s="2" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="n"/>
@@ -10860,6 +12158,8 @@
       <c r="L635" s="2" t="n"/>
       <c r="M635" s="2" t="n"/>
       <c r="N635" s="2" t="n"/>
+      <c r="O635" s="2" t="n"/>
+      <c r="P635" s="2" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="n"/>
@@ -10876,6 +12176,8 @@
       <c r="L636" s="2" t="n"/>
       <c r="M636" s="2" t="n"/>
       <c r="N636" s="2" t="n"/>
+      <c r="O636" s="2" t="n"/>
+      <c r="P636" s="2" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="n"/>
@@ -10892,6 +12194,8 @@
       <c r="L637" s="2" t="n"/>
       <c r="M637" s="2" t="n"/>
       <c r="N637" s="2" t="n"/>
+      <c r="O637" s="2" t="n"/>
+      <c r="P637" s="2" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n"/>
@@ -10908,6 +12212,8 @@
       <c r="L638" s="2" t="n"/>
       <c r="M638" s="2" t="n"/>
       <c r="N638" s="2" t="n"/>
+      <c r="O638" s="2" t="n"/>
+      <c r="P638" s="2" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="n"/>
@@ -10924,6 +12230,8 @@
       <c r="L639" s="2" t="n"/>
       <c r="M639" s="2" t="n"/>
       <c r="N639" s="2" t="n"/>
+      <c r="O639" s="2" t="n"/>
+      <c r="P639" s="2" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="n"/>
@@ -10940,6 +12248,8 @@
       <c r="L640" s="2" t="n"/>
       <c r="M640" s="2" t="n"/>
       <c r="N640" s="2" t="n"/>
+      <c r="O640" s="2" t="n"/>
+      <c r="P640" s="2" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="n"/>
@@ -10956,6 +12266,8 @@
       <c r="L641" s="2" t="n"/>
       <c r="M641" s="2" t="n"/>
       <c r="N641" s="2" t="n"/>
+      <c r="O641" s="2" t="n"/>
+      <c r="P641" s="2" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="n"/>
@@ -10972,6 +12284,8 @@
       <c r="L642" s="2" t="n"/>
       <c r="M642" s="2" t="n"/>
       <c r="N642" s="2" t="n"/>
+      <c r="O642" s="2" t="n"/>
+      <c r="P642" s="2" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="n"/>
@@ -10988,6 +12302,8 @@
       <c r="L643" s="2" t="n"/>
       <c r="M643" s="2" t="n"/>
       <c r="N643" s="2" t="n"/>
+      <c r="O643" s="2" t="n"/>
+      <c r="P643" s="2" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n"/>
@@ -11004,6 +12320,8 @@
       <c r="L644" s="2" t="n"/>
       <c r="M644" s="2" t="n"/>
       <c r="N644" s="2" t="n"/>
+      <c r="O644" s="2" t="n"/>
+      <c r="P644" s="2" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="n"/>
@@ -11020,6 +12338,8 @@
       <c r="L645" s="2" t="n"/>
       <c r="M645" s="2" t="n"/>
       <c r="N645" s="2" t="n"/>
+      <c r="O645" s="2" t="n"/>
+      <c r="P645" s="2" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n"/>
@@ -11036,6 +12356,8 @@
       <c r="L646" s="2" t="n"/>
       <c r="M646" s="2" t="n"/>
       <c r="N646" s="2" t="n"/>
+      <c r="O646" s="2" t="n"/>
+      <c r="P646" s="2" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="n"/>
@@ -11052,6 +12374,8 @@
       <c r="L647" s="2" t="n"/>
       <c r="M647" s="2" t="n"/>
       <c r="N647" s="2" t="n"/>
+      <c r="O647" s="2" t="n"/>
+      <c r="P647" s="2" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="n"/>
@@ -11068,6 +12392,8 @@
       <c r="L648" s="2" t="n"/>
       <c r="M648" s="2" t="n"/>
       <c r="N648" s="2" t="n"/>
+      <c r="O648" s="2" t="n"/>
+      <c r="P648" s="2" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="2" t="n"/>
@@ -11084,6 +12410,8 @@
       <c r="L649" s="2" t="n"/>
       <c r="M649" s="2" t="n"/>
       <c r="N649" s="2" t="n"/>
+      <c r="O649" s="2" t="n"/>
+      <c r="P649" s="2" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n"/>
@@ -11100,6 +12428,8 @@
       <c r="L650" s="2" t="n"/>
       <c r="M650" s="2" t="n"/>
       <c r="N650" s="2" t="n"/>
+      <c r="O650" s="2" t="n"/>
+      <c r="P650" s="2" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="n"/>
@@ -11116,6 +12446,8 @@
       <c r="L651" s="2" t="n"/>
       <c r="M651" s="2" t="n"/>
       <c r="N651" s="2" t="n"/>
+      <c r="O651" s="2" t="n"/>
+      <c r="P651" s="2" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="n"/>
@@ -11132,6 +12464,8 @@
       <c r="L652" s="2" t="n"/>
       <c r="M652" s="2" t="n"/>
       <c r="N652" s="2" t="n"/>
+      <c r="O652" s="2" t="n"/>
+      <c r="P652" s="2" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="n"/>
@@ -11148,6 +12482,8 @@
       <c r="L653" s="2" t="n"/>
       <c r="M653" s="2" t="n"/>
       <c r="N653" s="2" t="n"/>
+      <c r="O653" s="2" t="n"/>
+      <c r="P653" s="2" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n"/>
@@ -11164,6 +12500,8 @@
       <c r="L654" s="2" t="n"/>
       <c r="M654" s="2" t="n"/>
       <c r="N654" s="2" t="n"/>
+      <c r="O654" s="2" t="n"/>
+      <c r="P654" s="2" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="2" t="n"/>
@@ -11180,6 +12518,8 @@
       <c r="L655" s="2" t="n"/>
       <c r="M655" s="2" t="n"/>
       <c r="N655" s="2" t="n"/>
+      <c r="O655" s="2" t="n"/>
+      <c r="P655" s="2" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="n"/>
@@ -11196,6 +12536,8 @@
       <c r="L656" s="2" t="n"/>
       <c r="M656" s="2" t="n"/>
       <c r="N656" s="2" t="n"/>
+      <c r="O656" s="2" t="n"/>
+      <c r="P656" s="2" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="n"/>
@@ -11212,6 +12554,8 @@
       <c r="L657" s="2" t="n"/>
       <c r="M657" s="2" t="n"/>
       <c r="N657" s="2" t="n"/>
+      <c r="O657" s="2" t="n"/>
+      <c r="P657" s="2" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="n"/>
@@ -11228,6 +12572,8 @@
       <c r="L658" s="2" t="n"/>
       <c r="M658" s="2" t="n"/>
       <c r="N658" s="2" t="n"/>
+      <c r="O658" s="2" t="n"/>
+      <c r="P658" s="2" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="2" t="n"/>
@@ -11244,6 +12590,8 @@
       <c r="L659" s="2" t="n"/>
       <c r="M659" s="2" t="n"/>
       <c r="N659" s="2" t="n"/>
+      <c r="O659" s="2" t="n"/>
+      <c r="P659" s="2" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="n"/>
@@ -11260,6 +12608,8 @@
       <c r="L660" s="2" t="n"/>
       <c r="M660" s="2" t="n"/>
       <c r="N660" s="2" t="n"/>
+      <c r="O660" s="2" t="n"/>
+      <c r="P660" s="2" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="n"/>
@@ -11276,6 +12626,8 @@
       <c r="L661" s="2" t="n"/>
       <c r="M661" s="2" t="n"/>
       <c r="N661" s="2" t="n"/>
+      <c r="O661" s="2" t="n"/>
+      <c r="P661" s="2" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="n"/>
@@ -11292,6 +12644,8 @@
       <c r="L662" s="2" t="n"/>
       <c r="M662" s="2" t="n"/>
       <c r="N662" s="2" t="n"/>
+      <c r="O662" s="2" t="n"/>
+      <c r="P662" s="2" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="n"/>
@@ -11308,6 +12662,8 @@
       <c r="L663" s="2" t="n"/>
       <c r="M663" s="2" t="n"/>
       <c r="N663" s="2" t="n"/>
+      <c r="O663" s="2" t="n"/>
+      <c r="P663" s="2" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="n"/>
@@ -11324,6 +12680,8 @@
       <c r="L664" s="2" t="n"/>
       <c r="M664" s="2" t="n"/>
       <c r="N664" s="2" t="n"/>
+      <c r="O664" s="2" t="n"/>
+      <c r="P664" s="2" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="n"/>
@@ -11340,6 +12698,8 @@
       <c r="L665" s="2" t="n"/>
       <c r="M665" s="2" t="n"/>
       <c r="N665" s="2" t="n"/>
+      <c r="O665" s="2" t="n"/>
+      <c r="P665" s="2" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="n"/>
@@ -11356,6 +12716,8 @@
       <c r="L666" s="2" t="n"/>
       <c r="M666" s="2" t="n"/>
       <c r="N666" s="2" t="n"/>
+      <c r="O666" s="2" t="n"/>
+      <c r="P666" s="2" t="n"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="n"/>
@@ -11372,6 +12734,8 @@
       <c r="L667" s="2" t="n"/>
       <c r="M667" s="2" t="n"/>
       <c r="N667" s="2" t="n"/>
+      <c r="O667" s="2" t="n"/>
+      <c r="P667" s="2" t="n"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="n"/>
@@ -11388,6 +12752,8 @@
       <c r="L668" s="2" t="n"/>
       <c r="M668" s="2" t="n"/>
       <c r="N668" s="2" t="n"/>
+      <c r="O668" s="2" t="n"/>
+      <c r="P668" s="2" t="n"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="n"/>
@@ -11404,6 +12770,8 @@
       <c r="L669" s="2" t="n"/>
       <c r="M669" s="2" t="n"/>
       <c r="N669" s="2" t="n"/>
+      <c r="O669" s="2" t="n"/>
+      <c r="P669" s="2" t="n"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="n"/>
@@ -11420,6 +12788,8 @@
       <c r="L670" s="2" t="n"/>
       <c r="M670" s="2" t="n"/>
       <c r="N670" s="2" t="n"/>
+      <c r="O670" s="2" t="n"/>
+      <c r="P670" s="2" t="n"/>
     </row>
     <row r="671">
       <c r="A671" s="2" t="n"/>
@@ -11436,6 +12806,8 @@
       <c r="L671" s="2" t="n"/>
       <c r="M671" s="2" t="n"/>
       <c r="N671" s="2" t="n"/>
+      <c r="O671" s="2" t="n"/>
+      <c r="P671" s="2" t="n"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="n"/>
@@ -11452,6 +12824,8 @@
       <c r="L672" s="2" t="n"/>
       <c r="M672" s="2" t="n"/>
       <c r="N672" s="2" t="n"/>
+      <c r="O672" s="2" t="n"/>
+      <c r="P672" s="2" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="n"/>
@@ -11468,6 +12842,8 @@
       <c r="L673" s="2" t="n"/>
       <c r="M673" s="2" t="n"/>
       <c r="N673" s="2" t="n"/>
+      <c r="O673" s="2" t="n"/>
+      <c r="P673" s="2" t="n"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="n"/>
@@ -11484,6 +12860,8 @@
       <c r="L674" s="2" t="n"/>
       <c r="M674" s="2" t="n"/>
       <c r="N674" s="2" t="n"/>
+      <c r="O674" s="2" t="n"/>
+      <c r="P674" s="2" t="n"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="n"/>
@@ -11500,6 +12878,8 @@
       <c r="L675" s="2" t="n"/>
       <c r="M675" s="2" t="n"/>
       <c r="N675" s="2" t="n"/>
+      <c r="O675" s="2" t="n"/>
+      <c r="P675" s="2" t="n"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="n"/>
@@ -11516,6 +12896,8 @@
       <c r="L676" s="2" t="n"/>
       <c r="M676" s="2" t="n"/>
       <c r="N676" s="2" t="n"/>
+      <c r="O676" s="2" t="n"/>
+      <c r="P676" s="2" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="n"/>
@@ -11532,6 +12914,8 @@
       <c r="L677" s="2" t="n"/>
       <c r="M677" s="2" t="n"/>
       <c r="N677" s="2" t="n"/>
+      <c r="O677" s="2" t="n"/>
+      <c r="P677" s="2" t="n"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="n"/>
@@ -11548,6 +12932,8 @@
       <c r="L678" s="2" t="n"/>
       <c r="M678" s="2" t="n"/>
       <c r="N678" s="2" t="n"/>
+      <c r="O678" s="2" t="n"/>
+      <c r="P678" s="2" t="n"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="n"/>
@@ -11564,6 +12950,8 @@
       <c r="L679" s="2" t="n"/>
       <c r="M679" s="2" t="n"/>
       <c r="N679" s="2" t="n"/>
+      <c r="O679" s="2" t="n"/>
+      <c r="P679" s="2" t="n"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="n"/>
@@ -11580,6 +12968,8 @@
       <c r="L680" s="2" t="n"/>
       <c r="M680" s="2" t="n"/>
       <c r="N680" s="2" t="n"/>
+      <c r="O680" s="2" t="n"/>
+      <c r="P680" s="2" t="n"/>
     </row>
     <row r="681">
       <c r="A681" s="2" t="n"/>
@@ -11596,6 +12986,8 @@
       <c r="L681" s="2" t="n"/>
       <c r="M681" s="2" t="n"/>
       <c r="N681" s="2" t="n"/>
+      <c r="O681" s="2" t="n"/>
+      <c r="P681" s="2" t="n"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n"/>
@@ -11612,6 +13004,8 @@
       <c r="L682" s="2" t="n"/>
       <c r="M682" s="2" t="n"/>
       <c r="N682" s="2" t="n"/>
+      <c r="O682" s="2" t="n"/>
+      <c r="P682" s="2" t="n"/>
     </row>
     <row r="683">
       <c r="A683" s="2" t="n"/>
@@ -11628,6 +13022,8 @@
       <c r="L683" s="2" t="n"/>
       <c r="M683" s="2" t="n"/>
       <c r="N683" s="2" t="n"/>
+      <c r="O683" s="2" t="n"/>
+      <c r="P683" s="2" t="n"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="n"/>
@@ -11644,6 +13040,8 @@
       <c r="L684" s="2" t="n"/>
       <c r="M684" s="2" t="n"/>
       <c r="N684" s="2" t="n"/>
+      <c r="O684" s="2" t="n"/>
+      <c r="P684" s="2" t="n"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="n"/>
@@ -11660,6 +13058,8 @@
       <c r="L685" s="2" t="n"/>
       <c r="M685" s="2" t="n"/>
       <c r="N685" s="2" t="n"/>
+      <c r="O685" s="2" t="n"/>
+      <c r="P685" s="2" t="n"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="n"/>
@@ -11676,6 +13076,8 @@
       <c r="L686" s="2" t="n"/>
       <c r="M686" s="2" t="n"/>
       <c r="N686" s="2" t="n"/>
+      <c r="O686" s="2" t="n"/>
+      <c r="P686" s="2" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="n"/>
@@ -11692,6 +13094,8 @@
       <c r="L687" s="2" t="n"/>
       <c r="M687" s="2" t="n"/>
       <c r="N687" s="2" t="n"/>
+      <c r="O687" s="2" t="n"/>
+      <c r="P687" s="2" t="n"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="n"/>
@@ -11708,6 +13112,8 @@
       <c r="L688" s="2" t="n"/>
       <c r="M688" s="2" t="n"/>
       <c r="N688" s="2" t="n"/>
+      <c r="O688" s="2" t="n"/>
+      <c r="P688" s="2" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="n"/>
@@ -11724,6 +13130,8 @@
       <c r="L689" s="2" t="n"/>
       <c r="M689" s="2" t="n"/>
       <c r="N689" s="2" t="n"/>
+      <c r="O689" s="2" t="n"/>
+      <c r="P689" s="2" t="n"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="n"/>
@@ -11740,6 +13148,8 @@
       <c r="L690" s="2" t="n"/>
       <c r="M690" s="2" t="n"/>
       <c r="N690" s="2" t="n"/>
+      <c r="O690" s="2" t="n"/>
+      <c r="P690" s="2" t="n"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="n"/>
@@ -11756,6 +13166,8 @@
       <c r="L691" s="2" t="n"/>
       <c r="M691" s="2" t="n"/>
       <c r="N691" s="2" t="n"/>
+      <c r="O691" s="2" t="n"/>
+      <c r="P691" s="2" t="n"/>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n"/>
@@ -11772,6 +13184,8 @@
       <c r="L692" s="2" t="n"/>
       <c r="M692" s="2" t="n"/>
       <c r="N692" s="2" t="n"/>
+      <c r="O692" s="2" t="n"/>
+      <c r="P692" s="2" t="n"/>
     </row>
     <row r="693">
       <c r="A693" s="2" t="n"/>
@@ -11788,6 +13202,8 @@
       <c r="L693" s="2" t="n"/>
       <c r="M693" s="2" t="n"/>
       <c r="N693" s="2" t="n"/>
+      <c r="O693" s="2" t="n"/>
+      <c r="P693" s="2" t="n"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="n"/>
@@ -11804,6 +13220,8 @@
       <c r="L694" s="2" t="n"/>
       <c r="M694" s="2" t="n"/>
       <c r="N694" s="2" t="n"/>
+      <c r="O694" s="2" t="n"/>
+      <c r="P694" s="2" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="n"/>
@@ -11820,6 +13238,8 @@
       <c r="L695" s="2" t="n"/>
       <c r="M695" s="2" t="n"/>
       <c r="N695" s="2" t="n"/>
+      <c r="O695" s="2" t="n"/>
+      <c r="P695" s="2" t="n"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="n"/>
@@ -11836,6 +13256,8 @@
       <c r="L696" s="2" t="n"/>
       <c r="M696" s="2" t="n"/>
       <c r="N696" s="2" t="n"/>
+      <c r="O696" s="2" t="n"/>
+      <c r="P696" s="2" t="n"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="n"/>
@@ -11852,6 +13274,8 @@
       <c r="L697" s="2" t="n"/>
       <c r="M697" s="2" t="n"/>
       <c r="N697" s="2" t="n"/>
+      <c r="O697" s="2" t="n"/>
+      <c r="P697" s="2" t="n"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="n"/>
@@ -11868,6 +13292,8 @@
       <c r="L698" s="2" t="n"/>
       <c r="M698" s="2" t="n"/>
       <c r="N698" s="2" t="n"/>
+      <c r="O698" s="2" t="n"/>
+      <c r="P698" s="2" t="n"/>
     </row>
     <row r="699">
       <c r="A699" s="2" t="n"/>
@@ -11884,6 +13310,8 @@
       <c r="L699" s="2" t="n"/>
       <c r="M699" s="2" t="n"/>
       <c r="N699" s="2" t="n"/>
+      <c r="O699" s="2" t="n"/>
+      <c r="P699" s="2" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="n"/>
@@ -11900,6 +13328,8 @@
       <c r="L700" s="2" t="n"/>
       <c r="M700" s="2" t="n"/>
       <c r="N700" s="2" t="n"/>
+      <c r="O700" s="2" t="n"/>
+      <c r="P700" s="2" t="n"/>
     </row>
     <row r="701">
       <c r="A701" s="2" t="n"/>
@@ -11916,6 +13346,8 @@
       <c r="L701" s="2" t="n"/>
       <c r="M701" s="2" t="n"/>
       <c r="N701" s="2" t="n"/>
+      <c r="O701" s="2" t="n"/>
+      <c r="P701" s="2" t="n"/>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n"/>
@@ -11932,6 +13364,8 @@
       <c r="L702" s="2" t="n"/>
       <c r="M702" s="2" t="n"/>
       <c r="N702" s="2" t="n"/>
+      <c r="O702" s="2" t="n"/>
+      <c r="P702" s="2" t="n"/>
     </row>
     <row r="703">
       <c r="A703" s="2" t="n"/>
@@ -11948,6 +13382,8 @@
       <c r="L703" s="2" t="n"/>
       <c r="M703" s="2" t="n"/>
       <c r="N703" s="2" t="n"/>
+      <c r="O703" s="2" t="n"/>
+      <c r="P703" s="2" t="n"/>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n"/>
@@ -11964,6 +13400,8 @@
       <c r="L704" s="2" t="n"/>
       <c r="M704" s="2" t="n"/>
       <c r="N704" s="2" t="n"/>
+      <c r="O704" s="2" t="n"/>
+      <c r="P704" s="2" t="n"/>
     </row>
     <row r="705">
       <c r="A705" s="2" t="n"/>
@@ -11980,6 +13418,8 @@
       <c r="L705" s="2" t="n"/>
       <c r="M705" s="2" t="n"/>
       <c r="N705" s="2" t="n"/>
+      <c r="O705" s="2" t="n"/>
+      <c r="P705" s="2" t="n"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n"/>
@@ -11996,6 +13436,8 @@
       <c r="L706" s="2" t="n"/>
       <c r="M706" s="2" t="n"/>
       <c r="N706" s="2" t="n"/>
+      <c r="O706" s="2" t="n"/>
+      <c r="P706" s="2" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n"/>
@@ -12012,6 +13454,8 @@
       <c r="L707" s="2" t="n"/>
       <c r="M707" s="2" t="n"/>
       <c r="N707" s="2" t="n"/>
+      <c r="O707" s="2" t="n"/>
+      <c r="P707" s="2" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n"/>
@@ -12028,6 +13472,8 @@
       <c r="L708" s="2" t="n"/>
       <c r="M708" s="2" t="n"/>
       <c r="N708" s="2" t="n"/>
+      <c r="O708" s="2" t="n"/>
+      <c r="P708" s="2" t="n"/>
     </row>
     <row r="709">
       <c r="A709" s="2" t="n"/>
@@ -12044,6 +13490,8 @@
       <c r="L709" s="2" t="n"/>
       <c r="M709" s="2" t="n"/>
       <c r="N709" s="2" t="n"/>
+      <c r="O709" s="2" t="n"/>
+      <c r="P709" s="2" t="n"/>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n"/>
@@ -12060,6 +13508,8 @@
       <c r="L710" s="2" t="n"/>
       <c r="M710" s="2" t="n"/>
       <c r="N710" s="2" t="n"/>
+      <c r="O710" s="2" t="n"/>
+      <c r="P710" s="2" t="n"/>
     </row>
     <row r="711">
       <c r="A711" s="2" t="n"/>
@@ -12076,6 +13526,8 @@
       <c r="L711" s="2" t="n"/>
       <c r="M711" s="2" t="n"/>
       <c r="N711" s="2" t="n"/>
+      <c r="O711" s="2" t="n"/>
+      <c r="P711" s="2" t="n"/>
     </row>
     <row r="712">
       <c r="A712" s="2" t="n"/>
@@ -12092,6 +13544,8 @@
       <c r="L712" s="2" t="n"/>
       <c r="M712" s="2" t="n"/>
       <c r="N712" s="2" t="n"/>
+      <c r="O712" s="2" t="n"/>
+      <c r="P712" s="2" t="n"/>
     </row>
     <row r="713">
       <c r="A713" s="2" t="n"/>
@@ -12108,6 +13562,8 @@
       <c r="L713" s="2" t="n"/>
       <c r="M713" s="2" t="n"/>
       <c r="N713" s="2" t="n"/>
+      <c r="O713" s="2" t="n"/>
+      <c r="P713" s="2" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="2" t="n"/>
@@ -12124,6 +13580,8 @@
       <c r="L714" s="2" t="n"/>
       <c r="M714" s="2" t="n"/>
       <c r="N714" s="2" t="n"/>
+      <c r="O714" s="2" t="n"/>
+      <c r="P714" s="2" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="n"/>
@@ -12140,6 +13598,8 @@
       <c r="L715" s="2" t="n"/>
       <c r="M715" s="2" t="n"/>
       <c r="N715" s="2" t="n"/>
+      <c r="O715" s="2" t="n"/>
+      <c r="P715" s="2" t="n"/>
     </row>
     <row r="716">
       <c r="A716" s="2" t="n"/>
@@ -12156,6 +13616,8 @@
       <c r="L716" s="2" t="n"/>
       <c r="M716" s="2" t="n"/>
       <c r="N716" s="2" t="n"/>
+      <c r="O716" s="2" t="n"/>
+      <c r="P716" s="2" t="n"/>
     </row>
     <row r="717">
       <c r="A717" s="2" t="n"/>
@@ -12172,6 +13634,8 @@
       <c r="L717" s="2" t="n"/>
       <c r="M717" s="2" t="n"/>
       <c r="N717" s="2" t="n"/>
+      <c r="O717" s="2" t="n"/>
+      <c r="P717" s="2" t="n"/>
     </row>
     <row r="718">
       <c r="A718" s="2" t="n"/>
@@ -12188,6 +13652,8 @@
       <c r="L718" s="2" t="n"/>
       <c r="M718" s="2" t="n"/>
       <c r="N718" s="2" t="n"/>
+      <c r="O718" s="2" t="n"/>
+      <c r="P718" s="2" t="n"/>
     </row>
     <row r="719">
       <c r="A719" s="2" t="n"/>
@@ -12204,6 +13670,8 @@
       <c r="L719" s="2" t="n"/>
       <c r="M719" s="2" t="n"/>
       <c r="N719" s="2" t="n"/>
+      <c r="O719" s="2" t="n"/>
+      <c r="P719" s="2" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="2" t="n"/>
@@ -12220,6 +13688,8 @@
       <c r="L720" s="2" t="n"/>
       <c r="M720" s="2" t="n"/>
       <c r="N720" s="2" t="n"/>
+      <c r="O720" s="2" t="n"/>
+      <c r="P720" s="2" t="n"/>
     </row>
     <row r="721">
       <c r="A721" s="2" t="n"/>
@@ -12236,6 +13706,8 @@
       <c r="L721" s="2" t="n"/>
       <c r="M721" s="2" t="n"/>
       <c r="N721" s="2" t="n"/>
+      <c r="O721" s="2" t="n"/>
+      <c r="P721" s="2" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="2" t="n"/>
@@ -12252,6 +13724,8 @@
       <c r="L722" s="2" t="n"/>
       <c r="M722" s="2" t="n"/>
       <c r="N722" s="2" t="n"/>
+      <c r="O722" s="2" t="n"/>
+      <c r="P722" s="2" t="n"/>
     </row>
     <row r="723">
       <c r="A723" s="2" t="n"/>
@@ -12268,6 +13742,8 @@
       <c r="L723" s="2" t="n"/>
       <c r="M723" s="2" t="n"/>
       <c r="N723" s="2" t="n"/>
+      <c r="O723" s="2" t="n"/>
+      <c r="P723" s="2" t="n"/>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n"/>
@@ -12284,6 +13760,8 @@
       <c r="L724" s="2" t="n"/>
       <c r="M724" s="2" t="n"/>
       <c r="N724" s="2" t="n"/>
+      <c r="O724" s="2" t="n"/>
+      <c r="P724" s="2" t="n"/>
     </row>
     <row r="725">
       <c r="A725" s="2" t="n"/>
@@ -12300,6 +13778,8 @@
       <c r="L725" s="2" t="n"/>
       <c r="M725" s="2" t="n"/>
       <c r="N725" s="2" t="n"/>
+      <c r="O725" s="2" t="n"/>
+      <c r="P725" s="2" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="2" t="n"/>
@@ -12316,6 +13796,8 @@
       <c r="L726" s="2" t="n"/>
       <c r="M726" s="2" t="n"/>
       <c r="N726" s="2" t="n"/>
+      <c r="O726" s="2" t="n"/>
+      <c r="P726" s="2" t="n"/>
     </row>
     <row r="727">
       <c r="A727" s="2" t="n"/>
@@ -12332,6 +13814,8 @@
       <c r="L727" s="2" t="n"/>
       <c r="M727" s="2" t="n"/>
       <c r="N727" s="2" t="n"/>
+      <c r="O727" s="2" t="n"/>
+      <c r="P727" s="2" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n"/>
@@ -12348,6 +13832,8 @@
       <c r="L728" s="2" t="n"/>
       <c r="M728" s="2" t="n"/>
       <c r="N728" s="2" t="n"/>
+      <c r="O728" s="2" t="n"/>
+      <c r="P728" s="2" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n"/>
@@ -12364,6 +13850,8 @@
       <c r="L729" s="2" t="n"/>
       <c r="M729" s="2" t="n"/>
       <c r="N729" s="2" t="n"/>
+      <c r="O729" s="2" t="n"/>
+      <c r="P729" s="2" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n"/>
@@ -12380,6 +13868,8 @@
       <c r="L730" s="2" t="n"/>
       <c r="M730" s="2" t="n"/>
       <c r="N730" s="2" t="n"/>
+      <c r="O730" s="2" t="n"/>
+      <c r="P730" s="2" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n"/>
@@ -12396,6 +13886,8 @@
       <c r="L731" s="2" t="n"/>
       <c r="M731" s="2" t="n"/>
       <c r="N731" s="2" t="n"/>
+      <c r="O731" s="2" t="n"/>
+      <c r="P731" s="2" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n"/>
@@ -12412,6 +13904,8 @@
       <c r="L732" s="2" t="n"/>
       <c r="M732" s="2" t="n"/>
       <c r="N732" s="2" t="n"/>
+      <c r="O732" s="2" t="n"/>
+      <c r="P732" s="2" t="n"/>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n"/>
@@ -12428,6 +13922,8 @@
       <c r="L733" s="2" t="n"/>
       <c r="M733" s="2" t="n"/>
       <c r="N733" s="2" t="n"/>
+      <c r="O733" s="2" t="n"/>
+      <c r="P733" s="2" t="n"/>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n"/>
@@ -12444,6 +13940,8 @@
       <c r="L734" s="2" t="n"/>
       <c r="M734" s="2" t="n"/>
       <c r="N734" s="2" t="n"/>
+      <c r="O734" s="2" t="n"/>
+      <c r="P734" s="2" t="n"/>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n"/>
@@ -12460,6 +13958,8 @@
       <c r="L735" s="2" t="n"/>
       <c r="M735" s="2" t="n"/>
       <c r="N735" s="2" t="n"/>
+      <c r="O735" s="2" t="n"/>
+      <c r="P735" s="2" t="n"/>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n"/>
@@ -12476,6 +13976,8 @@
       <c r="L736" s="2" t="n"/>
       <c r="M736" s="2" t="n"/>
       <c r="N736" s="2" t="n"/>
+      <c r="O736" s="2" t="n"/>
+      <c r="P736" s="2" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n"/>
@@ -12492,6 +13994,8 @@
       <c r="L737" s="2" t="n"/>
       <c r="M737" s="2" t="n"/>
       <c r="N737" s="2" t="n"/>
+      <c r="O737" s="2" t="n"/>
+      <c r="P737" s="2" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n"/>
@@ -12508,6 +14012,8 @@
       <c r="L738" s="2" t="n"/>
       <c r="M738" s="2" t="n"/>
       <c r="N738" s="2" t="n"/>
+      <c r="O738" s="2" t="n"/>
+      <c r="P738" s="2" t="n"/>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n"/>
@@ -12524,6 +14030,8 @@
       <c r="L739" s="2" t="n"/>
       <c r="M739" s="2" t="n"/>
       <c r="N739" s="2" t="n"/>
+      <c r="O739" s="2" t="n"/>
+      <c r="P739" s="2" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n"/>
@@ -12540,6 +14048,8 @@
       <c r="L740" s="2" t="n"/>
       <c r="M740" s="2" t="n"/>
       <c r="N740" s="2" t="n"/>
+      <c r="O740" s="2" t="n"/>
+      <c r="P740" s="2" t="n"/>
     </row>
     <row r="741">
       <c r="A741" s="2" t="n"/>
@@ -12556,6 +14066,8 @@
       <c r="L741" s="2" t="n"/>
       <c r="M741" s="2" t="n"/>
       <c r="N741" s="2" t="n"/>
+      <c r="O741" s="2" t="n"/>
+      <c r="P741" s="2" t="n"/>
     </row>
     <row r="742">
       <c r="A742" s="2" t="n"/>
@@ -12572,6 +14084,8 @@
       <c r="L742" s="2" t="n"/>
       <c r="M742" s="2" t="n"/>
       <c r="N742" s="2" t="n"/>
+      <c r="O742" s="2" t="n"/>
+      <c r="P742" s="2" t="n"/>
     </row>
     <row r="743">
       <c r="A743" s="2" t="n"/>
@@ -12588,6 +14102,8 @@
       <c r="L743" s="2" t="n"/>
       <c r="M743" s="2" t="n"/>
       <c r="N743" s="2" t="n"/>
+      <c r="O743" s="2" t="n"/>
+      <c r="P743" s="2" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n"/>
@@ -12604,6 +14120,8 @@
       <c r="L744" s="2" t="n"/>
       <c r="M744" s="2" t="n"/>
       <c r="N744" s="2" t="n"/>
+      <c r="O744" s="2" t="n"/>
+      <c r="P744" s="2" t="n"/>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n"/>
@@ -12620,6 +14138,8 @@
       <c r="L745" s="2" t="n"/>
       <c r="M745" s="2" t="n"/>
       <c r="N745" s="2" t="n"/>
+      <c r="O745" s="2" t="n"/>
+      <c r="P745" s="2" t="n"/>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n"/>
@@ -12636,6 +14156,8 @@
       <c r="L746" s="2" t="n"/>
       <c r="M746" s="2" t="n"/>
       <c r="N746" s="2" t="n"/>
+      <c r="O746" s="2" t="n"/>
+      <c r="P746" s="2" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="2" t="n"/>
@@ -12652,6 +14174,8 @@
       <c r="L747" s="2" t="n"/>
       <c r="M747" s="2" t="n"/>
       <c r="N747" s="2" t="n"/>
+      <c r="O747" s="2" t="n"/>
+      <c r="P747" s="2" t="n"/>
     </row>
     <row r="748">
       <c r="A748" s="2" t="n"/>
@@ -12668,6 +14192,8 @@
       <c r="L748" s="2" t="n"/>
       <c r="M748" s="2" t="n"/>
       <c r="N748" s="2" t="n"/>
+      <c r="O748" s="2" t="n"/>
+      <c r="P748" s="2" t="n"/>
     </row>
     <row r="749">
       <c r="A749" s="2" t="n"/>
@@ -12684,6 +14210,8 @@
       <c r="L749" s="2" t="n"/>
       <c r="M749" s="2" t="n"/>
       <c r="N749" s="2" t="n"/>
+      <c r="O749" s="2" t="n"/>
+      <c r="P749" s="2" t="n"/>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n"/>
@@ -12700,6 +14228,8 @@
       <c r="L750" s="2" t="n"/>
       <c r="M750" s="2" t="n"/>
       <c r="N750" s="2" t="n"/>
+      <c r="O750" s="2" t="n"/>
+      <c r="P750" s="2" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n"/>
@@ -12716,6 +14246,8 @@
       <c r="L751" s="2" t="n"/>
       <c r="M751" s="2" t="n"/>
       <c r="N751" s="2" t="n"/>
+      <c r="O751" s="2" t="n"/>
+      <c r="P751" s="2" t="n"/>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n"/>
@@ -12732,6 +14264,8 @@
       <c r="L752" s="2" t="n"/>
       <c r="M752" s="2" t="n"/>
       <c r="N752" s="2" t="n"/>
+      <c r="O752" s="2" t="n"/>
+      <c r="P752" s="2" t="n"/>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n"/>
@@ -12748,6 +14282,8 @@
       <c r="L753" s="2" t="n"/>
       <c r="M753" s="2" t="n"/>
       <c r="N753" s="2" t="n"/>
+      <c r="O753" s="2" t="n"/>
+      <c r="P753" s="2" t="n"/>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n"/>
@@ -12764,6 +14300,8 @@
       <c r="L754" s="2" t="n"/>
       <c r="M754" s="2" t="n"/>
       <c r="N754" s="2" t="n"/>
+      <c r="O754" s="2" t="n"/>
+      <c r="P754" s="2" t="n"/>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n"/>
@@ -12780,6 +14318,8 @@
       <c r="L755" s="2" t="n"/>
       <c r="M755" s="2" t="n"/>
       <c r="N755" s="2" t="n"/>
+      <c r="O755" s="2" t="n"/>
+      <c r="P755" s="2" t="n"/>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n"/>
@@ -12796,6 +14336,8 @@
       <c r="L756" s="2" t="n"/>
       <c r="M756" s="2" t="n"/>
       <c r="N756" s="2" t="n"/>
+      <c r="O756" s="2" t="n"/>
+      <c r="P756" s="2" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="2" t="n"/>
@@ -12812,6 +14354,8 @@
       <c r="L757" s="2" t="n"/>
       <c r="M757" s="2" t="n"/>
       <c r="N757" s="2" t="n"/>
+      <c r="O757" s="2" t="n"/>
+      <c r="P757" s="2" t="n"/>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n"/>
@@ -12828,6 +14372,8 @@
       <c r="L758" s="2" t="n"/>
       <c r="M758" s="2" t="n"/>
       <c r="N758" s="2" t="n"/>
+      <c r="O758" s="2" t="n"/>
+      <c r="P758" s="2" t="n"/>
     </row>
     <row r="759">
       <c r="A759" s="2" t="n"/>
@@ -12844,6 +14390,8 @@
       <c r="L759" s="2" t="n"/>
       <c r="M759" s="2" t="n"/>
       <c r="N759" s="2" t="n"/>
+      <c r="O759" s="2" t="n"/>
+      <c r="P759" s="2" t="n"/>
     </row>
     <row r="760">
       <c r="A760" s="2" t="n"/>
@@ -12860,6 +14408,8 @@
       <c r="L760" s="2" t="n"/>
       <c r="M760" s="2" t="n"/>
       <c r="N760" s="2" t="n"/>
+      <c r="O760" s="2" t="n"/>
+      <c r="P760" s="2" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="2" t="n"/>
@@ -12876,6 +14426,8 @@
       <c r="L761" s="2" t="n"/>
       <c r="M761" s="2" t="n"/>
       <c r="N761" s="2" t="n"/>
+      <c r="O761" s="2" t="n"/>
+      <c r="P761" s="2" t="n"/>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n"/>
@@ -12892,6 +14444,8 @@
       <c r="L762" s="2" t="n"/>
       <c r="M762" s="2" t="n"/>
       <c r="N762" s="2" t="n"/>
+      <c r="O762" s="2" t="n"/>
+      <c r="P762" s="2" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n"/>
@@ -12908,6 +14462,8 @@
       <c r="L763" s="2" t="n"/>
       <c r="M763" s="2" t="n"/>
       <c r="N763" s="2" t="n"/>
+      <c r="O763" s="2" t="n"/>
+      <c r="P763" s="2" t="n"/>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n"/>
@@ -12924,6 +14480,8 @@
       <c r="L764" s="2" t="n"/>
       <c r="M764" s="2" t="n"/>
       <c r="N764" s="2" t="n"/>
+      <c r="O764" s="2" t="n"/>
+      <c r="P764" s="2" t="n"/>
     </row>
     <row r="765">
       <c r="A765" s="2" t="n"/>
@@ -12940,6 +14498,8 @@
       <c r="L765" s="2" t="n"/>
       <c r="M765" s="2" t="n"/>
       <c r="N765" s="2" t="n"/>
+      <c r="O765" s="2" t="n"/>
+      <c r="P765" s="2" t="n"/>
     </row>
     <row r="766">
       <c r="A766" s="2" t="n"/>
@@ -12956,6 +14516,8 @@
       <c r="L766" s="2" t="n"/>
       <c r="M766" s="2" t="n"/>
       <c r="N766" s="2" t="n"/>
+      <c r="O766" s="2" t="n"/>
+      <c r="P766" s="2" t="n"/>
     </row>
     <row r="767">
       <c r="A767" s="2" t="n"/>
@@ -12972,6 +14534,8 @@
       <c r="L767" s="2" t="n"/>
       <c r="M767" s="2" t="n"/>
       <c r="N767" s="2" t="n"/>
+      <c r="O767" s="2" t="n"/>
+      <c r="P767" s="2" t="n"/>
     </row>
     <row r="768">
       <c r="A768" s="2" t="n"/>
@@ -12988,6 +14552,8 @@
       <c r="L768" s="2" t="n"/>
       <c r="M768" s="2" t="n"/>
       <c r="N768" s="2" t="n"/>
+      <c r="O768" s="2" t="n"/>
+      <c r="P768" s="2" t="n"/>
     </row>
     <row r="769">
       <c r="A769" s="2" t="n"/>
@@ -13004,6 +14570,8 @@
       <c r="L769" s="2" t="n"/>
       <c r="M769" s="2" t="n"/>
       <c r="N769" s="2" t="n"/>
+      <c r="O769" s="2" t="n"/>
+      <c r="P769" s="2" t="n"/>
     </row>
     <row r="770">
       <c r="A770" s="2" t="n"/>
@@ -13020,6 +14588,8 @@
       <c r="L770" s="2" t="n"/>
       <c r="M770" s="2" t="n"/>
       <c r="N770" s="2" t="n"/>
+      <c r="O770" s="2" t="n"/>
+      <c r="P770" s="2" t="n"/>
     </row>
     <row r="771">
       <c r="A771" s="2" t="n"/>
@@ -13036,6 +14606,8 @@
       <c r="L771" s="2" t="n"/>
       <c r="M771" s="2" t="n"/>
       <c r="N771" s="2" t="n"/>
+      <c r="O771" s="2" t="n"/>
+      <c r="P771" s="2" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="2" t="n"/>
@@ -13052,6 +14624,8 @@
       <c r="L772" s="2" t="n"/>
       <c r="M772" s="2" t="n"/>
       <c r="N772" s="2" t="n"/>
+      <c r="O772" s="2" t="n"/>
+      <c r="P772" s="2" t="n"/>
     </row>
     <row r="773">
       <c r="A773" s="2" t="n"/>
@@ -13068,6 +14642,8 @@
       <c r="L773" s="2" t="n"/>
       <c r="M773" s="2" t="n"/>
       <c r="N773" s="2" t="n"/>
+      <c r="O773" s="2" t="n"/>
+      <c r="P773" s="2" t="n"/>
     </row>
     <row r="774">
       <c r="A774" s="2" t="n"/>
@@ -13084,6 +14660,8 @@
       <c r="L774" s="2" t="n"/>
       <c r="M774" s="2" t="n"/>
       <c r="N774" s="2" t="n"/>
+      <c r="O774" s="2" t="n"/>
+      <c r="P774" s="2" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="2" t="n"/>
@@ -13100,6 +14678,8 @@
       <c r="L775" s="2" t="n"/>
       <c r="M775" s="2" t="n"/>
       <c r="N775" s="2" t="n"/>
+      <c r="O775" s="2" t="n"/>
+      <c r="P775" s="2" t="n"/>
     </row>
     <row r="776">
       <c r="A776" s="2" t="n"/>
@@ -13116,6 +14696,8 @@
       <c r="L776" s="2" t="n"/>
       <c r="M776" s="2" t="n"/>
       <c r="N776" s="2" t="n"/>
+      <c r="O776" s="2" t="n"/>
+      <c r="P776" s="2" t="n"/>
     </row>
     <row r="777">
       <c r="A777" s="2" t="n"/>
@@ -13132,6 +14714,8 @@
       <c r="L777" s="2" t="n"/>
       <c r="M777" s="2" t="n"/>
       <c r="N777" s="2" t="n"/>
+      <c r="O777" s="2" t="n"/>
+      <c r="P777" s="2" t="n"/>
     </row>
     <row r="778">
       <c r="A778" s="2" t="n"/>
@@ -13148,6 +14732,8 @@
       <c r="L778" s="2" t="n"/>
       <c r="M778" s="2" t="n"/>
       <c r="N778" s="2" t="n"/>
+      <c r="O778" s="2" t="n"/>
+      <c r="P778" s="2" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="2" t="n"/>
@@ -13164,6 +14750,8 @@
       <c r="L779" s="2" t="n"/>
       <c r="M779" s="2" t="n"/>
       <c r="N779" s="2" t="n"/>
+      <c r="O779" s="2" t="n"/>
+      <c r="P779" s="2" t="n"/>
     </row>
     <row r="780">
       <c r="A780" s="2" t="n"/>
@@ -13180,6 +14768,8 @@
       <c r="L780" s="2" t="n"/>
       <c r="M780" s="2" t="n"/>
       <c r="N780" s="2" t="n"/>
+      <c r="O780" s="2" t="n"/>
+      <c r="P780" s="2" t="n"/>
     </row>
     <row r="781">
       <c r="A781" s="2" t="n"/>
@@ -13196,6 +14786,8 @@
       <c r="L781" s="2" t="n"/>
       <c r="M781" s="2" t="n"/>
       <c r="N781" s="2" t="n"/>
+      <c r="O781" s="2" t="n"/>
+      <c r="P781" s="2" t="n"/>
     </row>
     <row r="782">
       <c r="A782" s="2" t="n"/>
@@ -13212,6 +14804,8 @@
       <c r="L782" s="2" t="n"/>
       <c r="M782" s="2" t="n"/>
       <c r="N782" s="2" t="n"/>
+      <c r="O782" s="2" t="n"/>
+      <c r="P782" s="2" t="n"/>
     </row>
     <row r="783">
       <c r="A783" s="2" t="n"/>
@@ -13228,6 +14822,8 @@
       <c r="L783" s="2" t="n"/>
       <c r="M783" s="2" t="n"/>
       <c r="N783" s="2" t="n"/>
+      <c r="O783" s="2" t="n"/>
+      <c r="P783" s="2" t="n"/>
     </row>
     <row r="784">
       <c r="A784" s="2" t="n"/>
@@ -13244,6 +14840,8 @@
       <c r="L784" s="2" t="n"/>
       <c r="M784" s="2" t="n"/>
       <c r="N784" s="2" t="n"/>
+      <c r="O784" s="2" t="n"/>
+      <c r="P784" s="2" t="n"/>
     </row>
     <row r="785">
       <c r="A785" s="2" t="n"/>
@@ -13260,6 +14858,8 @@
       <c r="L785" s="2" t="n"/>
       <c r="M785" s="2" t="n"/>
       <c r="N785" s="2" t="n"/>
+      <c r="O785" s="2" t="n"/>
+      <c r="P785" s="2" t="n"/>
     </row>
     <row r="786">
       <c r="A786" s="2" t="n"/>
@@ -13276,6 +14876,8 @@
       <c r="L786" s="2" t="n"/>
       <c r="M786" s="2" t="n"/>
       <c r="N786" s="2" t="n"/>
+      <c r="O786" s="2" t="n"/>
+      <c r="P786" s="2" t="n"/>
     </row>
     <row r="787">
       <c r="A787" s="2" t="n"/>
@@ -13292,6 +14894,8 @@
       <c r="L787" s="2" t="n"/>
       <c r="M787" s="2" t="n"/>
       <c r="N787" s="2" t="n"/>
+      <c r="O787" s="2" t="n"/>
+      <c r="P787" s="2" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="2" t="n"/>
@@ -13308,6 +14912,8 @@
       <c r="L788" s="2" t="n"/>
       <c r="M788" s="2" t="n"/>
       <c r="N788" s="2" t="n"/>
+      <c r="O788" s="2" t="n"/>
+      <c r="P788" s="2" t="n"/>
     </row>
     <row r="789">
       <c r="A789" s="2" t="n"/>
@@ -13324,6 +14930,8 @@
       <c r="L789" s="2" t="n"/>
       <c r="M789" s="2" t="n"/>
       <c r="N789" s="2" t="n"/>
+      <c r="O789" s="2" t="n"/>
+      <c r="P789" s="2" t="n"/>
     </row>
     <row r="790">
       <c r="A790" s="2" t="n"/>
@@ -13340,6 +14948,8 @@
       <c r="L790" s="2" t="n"/>
       <c r="M790" s="2" t="n"/>
       <c r="N790" s="2" t="n"/>
+      <c r="O790" s="2" t="n"/>
+      <c r="P790" s="2" t="n"/>
     </row>
     <row r="791">
       <c r="A791" s="2" t="n"/>
@@ -13356,6 +14966,8 @@
       <c r="L791" s="2" t="n"/>
       <c r="M791" s="2" t="n"/>
       <c r="N791" s="2" t="n"/>
+      <c r="O791" s="2" t="n"/>
+      <c r="P791" s="2" t="n"/>
     </row>
     <row r="792">
       <c r="A792" s="2" t="n"/>
@@ -13372,6 +14984,8 @@
       <c r="L792" s="2" t="n"/>
       <c r="M792" s="2" t="n"/>
       <c r="N792" s="2" t="n"/>
+      <c r="O792" s="2" t="n"/>
+      <c r="P792" s="2" t="n"/>
     </row>
     <row r="793">
       <c r="A793" s="2" t="n"/>
@@ -13388,6 +15002,8 @@
       <c r="L793" s="2" t="n"/>
       <c r="M793" s="2" t="n"/>
       <c r="N793" s="2" t="n"/>
+      <c r="O793" s="2" t="n"/>
+      <c r="P793" s="2" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="2" t="n"/>
@@ -13404,6 +15020,8 @@
       <c r="L794" s="2" t="n"/>
       <c r="M794" s="2" t="n"/>
       <c r="N794" s="2" t="n"/>
+      <c r="O794" s="2" t="n"/>
+      <c r="P794" s="2" t="n"/>
     </row>
     <row r="795">
       <c r="A795" s="2" t="n"/>
@@ -13420,6 +15038,8 @@
       <c r="L795" s="2" t="n"/>
       <c r="M795" s="2" t="n"/>
       <c r="N795" s="2" t="n"/>
+      <c r="O795" s="2" t="n"/>
+      <c r="P795" s="2" t="n"/>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n"/>
@@ -13436,6 +15056,8 @@
       <c r="L796" s="2" t="n"/>
       <c r="M796" s="2" t="n"/>
       <c r="N796" s="2" t="n"/>
+      <c r="O796" s="2" t="n"/>
+      <c r="P796" s="2" t="n"/>
     </row>
     <row r="797">
       <c r="A797" s="2" t="n"/>
@@ -13452,6 +15074,8 @@
       <c r="L797" s="2" t="n"/>
       <c r="M797" s="2" t="n"/>
       <c r="N797" s="2" t="n"/>
+      <c r="O797" s="2" t="n"/>
+      <c r="P797" s="2" t="n"/>
     </row>
     <row r="798">
       <c r="A798" s="2" t="n"/>
@@ -13468,6 +15092,8 @@
       <c r="L798" s="2" t="n"/>
       <c r="M798" s="2" t="n"/>
       <c r="N798" s="2" t="n"/>
+      <c r="O798" s="2" t="n"/>
+      <c r="P798" s="2" t="n"/>
     </row>
     <row r="799">
       <c r="A799" s="2" t="n"/>
@@ -13484,6 +15110,8 @@
       <c r="L799" s="2" t="n"/>
       <c r="M799" s="2" t="n"/>
       <c r="N799" s="2" t="n"/>
+      <c r="O799" s="2" t="n"/>
+      <c r="P799" s="2" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="2" t="n"/>
@@ -13500,6 +15128,8 @@
       <c r="L800" s="2" t="n"/>
       <c r="M800" s="2" t="n"/>
       <c r="N800" s="2" t="n"/>
+      <c r="O800" s="2" t="n"/>
+      <c r="P800" s="2" t="n"/>
     </row>
     <row r="801">
       <c r="A801" s="2" t="n"/>
@@ -13516,6 +15146,8 @@
       <c r="L801" s="2" t="n"/>
       <c r="M801" s="2" t="n"/>
       <c r="N801" s="2" t="n"/>
+      <c r="O801" s="2" t="n"/>
+      <c r="P801" s="2" t="n"/>
     </row>
     <row r="802">
       <c r="A802" s="2" t="n"/>
@@ -13532,6 +15164,8 @@
       <c r="L802" s="2" t="n"/>
       <c r="M802" s="2" t="n"/>
       <c r="N802" s="2" t="n"/>
+      <c r="O802" s="2" t="n"/>
+      <c r="P802" s="2" t="n"/>
     </row>
     <row r="803">
       <c r="A803" s="2" t="n"/>
@@ -13548,6 +15182,8 @@
       <c r="L803" s="2" t="n"/>
       <c r="M803" s="2" t="n"/>
       <c r="N803" s="2" t="n"/>
+      <c r="O803" s="2" t="n"/>
+      <c r="P803" s="2" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="2" t="n"/>
@@ -13564,6 +15200,8 @@
       <c r="L804" s="2" t="n"/>
       <c r="M804" s="2" t="n"/>
       <c r="N804" s="2" t="n"/>
+      <c r="O804" s="2" t="n"/>
+      <c r="P804" s="2" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="2" t="n"/>
@@ -13580,6 +15218,8 @@
       <c r="L805" s="2" t="n"/>
       <c r="M805" s="2" t="n"/>
       <c r="N805" s="2" t="n"/>
+      <c r="O805" s="2" t="n"/>
+      <c r="P805" s="2" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="2" t="n"/>
@@ -13596,6 +15236,8 @@
       <c r="L806" s="2" t="n"/>
       <c r="M806" s="2" t="n"/>
       <c r="N806" s="2" t="n"/>
+      <c r="O806" s="2" t="n"/>
+      <c r="P806" s="2" t="n"/>
     </row>
     <row r="807">
       <c r="A807" s="2" t="n"/>
@@ -13612,6 +15254,8 @@
       <c r="L807" s="2" t="n"/>
       <c r="M807" s="2" t="n"/>
       <c r="N807" s="2" t="n"/>
+      <c r="O807" s="2" t="n"/>
+      <c r="P807" s="2" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="2" t="n"/>
@@ -13628,6 +15272,8 @@
       <c r="L808" s="2" t="n"/>
       <c r="M808" s="2" t="n"/>
       <c r="N808" s="2" t="n"/>
+      <c r="O808" s="2" t="n"/>
+      <c r="P808" s="2" t="n"/>
     </row>
     <row r="809">
       <c r="A809" s="2" t="n"/>
@@ -13644,6 +15290,8 @@
       <c r="L809" s="2" t="n"/>
       <c r="M809" s="2" t="n"/>
       <c r="N809" s="2" t="n"/>
+      <c r="O809" s="2" t="n"/>
+      <c r="P809" s="2" t="n"/>
     </row>
     <row r="810">
       <c r="A810" s="2" t="n"/>
@@ -13660,6 +15308,8 @@
       <c r="L810" s="2" t="n"/>
       <c r="M810" s="2" t="n"/>
       <c r="N810" s="2" t="n"/>
+      <c r="O810" s="2" t="n"/>
+      <c r="P810" s="2" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="2" t="n"/>
@@ -13676,6 +15326,8 @@
       <c r="L811" s="2" t="n"/>
       <c r="M811" s="2" t="n"/>
       <c r="N811" s="2" t="n"/>
+      <c r="O811" s="2" t="n"/>
+      <c r="P811" s="2" t="n"/>
     </row>
     <row r="812">
       <c r="A812" s="2" t="n"/>
@@ -13692,6 +15344,8 @@
       <c r="L812" s="2" t="n"/>
       <c r="M812" s="2" t="n"/>
       <c r="N812" s="2" t="n"/>
+      <c r="O812" s="2" t="n"/>
+      <c r="P812" s="2" t="n"/>
     </row>
     <row r="813">
       <c r="A813" s="2" t="n"/>
@@ -13708,6 +15362,8 @@
       <c r="L813" s="2" t="n"/>
       <c r="M813" s="2" t="n"/>
       <c r="N813" s="2" t="n"/>
+      <c r="O813" s="2" t="n"/>
+      <c r="P813" s="2" t="n"/>
     </row>
     <row r="814">
       <c r="A814" s="2" t="n"/>
@@ -13724,6 +15380,8 @@
       <c r="L814" s="2" t="n"/>
       <c r="M814" s="2" t="n"/>
       <c r="N814" s="2" t="n"/>
+      <c r="O814" s="2" t="n"/>
+      <c r="P814" s="2" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="2" t="n"/>
@@ -13740,6 +15398,8 @@
       <c r="L815" s="2" t="n"/>
       <c r="M815" s="2" t="n"/>
       <c r="N815" s="2" t="n"/>
+      <c r="O815" s="2" t="n"/>
+      <c r="P815" s="2" t="n"/>
     </row>
     <row r="816">
       <c r="A816" s="2" t="n"/>
@@ -13756,6 +15416,8 @@
       <c r="L816" s="2" t="n"/>
       <c r="M816" s="2" t="n"/>
       <c r="N816" s="2" t="n"/>
+      <c r="O816" s="2" t="n"/>
+      <c r="P816" s="2" t="n"/>
     </row>
     <row r="817">
       <c r="A817" s="2" t="n"/>
@@ -13772,6 +15434,8 @@
       <c r="L817" s="2" t="n"/>
       <c r="M817" s="2" t="n"/>
       <c r="N817" s="2" t="n"/>
+      <c r="O817" s="2" t="n"/>
+      <c r="P817" s="2" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="2" t="n"/>
@@ -13788,6 +15452,8 @@
       <c r="L818" s="2" t="n"/>
       <c r="M818" s="2" t="n"/>
       <c r="N818" s="2" t="n"/>
+      <c r="O818" s="2" t="n"/>
+      <c r="P818" s="2" t="n"/>
     </row>
     <row r="819">
       <c r="A819" s="2" t="n"/>
@@ -13804,6 +15470,8 @@
       <c r="L819" s="2" t="n"/>
       <c r="M819" s="2" t="n"/>
       <c r="N819" s="2" t="n"/>
+      <c r="O819" s="2" t="n"/>
+      <c r="P819" s="2" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="2" t="n"/>
@@ -13820,6 +15488,8 @@
       <c r="L820" s="2" t="n"/>
       <c r="M820" s="2" t="n"/>
       <c r="N820" s="2" t="n"/>
+      <c r="O820" s="2" t="n"/>
+      <c r="P820" s="2" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="2" t="n"/>
@@ -13836,6 +15506,8 @@
       <c r="L821" s="2" t="n"/>
       <c r="M821" s="2" t="n"/>
       <c r="N821" s="2" t="n"/>
+      <c r="O821" s="2" t="n"/>
+      <c r="P821" s="2" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="2" t="n"/>
@@ -13852,6 +15524,8 @@
       <c r="L822" s="2" t="n"/>
       <c r="M822" s="2" t="n"/>
       <c r="N822" s="2" t="n"/>
+      <c r="O822" s="2" t="n"/>
+      <c r="P822" s="2" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="2" t="n"/>
@@ -13868,6 +15542,8 @@
       <c r="L823" s="2" t="n"/>
       <c r="M823" s="2" t="n"/>
       <c r="N823" s="2" t="n"/>
+      <c r="O823" s="2" t="n"/>
+      <c r="P823" s="2" t="n"/>
     </row>
     <row r="824">
       <c r="A824" s="2" t="n"/>
@@ -13884,6 +15560,8 @@
       <c r="L824" s="2" t="n"/>
       <c r="M824" s="2" t="n"/>
       <c r="N824" s="2" t="n"/>
+      <c r="O824" s="2" t="n"/>
+      <c r="P824" s="2" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="2" t="n"/>
@@ -13900,6 +15578,8 @@
       <c r="L825" s="2" t="n"/>
       <c r="M825" s="2" t="n"/>
       <c r="N825" s="2" t="n"/>
+      <c r="O825" s="2" t="n"/>
+      <c r="P825" s="2" t="n"/>
     </row>
     <row r="826">
       <c r="A826" s="2" t="n"/>
@@ -13916,6 +15596,8 @@
       <c r="L826" s="2" t="n"/>
       <c r="M826" s="2" t="n"/>
       <c r="N826" s="2" t="n"/>
+      <c r="O826" s="2" t="n"/>
+      <c r="P826" s="2" t="n"/>
     </row>
     <row r="827">
       <c r="A827" s="2" t="n"/>
@@ -13932,6 +15614,8 @@
       <c r="L827" s="2" t="n"/>
       <c r="M827" s="2" t="n"/>
       <c r="N827" s="2" t="n"/>
+      <c r="O827" s="2" t="n"/>
+      <c r="P827" s="2" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="2" t="n"/>
@@ -13948,6 +15632,8 @@
       <c r="L828" s="2" t="n"/>
       <c r="M828" s="2" t="n"/>
       <c r="N828" s="2" t="n"/>
+      <c r="O828" s="2" t="n"/>
+      <c r="P828" s="2" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="2" t="n"/>
@@ -13964,6 +15650,8 @@
       <c r="L829" s="2" t="n"/>
       <c r="M829" s="2" t="n"/>
       <c r="N829" s="2" t="n"/>
+      <c r="O829" s="2" t="n"/>
+      <c r="P829" s="2" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="2" t="n"/>
@@ -13980,6 +15668,8 @@
       <c r="L830" s="2" t="n"/>
       <c r="M830" s="2" t="n"/>
       <c r="N830" s="2" t="n"/>
+      <c r="O830" s="2" t="n"/>
+      <c r="P830" s="2" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="2" t="n"/>
@@ -13996,6 +15686,8 @@
       <c r="L831" s="2" t="n"/>
       <c r="M831" s="2" t="n"/>
       <c r="N831" s="2" t="n"/>
+      <c r="O831" s="2" t="n"/>
+      <c r="P831" s="2" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="2" t="n"/>
@@ -14012,6 +15704,8 @@
       <c r="L832" s="2" t="n"/>
       <c r="M832" s="2" t="n"/>
       <c r="N832" s="2" t="n"/>
+      <c r="O832" s="2" t="n"/>
+      <c r="P832" s="2" t="n"/>
     </row>
     <row r="833">
       <c r="A833" s="2" t="n"/>
@@ -14028,6 +15722,8 @@
       <c r="L833" s="2" t="n"/>
       <c r="M833" s="2" t="n"/>
       <c r="N833" s="2" t="n"/>
+      <c r="O833" s="2" t="n"/>
+      <c r="P833" s="2" t="n"/>
     </row>
     <row r="834">
       <c r="A834" s="2" t="n"/>
@@ -14044,6 +15740,8 @@
       <c r="L834" s="2" t="n"/>
       <c r="M834" s="2" t="n"/>
       <c r="N834" s="2" t="n"/>
+      <c r="O834" s="2" t="n"/>
+      <c r="P834" s="2" t="n"/>
     </row>
     <row r="835">
       <c r="A835" s="2" t="n"/>
@@ -14060,6 +15758,8 @@
       <c r="L835" s="2" t="n"/>
       <c r="M835" s="2" t="n"/>
       <c r="N835" s="2" t="n"/>
+      <c r="O835" s="2" t="n"/>
+      <c r="P835" s="2" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="2" t="n"/>
@@ -14076,6 +15776,8 @@
       <c r="L836" s="2" t="n"/>
       <c r="M836" s="2" t="n"/>
       <c r="N836" s="2" t="n"/>
+      <c r="O836" s="2" t="n"/>
+      <c r="P836" s="2" t="n"/>
     </row>
     <row r="837">
       <c r="A837" s="2" t="n"/>
@@ -14092,6 +15794,8 @@
       <c r="L837" s="2" t="n"/>
       <c r="M837" s="2" t="n"/>
       <c r="N837" s="2" t="n"/>
+      <c r="O837" s="2" t="n"/>
+      <c r="P837" s="2" t="n"/>
     </row>
     <row r="838">
       <c r="A838" s="2" t="n"/>
@@ -14108,6 +15812,8 @@
       <c r="L838" s="2" t="n"/>
       <c r="M838" s="2" t="n"/>
       <c r="N838" s="2" t="n"/>
+      <c r="O838" s="2" t="n"/>
+      <c r="P838" s="2" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="2" t="n"/>
@@ -14124,6 +15830,8 @@
       <c r="L839" s="2" t="n"/>
       <c r="M839" s="2" t="n"/>
       <c r="N839" s="2" t="n"/>
+      <c r="O839" s="2" t="n"/>
+      <c r="P839" s="2" t="n"/>
     </row>
     <row r="840">
       <c r="A840" s="2" t="n"/>
@@ -14140,6 +15848,8 @@
       <c r="L840" s="2" t="n"/>
       <c r="M840" s="2" t="n"/>
       <c r="N840" s="2" t="n"/>
+      <c r="O840" s="2" t="n"/>
+      <c r="P840" s="2" t="n"/>
     </row>
     <row r="841">
       <c r="A841" s="2" t="n"/>
@@ -14156,6 +15866,8 @@
       <c r="L841" s="2" t="n"/>
       <c r="M841" s="2" t="n"/>
       <c r="N841" s="2" t="n"/>
+      <c r="O841" s="2" t="n"/>
+      <c r="P841" s="2" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="2" t="n"/>
@@ -14172,6 +15884,8 @@
       <c r="L842" s="2" t="n"/>
       <c r="M842" s="2" t="n"/>
       <c r="N842" s="2" t="n"/>
+      <c r="O842" s="2" t="n"/>
+      <c r="P842" s="2" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="2" t="n"/>
@@ -14188,6 +15902,8 @@
       <c r="L843" s="2" t="n"/>
       <c r="M843" s="2" t="n"/>
       <c r="N843" s="2" t="n"/>
+      <c r="O843" s="2" t="n"/>
+      <c r="P843" s="2" t="n"/>
     </row>
     <row r="844">
       <c r="A844" s="2" t="n"/>
@@ -14204,6 +15920,8 @@
       <c r="L844" s="2" t="n"/>
       <c r="M844" s="2" t="n"/>
       <c r="N844" s="2" t="n"/>
+      <c r="O844" s="2" t="n"/>
+      <c r="P844" s="2" t="n"/>
     </row>
     <row r="845">
       <c r="A845" s="2" t="n"/>
@@ -14220,6 +15938,8 @@
       <c r="L845" s="2" t="n"/>
       <c r="M845" s="2" t="n"/>
       <c r="N845" s="2" t="n"/>
+      <c r="O845" s="2" t="n"/>
+      <c r="P845" s="2" t="n"/>
     </row>
     <row r="846">
       <c r="A846" s="2" t="n"/>
@@ -14236,6 +15956,8 @@
       <c r="L846" s="2" t="n"/>
       <c r="M846" s="2" t="n"/>
       <c r="N846" s="2" t="n"/>
+      <c r="O846" s="2" t="n"/>
+      <c r="P846" s="2" t="n"/>
     </row>
     <row r="847">
       <c r="A847" s="2" t="n"/>
@@ -14252,6 +15974,8 @@
       <c r="L847" s="2" t="n"/>
       <c r="M847" s="2" t="n"/>
       <c r="N847" s="2" t="n"/>
+      <c r="O847" s="2" t="n"/>
+      <c r="P847" s="2" t="n"/>
     </row>
     <row r="848">
       <c r="A848" s="2" t="n"/>
@@ -14268,6 +15992,8 @@
       <c r="L848" s="2" t="n"/>
       <c r="M848" s="2" t="n"/>
       <c r="N848" s="2" t="n"/>
+      <c r="O848" s="2" t="n"/>
+      <c r="P848" s="2" t="n"/>
     </row>
     <row r="849">
       <c r="A849" s="2" t="n"/>
@@ -14284,6 +16010,8 @@
       <c r="L849" s="2" t="n"/>
       <c r="M849" s="2" t="n"/>
       <c r="N849" s="2" t="n"/>
+      <c r="O849" s="2" t="n"/>
+      <c r="P849" s="2" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="2" t="n"/>
@@ -14300,6 +16028,8 @@
       <c r="L850" s="2" t="n"/>
       <c r="M850" s="2" t="n"/>
       <c r="N850" s="2" t="n"/>
+      <c r="O850" s="2" t="n"/>
+      <c r="P850" s="2" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="2" t="n"/>
@@ -14316,6 +16046,8 @@
       <c r="L851" s="2" t="n"/>
       <c r="M851" s="2" t="n"/>
       <c r="N851" s="2" t="n"/>
+      <c r="O851" s="2" t="n"/>
+      <c r="P851" s="2" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="2" t="n"/>
@@ -14332,6 +16064,8 @@
       <c r="L852" s="2" t="n"/>
       <c r="M852" s="2" t="n"/>
       <c r="N852" s="2" t="n"/>
+      <c r="O852" s="2" t="n"/>
+      <c r="P852" s="2" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="2" t="n"/>
@@ -14348,6 +16082,8 @@
       <c r="L853" s="2" t="n"/>
       <c r="M853" s="2" t="n"/>
       <c r="N853" s="2" t="n"/>
+      <c r="O853" s="2" t="n"/>
+      <c r="P853" s="2" t="n"/>
     </row>
     <row r="854">
       <c r="A854" s="2" t="n"/>
@@ -14364,6 +16100,8 @@
       <c r="L854" s="2" t="n"/>
       <c r="M854" s="2" t="n"/>
       <c r="N854" s="2" t="n"/>
+      <c r="O854" s="2" t="n"/>
+      <c r="P854" s="2" t="n"/>
     </row>
     <row r="855">
       <c r="A855" s="2" t="n"/>
@@ -14380,6 +16118,8 @@
       <c r="L855" s="2" t="n"/>
       <c r="M855" s="2" t="n"/>
       <c r="N855" s="2" t="n"/>
+      <c r="O855" s="2" t="n"/>
+      <c r="P855" s="2" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="2" t="n"/>
@@ -14396,6 +16136,8 @@
       <c r="L856" s="2" t="n"/>
       <c r="M856" s="2" t="n"/>
       <c r="N856" s="2" t="n"/>
+      <c r="O856" s="2" t="n"/>
+      <c r="P856" s="2" t="n"/>
     </row>
     <row r="857">
       <c r="A857" s="2" t="n"/>
@@ -14412,6 +16154,8 @@
       <c r="L857" s="2" t="n"/>
       <c r="M857" s="2" t="n"/>
       <c r="N857" s="2" t="n"/>
+      <c r="O857" s="2" t="n"/>
+      <c r="P857" s="2" t="n"/>
     </row>
     <row r="858">
       <c r="A858" s="2" t="n"/>
@@ -14428,6 +16172,8 @@
       <c r="L858" s="2" t="n"/>
       <c r="M858" s="2" t="n"/>
       <c r="N858" s="2" t="n"/>
+      <c r="O858" s="2" t="n"/>
+      <c r="P858" s="2" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="2" t="n"/>
@@ -14444,6 +16190,8 @@
       <c r="L859" s="2" t="n"/>
       <c r="M859" s="2" t="n"/>
       <c r="N859" s="2" t="n"/>
+      <c r="O859" s="2" t="n"/>
+      <c r="P859" s="2" t="n"/>
     </row>
     <row r="860">
       <c r="A860" s="2" t="n"/>
@@ -14460,6 +16208,8 @@
       <c r="L860" s="2" t="n"/>
       <c r="M860" s="2" t="n"/>
       <c r="N860" s="2" t="n"/>
+      <c r="O860" s="2" t="n"/>
+      <c r="P860" s="2" t="n"/>
     </row>
     <row r="861">
       <c r="A861" s="2" t="n"/>
@@ -14476,6 +16226,8 @@
       <c r="L861" s="2" t="n"/>
       <c r="M861" s="2" t="n"/>
       <c r="N861" s="2" t="n"/>
+      <c r="O861" s="2" t="n"/>
+      <c r="P861" s="2" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="2" t="n"/>
@@ -14492,6 +16244,8 @@
       <c r="L862" s="2" t="n"/>
       <c r="M862" s="2" t="n"/>
       <c r="N862" s="2" t="n"/>
+      <c r="O862" s="2" t="n"/>
+      <c r="P862" s="2" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="2" t="n"/>
@@ -14508,6 +16262,8 @@
       <c r="L863" s="2" t="n"/>
       <c r="M863" s="2" t="n"/>
       <c r="N863" s="2" t="n"/>
+      <c r="O863" s="2" t="n"/>
+      <c r="P863" s="2" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="2" t="n"/>
@@ -14524,6 +16280,8 @@
       <c r="L864" s="2" t="n"/>
       <c r="M864" s="2" t="n"/>
       <c r="N864" s="2" t="n"/>
+      <c r="O864" s="2" t="n"/>
+      <c r="P864" s="2" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="2" t="n"/>
@@ -14540,6 +16298,8 @@
       <c r="L865" s="2" t="n"/>
       <c r="M865" s="2" t="n"/>
       <c r="N865" s="2" t="n"/>
+      <c r="O865" s="2" t="n"/>
+      <c r="P865" s="2" t="n"/>
     </row>
     <row r="866">
       <c r="A866" s="2" t="n"/>
@@ -14556,6 +16316,8 @@
       <c r="L866" s="2" t="n"/>
       <c r="M866" s="2" t="n"/>
       <c r="N866" s="2" t="n"/>
+      <c r="O866" s="2" t="n"/>
+      <c r="P866" s="2" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="2" t="n"/>
@@ -14572,6 +16334,8 @@
       <c r="L867" s="2" t="n"/>
       <c r="M867" s="2" t="n"/>
       <c r="N867" s="2" t="n"/>
+      <c r="O867" s="2" t="n"/>
+      <c r="P867" s="2" t="n"/>
     </row>
     <row r="868">
       <c r="A868" s="2" t="n"/>
@@ -14588,6 +16352,8 @@
       <c r="L868" s="2" t="n"/>
       <c r="M868" s="2" t="n"/>
       <c r="N868" s="2" t="n"/>
+      <c r="O868" s="2" t="n"/>
+      <c r="P868" s="2" t="n"/>
     </row>
     <row r="869">
       <c r="A869" s="2" t="n"/>
@@ -14604,6 +16370,8 @@
       <c r="L869" s="2" t="n"/>
       <c r="M869" s="2" t="n"/>
       <c r="N869" s="2" t="n"/>
+      <c r="O869" s="2" t="n"/>
+      <c r="P869" s="2" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="2" t="n"/>
@@ -14620,6 +16388,8 @@
       <c r="L870" s="2" t="n"/>
       <c r="M870" s="2" t="n"/>
       <c r="N870" s="2" t="n"/>
+      <c r="O870" s="2" t="n"/>
+      <c r="P870" s="2" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="2" t="n"/>
@@ -14636,6 +16406,8 @@
       <c r="L871" s="2" t="n"/>
       <c r="M871" s="2" t="n"/>
       <c r="N871" s="2" t="n"/>
+      <c r="O871" s="2" t="n"/>
+      <c r="P871" s="2" t="n"/>
     </row>
     <row r="872">
       <c r="A872" s="2" t="n"/>
@@ -14652,6 +16424,8 @@
       <c r="L872" s="2" t="n"/>
       <c r="M872" s="2" t="n"/>
       <c r="N872" s="2" t="n"/>
+      <c r="O872" s="2" t="n"/>
+      <c r="P872" s="2" t="n"/>
     </row>
     <row r="873">
       <c r="A873" s="2" t="n"/>
@@ -14668,6 +16442,8 @@
       <c r="L873" s="2" t="n"/>
       <c r="M873" s="2" t="n"/>
       <c r="N873" s="2" t="n"/>
+      <c r="O873" s="2" t="n"/>
+      <c r="P873" s="2" t="n"/>
     </row>
     <row r="874">
       <c r="A874" s="2" t="n"/>
@@ -14684,6 +16460,8 @@
       <c r="L874" s="2" t="n"/>
       <c r="M874" s="2" t="n"/>
       <c r="N874" s="2" t="n"/>
+      <c r="O874" s="2" t="n"/>
+      <c r="P874" s="2" t="n"/>
     </row>
     <row r="875">
       <c r="A875" s="2" t="n"/>
@@ -14700,6 +16478,8 @@
       <c r="L875" s="2" t="n"/>
       <c r="M875" s="2" t="n"/>
       <c r="N875" s="2" t="n"/>
+      <c r="O875" s="2" t="n"/>
+      <c r="P875" s="2" t="n"/>
     </row>
     <row r="876">
       <c r="A876" s="2" t="n"/>
@@ -14716,6 +16496,8 @@
       <c r="L876" s="2" t="n"/>
       <c r="M876" s="2" t="n"/>
       <c r="N876" s="2" t="n"/>
+      <c r="O876" s="2" t="n"/>
+      <c r="P876" s="2" t="n"/>
     </row>
     <row r="877">
       <c r="A877" s="2" t="n"/>
@@ -14732,6 +16514,8 @@
       <c r="L877" s="2" t="n"/>
       <c r="M877" s="2" t="n"/>
       <c r="N877" s="2" t="n"/>
+      <c r="O877" s="2" t="n"/>
+      <c r="P877" s="2" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="2" t="n"/>
@@ -14748,6 +16532,8 @@
       <c r="L878" s="2" t="n"/>
       <c r="M878" s="2" t="n"/>
       <c r="N878" s="2" t="n"/>
+      <c r="O878" s="2" t="n"/>
+      <c r="P878" s="2" t="n"/>
     </row>
     <row r="879">
       <c r="A879" s="2" t="n"/>
@@ -14764,6 +16550,8 @@
       <c r="L879" s="2" t="n"/>
       <c r="M879" s="2" t="n"/>
       <c r="N879" s="2" t="n"/>
+      <c r="O879" s="2" t="n"/>
+      <c r="P879" s="2" t="n"/>
     </row>
     <row r="880">
       <c r="A880" s="2" t="n"/>
@@ -14780,6 +16568,8 @@
       <c r="L880" s="2" t="n"/>
       <c r="M880" s="2" t="n"/>
       <c r="N880" s="2" t="n"/>
+      <c r="O880" s="2" t="n"/>
+      <c r="P880" s="2" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="2" t="n"/>
@@ -14796,6 +16586,8 @@
       <c r="L881" s="2" t="n"/>
       <c r="M881" s="2" t="n"/>
       <c r="N881" s="2" t="n"/>
+      <c r="O881" s="2" t="n"/>
+      <c r="P881" s="2" t="n"/>
     </row>
     <row r="882">
       <c r="A882" s="2" t="n"/>
@@ -14812,6 +16604,8 @@
       <c r="L882" s="2" t="n"/>
       <c r="M882" s="2" t="n"/>
       <c r="N882" s="2" t="n"/>
+      <c r="O882" s="2" t="n"/>
+      <c r="P882" s="2" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="2" t="n"/>
@@ -14828,6 +16622,8 @@
       <c r="L883" s="2" t="n"/>
       <c r="M883" s="2" t="n"/>
       <c r="N883" s="2" t="n"/>
+      <c r="O883" s="2" t="n"/>
+      <c r="P883" s="2" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="2" t="n"/>
@@ -14844,6 +16640,8 @@
       <c r="L884" s="2" t="n"/>
       <c r="M884" s="2" t="n"/>
       <c r="N884" s="2" t="n"/>
+      <c r="O884" s="2" t="n"/>
+      <c r="P884" s="2" t="n"/>
     </row>
     <row r="885">
       <c r="A885" s="2" t="n"/>
@@ -14860,6 +16658,8 @@
       <c r="L885" s="2" t="n"/>
       <c r="M885" s="2" t="n"/>
       <c r="N885" s="2" t="n"/>
+      <c r="O885" s="2" t="n"/>
+      <c r="P885" s="2" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="2" t="n"/>
@@ -14876,6 +16676,8 @@
       <c r="L886" s="2" t="n"/>
       <c r="M886" s="2" t="n"/>
       <c r="N886" s="2" t="n"/>
+      <c r="O886" s="2" t="n"/>
+      <c r="P886" s="2" t="n"/>
     </row>
     <row r="887">
       <c r="A887" s="2" t="n"/>
@@ -14892,6 +16694,8 @@
       <c r="L887" s="2" t="n"/>
       <c r="M887" s="2" t="n"/>
       <c r="N887" s="2" t="n"/>
+      <c r="O887" s="2" t="n"/>
+      <c r="P887" s="2" t="n"/>
     </row>
     <row r="888">
       <c r="A888" s="2" t="n"/>
@@ -14908,6 +16712,8 @@
       <c r="L888" s="2" t="n"/>
       <c r="M888" s="2" t="n"/>
       <c r="N888" s="2" t="n"/>
+      <c r="O888" s="2" t="n"/>
+      <c r="P888" s="2" t="n"/>
     </row>
     <row r="889">
       <c r="A889" s="2" t="n"/>
@@ -14924,6 +16730,8 @@
       <c r="L889" s="2" t="n"/>
       <c r="M889" s="2" t="n"/>
       <c r="N889" s="2" t="n"/>
+      <c r="O889" s="2" t="n"/>
+      <c r="P889" s="2" t="n"/>
     </row>
     <row r="890">
       <c r="A890" s="2" t="n"/>
@@ -14940,6 +16748,8 @@
       <c r="L890" s="2" t="n"/>
       <c r="M890" s="2" t="n"/>
       <c r="N890" s="2" t="n"/>
+      <c r="O890" s="2" t="n"/>
+      <c r="P890" s="2" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="2" t="n"/>
@@ -14956,6 +16766,8 @@
       <c r="L891" s="2" t="n"/>
       <c r="M891" s="2" t="n"/>
       <c r="N891" s="2" t="n"/>
+      <c r="O891" s="2" t="n"/>
+      <c r="P891" s="2" t="n"/>
     </row>
     <row r="892">
       <c r="A892" s="2" t="n"/>
@@ -14972,6 +16784,8 @@
       <c r="L892" s="2" t="n"/>
       <c r="M892" s="2" t="n"/>
       <c r="N892" s="2" t="n"/>
+      <c r="O892" s="2" t="n"/>
+      <c r="P892" s="2" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="2" t="n"/>
@@ -14988,6 +16802,8 @@
       <c r="L893" s="2" t="n"/>
       <c r="M893" s="2" t="n"/>
       <c r="N893" s="2" t="n"/>
+      <c r="O893" s="2" t="n"/>
+      <c r="P893" s="2" t="n"/>
     </row>
     <row r="894">
       <c r="A894" s="2" t="n"/>
@@ -15004,6 +16820,8 @@
       <c r="L894" s="2" t="n"/>
       <c r="M894" s="2" t="n"/>
       <c r="N894" s="2" t="n"/>
+      <c r="O894" s="2" t="n"/>
+      <c r="P894" s="2" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="2" t="n"/>
@@ -15020,6 +16838,8 @@
       <c r="L895" s="2" t="n"/>
       <c r="M895" s="2" t="n"/>
       <c r="N895" s="2" t="n"/>
+      <c r="O895" s="2" t="n"/>
+      <c r="P895" s="2" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="2" t="n"/>
@@ -15036,6 +16856,8 @@
       <c r="L896" s="2" t="n"/>
       <c r="M896" s="2" t="n"/>
       <c r="N896" s="2" t="n"/>
+      <c r="O896" s="2" t="n"/>
+      <c r="P896" s="2" t="n"/>
     </row>
     <row r="897">
       <c r="A897" s="2" t="n"/>
@@ -15052,6 +16874,8 @@
       <c r="L897" s="2" t="n"/>
       <c r="M897" s="2" t="n"/>
       <c r="N897" s="2" t="n"/>
+      <c r="O897" s="2" t="n"/>
+      <c r="P897" s="2" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="2" t="n"/>
@@ -15068,6 +16892,8 @@
       <c r="L898" s="2" t="n"/>
       <c r="M898" s="2" t="n"/>
       <c r="N898" s="2" t="n"/>
+      <c r="O898" s="2" t="n"/>
+      <c r="P898" s="2" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="2" t="n"/>
@@ -15084,6 +16910,8 @@
       <c r="L899" s="2" t="n"/>
       <c r="M899" s="2" t="n"/>
       <c r="N899" s="2" t="n"/>
+      <c r="O899" s="2" t="n"/>
+      <c r="P899" s="2" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="2" t="n"/>
@@ -15100,6 +16928,8 @@
       <c r="L900" s="2" t="n"/>
       <c r="M900" s="2" t="n"/>
       <c r="N900" s="2" t="n"/>
+      <c r="O900" s="2" t="n"/>
+      <c r="P900" s="2" t="n"/>
     </row>
     <row r="901">
       <c r="A901" s="2" t="n"/>
@@ -15116,6 +16946,8 @@
       <c r="L901" s="2" t="n"/>
       <c r="M901" s="2" t="n"/>
       <c r="N901" s="2" t="n"/>
+      <c r="O901" s="2" t="n"/>
+      <c r="P901" s="2" t="n"/>
     </row>
     <row r="902">
       <c r="A902" s="2" t="n"/>
@@ -15132,6 +16964,8 @@
       <c r="L902" s="2" t="n"/>
       <c r="M902" s="2" t="n"/>
       <c r="N902" s="2" t="n"/>
+      <c r="O902" s="2" t="n"/>
+      <c r="P902" s="2" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="2" t="n"/>
@@ -15148,6 +16982,8 @@
       <c r="L903" s="2" t="n"/>
       <c r="M903" s="2" t="n"/>
       <c r="N903" s="2" t="n"/>
+      <c r="O903" s="2" t="n"/>
+      <c r="P903" s="2" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="2" t="n"/>
@@ -15164,6 +17000,8 @@
       <c r="L904" s="2" t="n"/>
       <c r="M904" s="2" t="n"/>
       <c r="N904" s="2" t="n"/>
+      <c r="O904" s="2" t="n"/>
+      <c r="P904" s="2" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="2" t="n"/>
@@ -15180,6 +17018,8 @@
       <c r="L905" s="2" t="n"/>
       <c r="M905" s="2" t="n"/>
       <c r="N905" s="2" t="n"/>
+      <c r="O905" s="2" t="n"/>
+      <c r="P905" s="2" t="n"/>
     </row>
     <row r="906">
       <c r="A906" s="2" t="n"/>
@@ -15196,6 +17036,8 @@
       <c r="L906" s="2" t="n"/>
       <c r="M906" s="2" t="n"/>
       <c r="N906" s="2" t="n"/>
+      <c r="O906" s="2" t="n"/>
+      <c r="P906" s="2" t="n"/>
     </row>
     <row r="907">
       <c r="A907" s="2" t="n"/>
@@ -15212,6 +17054,8 @@
       <c r="L907" s="2" t="n"/>
       <c r="M907" s="2" t="n"/>
       <c r="N907" s="2" t="n"/>
+      <c r="O907" s="2" t="n"/>
+      <c r="P907" s="2" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="2" t="n"/>
@@ -15228,6 +17072,8 @@
       <c r="L908" s="2" t="n"/>
       <c r="M908" s="2" t="n"/>
       <c r="N908" s="2" t="n"/>
+      <c r="O908" s="2" t="n"/>
+      <c r="P908" s="2" t="n"/>
     </row>
     <row r="909">
       <c r="A909" s="2" t="n"/>
@@ -15244,6 +17090,8 @@
       <c r="L909" s="2" t="n"/>
       <c r="M909" s="2" t="n"/>
       <c r="N909" s="2" t="n"/>
+      <c r="O909" s="2" t="n"/>
+      <c r="P909" s="2" t="n"/>
     </row>
     <row r="910">
       <c r="A910" s="2" t="n"/>
@@ -15260,6 +17108,8 @@
       <c r="L910" s="2" t="n"/>
       <c r="M910" s="2" t="n"/>
       <c r="N910" s="2" t="n"/>
+      <c r="O910" s="2" t="n"/>
+      <c r="P910" s="2" t="n"/>
     </row>
     <row r="911">
       <c r="A911" s="2" t="n"/>
@@ -15276,6 +17126,8 @@
       <c r="L911" s="2" t="n"/>
       <c r="M911" s="2" t="n"/>
       <c r="N911" s="2" t="n"/>
+      <c r="O911" s="2" t="n"/>
+      <c r="P911" s="2" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="2" t="n"/>
@@ -15292,6 +17144,8 @@
       <c r="L912" s="2" t="n"/>
       <c r="M912" s="2" t="n"/>
       <c r="N912" s="2" t="n"/>
+      <c r="O912" s="2" t="n"/>
+      <c r="P912" s="2" t="n"/>
     </row>
     <row r="913">
       <c r="A913" s="2" t="n"/>
@@ -15308,6 +17162,8 @@
       <c r="L913" s="2" t="n"/>
       <c r="M913" s="2" t="n"/>
       <c r="N913" s="2" t="n"/>
+      <c r="O913" s="2" t="n"/>
+      <c r="P913" s="2" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="2" t="n"/>
@@ -15324,6 +17180,8 @@
       <c r="L914" s="2" t="n"/>
       <c r="M914" s="2" t="n"/>
       <c r="N914" s="2" t="n"/>
+      <c r="O914" s="2" t="n"/>
+      <c r="P914" s="2" t="n"/>
     </row>
     <row r="915">
       <c r="A915" s="2" t="n"/>
@@ -15340,6 +17198,8 @@
       <c r="L915" s="2" t="n"/>
       <c r="M915" s="2" t="n"/>
       <c r="N915" s="2" t="n"/>
+      <c r="O915" s="2" t="n"/>
+      <c r="P915" s="2" t="n"/>
     </row>
     <row r="916">
       <c r="A916" s="2" t="n"/>
@@ -15356,6 +17216,8 @@
       <c r="L916" s="2" t="n"/>
       <c r="M916" s="2" t="n"/>
       <c r="N916" s="2" t="n"/>
+      <c r="O916" s="2" t="n"/>
+      <c r="P916" s="2" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="2" t="n"/>
@@ -15372,6 +17234,8 @@
       <c r="L917" s="2" t="n"/>
       <c r="M917" s="2" t="n"/>
       <c r="N917" s="2" t="n"/>
+      <c r="O917" s="2" t="n"/>
+      <c r="P917" s="2" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="2" t="n"/>
@@ -15388,6 +17252,8 @@
       <c r="L918" s="2" t="n"/>
       <c r="M918" s="2" t="n"/>
       <c r="N918" s="2" t="n"/>
+      <c r="O918" s="2" t="n"/>
+      <c r="P918" s="2" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="2" t="n"/>
@@ -15404,6 +17270,8 @@
       <c r="L919" s="2" t="n"/>
       <c r="M919" s="2" t="n"/>
       <c r="N919" s="2" t="n"/>
+      <c r="O919" s="2" t="n"/>
+      <c r="P919" s="2" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="2" t="n"/>
@@ -15420,6 +17288,8 @@
       <c r="L920" s="2" t="n"/>
       <c r="M920" s="2" t="n"/>
       <c r="N920" s="2" t="n"/>
+      <c r="O920" s="2" t="n"/>
+      <c r="P920" s="2" t="n"/>
     </row>
     <row r="921">
       <c r="A921" s="2" t="n"/>
@@ -15436,6 +17306,8 @@
       <c r="L921" s="2" t="n"/>
       <c r="M921" s="2" t="n"/>
       <c r="N921" s="2" t="n"/>
+      <c r="O921" s="2" t="n"/>
+      <c r="P921" s="2" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="2" t="n"/>
@@ -15452,6 +17324,8 @@
       <c r="L922" s="2" t="n"/>
       <c r="M922" s="2" t="n"/>
       <c r="N922" s="2" t="n"/>
+      <c r="O922" s="2" t="n"/>
+      <c r="P922" s="2" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="2" t="n"/>
@@ -15468,6 +17342,8 @@
       <c r="L923" s="2" t="n"/>
       <c r="M923" s="2" t="n"/>
       <c r="N923" s="2" t="n"/>
+      <c r="O923" s="2" t="n"/>
+      <c r="P923" s="2" t="n"/>
     </row>
     <row r="924">
       <c r="A924" s="2" t="n"/>
@@ -15484,6 +17360,8 @@
       <c r="L924" s="2" t="n"/>
       <c r="M924" s="2" t="n"/>
       <c r="N924" s="2" t="n"/>
+      <c r="O924" s="2" t="n"/>
+      <c r="P924" s="2" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="2" t="n"/>
@@ -15500,6 +17378,8 @@
       <c r="L925" s="2" t="n"/>
       <c r="M925" s="2" t="n"/>
       <c r="N925" s="2" t="n"/>
+      <c r="O925" s="2" t="n"/>
+      <c r="P925" s="2" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="2" t="n"/>
@@ -15516,6 +17396,8 @@
       <c r="L926" s="2" t="n"/>
       <c r="M926" s="2" t="n"/>
       <c r="N926" s="2" t="n"/>
+      <c r="O926" s="2" t="n"/>
+      <c r="P926" s="2" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="2" t="n"/>
@@ -15532,6 +17414,8 @@
       <c r="L927" s="2" t="n"/>
       <c r="M927" s="2" t="n"/>
       <c r="N927" s="2" t="n"/>
+      <c r="O927" s="2" t="n"/>
+      <c r="P927" s="2" t="n"/>
     </row>
     <row r="928">
       <c r="A928" s="2" t="n"/>
@@ -15548,6 +17432,8 @@
       <c r="L928" s="2" t="n"/>
       <c r="M928" s="2" t="n"/>
       <c r="N928" s="2" t="n"/>
+      <c r="O928" s="2" t="n"/>
+      <c r="P928" s="2" t="n"/>
     </row>
     <row r="929">
       <c r="A929" s="2" t="n"/>
@@ -15564,6 +17450,8 @@
       <c r="L929" s="2" t="n"/>
       <c r="M929" s="2" t="n"/>
       <c r="N929" s="2" t="n"/>
+      <c r="O929" s="2" t="n"/>
+      <c r="P929" s="2" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="2" t="n"/>
@@ -15580,6 +17468,8 @@
       <c r="L930" s="2" t="n"/>
       <c r="M930" s="2" t="n"/>
       <c r="N930" s="2" t="n"/>
+      <c r="O930" s="2" t="n"/>
+      <c r="P930" s="2" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="2" t="n"/>
@@ -15596,6 +17486,8 @@
       <c r="L931" s="2" t="n"/>
       <c r="M931" s="2" t="n"/>
       <c r="N931" s="2" t="n"/>
+      <c r="O931" s="2" t="n"/>
+      <c r="P931" s="2" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="2" t="n"/>
@@ -15612,6 +17504,8 @@
       <c r="L932" s="2" t="n"/>
       <c r="M932" s="2" t="n"/>
       <c r="N932" s="2" t="n"/>
+      <c r="O932" s="2" t="n"/>
+      <c r="P932" s="2" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="2" t="n"/>
@@ -15628,6 +17522,8 @@
       <c r="L933" s="2" t="n"/>
       <c r="M933" s="2" t="n"/>
       <c r="N933" s="2" t="n"/>
+      <c r="O933" s="2" t="n"/>
+      <c r="P933" s="2" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="2" t="n"/>
@@ -15644,6 +17540,8 @@
       <c r="L934" s="2" t="n"/>
       <c r="M934" s="2" t="n"/>
       <c r="N934" s="2" t="n"/>
+      <c r="O934" s="2" t="n"/>
+      <c r="P934" s="2" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="2" t="n"/>
@@ -15660,6 +17558,8 @@
       <c r="L935" s="2" t="n"/>
       <c r="M935" s="2" t="n"/>
       <c r="N935" s="2" t="n"/>
+      <c r="O935" s="2" t="n"/>
+      <c r="P935" s="2" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="2" t="n"/>
@@ -15676,6 +17576,8 @@
       <c r="L936" s="2" t="n"/>
       <c r="M936" s="2" t="n"/>
       <c r="N936" s="2" t="n"/>
+      <c r="O936" s="2" t="n"/>
+      <c r="P936" s="2" t="n"/>
     </row>
     <row r="937">
       <c r="A937" s="2" t="n"/>
@@ -15692,6 +17594,8 @@
       <c r="L937" s="2" t="n"/>
       <c r="M937" s="2" t="n"/>
       <c r="N937" s="2" t="n"/>
+      <c r="O937" s="2" t="n"/>
+      <c r="P937" s="2" t="n"/>
     </row>
     <row r="938">
       <c r="A938" s="2" t="n"/>
@@ -15708,6 +17612,8 @@
       <c r="L938" s="2" t="n"/>
       <c r="M938" s="2" t="n"/>
       <c r="N938" s="2" t="n"/>
+      <c r="O938" s="2" t="n"/>
+      <c r="P938" s="2" t="n"/>
     </row>
     <row r="939">
       <c r="A939" s="2" t="n"/>
@@ -15724,6 +17630,8 @@
       <c r="L939" s="2" t="n"/>
       <c r="M939" s="2" t="n"/>
       <c r="N939" s="2" t="n"/>
+      <c r="O939" s="2" t="n"/>
+      <c r="P939" s="2" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="2" t="n"/>
@@ -15740,6 +17648,8 @@
       <c r="L940" s="2" t="n"/>
       <c r="M940" s="2" t="n"/>
       <c r="N940" s="2" t="n"/>
+      <c r="O940" s="2" t="n"/>
+      <c r="P940" s="2" t="n"/>
     </row>
     <row r="941">
       <c r="A941" s="2" t="n"/>
@@ -15756,6 +17666,8 @@
       <c r="L941" s="2" t="n"/>
       <c r="M941" s="2" t="n"/>
       <c r="N941" s="2" t="n"/>
+      <c r="O941" s="2" t="n"/>
+      <c r="P941" s="2" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="2" t="n"/>
@@ -15772,6 +17684,8 @@
       <c r="L942" s="2" t="n"/>
       <c r="M942" s="2" t="n"/>
       <c r="N942" s="2" t="n"/>
+      <c r="O942" s="2" t="n"/>
+      <c r="P942" s="2" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="2" t="n"/>
@@ -15788,6 +17702,8 @@
       <c r="L943" s="2" t="n"/>
       <c r="M943" s="2" t="n"/>
       <c r="N943" s="2" t="n"/>
+      <c r="O943" s="2" t="n"/>
+      <c r="P943" s="2" t="n"/>
     </row>
     <row r="944">
       <c r="A944" s="2" t="n"/>
@@ -15804,6 +17720,8 @@
       <c r="L944" s="2" t="n"/>
       <c r="M944" s="2" t="n"/>
       <c r="N944" s="2" t="n"/>
+      <c r="O944" s="2" t="n"/>
+      <c r="P944" s="2" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="2" t="n"/>
@@ -15820,6 +17738,8 @@
       <c r="L945" s="2" t="n"/>
       <c r="M945" s="2" t="n"/>
       <c r="N945" s="2" t="n"/>
+      <c r="O945" s="2" t="n"/>
+      <c r="P945" s="2" t="n"/>
     </row>
     <row r="946">
       <c r="A946" s="2" t="n"/>
@@ -15836,6 +17756,8 @@
       <c r="L946" s="2" t="n"/>
       <c r="M946" s="2" t="n"/>
       <c r="N946" s="2" t="n"/>
+      <c r="O946" s="2" t="n"/>
+      <c r="P946" s="2" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="2" t="n"/>
@@ -15852,6 +17774,8 @@
       <c r="L947" s="2" t="n"/>
       <c r="M947" s="2" t="n"/>
       <c r="N947" s="2" t="n"/>
+      <c r="O947" s="2" t="n"/>
+      <c r="P947" s="2" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="2" t="n"/>
@@ -15868,6 +17792,8 @@
       <c r="L948" s="2" t="n"/>
       <c r="M948" s="2" t="n"/>
       <c r="N948" s="2" t="n"/>
+      <c r="O948" s="2" t="n"/>
+      <c r="P948" s="2" t="n"/>
     </row>
     <row r="949">
       <c r="A949" s="2" t="n"/>
@@ -15884,6 +17810,8 @@
       <c r="L949" s="2" t="n"/>
       <c r="M949" s="2" t="n"/>
       <c r="N949" s="2" t="n"/>
+      <c r="O949" s="2" t="n"/>
+      <c r="P949" s="2" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="2" t="n"/>
@@ -15900,6 +17828,8 @@
       <c r="L950" s="2" t="n"/>
       <c r="M950" s="2" t="n"/>
       <c r="N950" s="2" t="n"/>
+      <c r="O950" s="2" t="n"/>
+      <c r="P950" s="2" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="2" t="n"/>
@@ -15916,6 +17846,8 @@
       <c r="L951" s="2" t="n"/>
       <c r="M951" s="2" t="n"/>
       <c r="N951" s="2" t="n"/>
+      <c r="O951" s="2" t="n"/>
+      <c r="P951" s="2" t="n"/>
     </row>
     <row r="952">
       <c r="A952" s="2" t="n"/>
@@ -15932,6 +17864,8 @@
       <c r="L952" s="2" t="n"/>
       <c r="M952" s="2" t="n"/>
       <c r="N952" s="2" t="n"/>
+      <c r="O952" s="2" t="n"/>
+      <c r="P952" s="2" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="2" t="n"/>
@@ -15948,6 +17882,8 @@
       <c r="L953" s="2" t="n"/>
       <c r="M953" s="2" t="n"/>
       <c r="N953" s="2" t="n"/>
+      <c r="O953" s="2" t="n"/>
+      <c r="P953" s="2" t="n"/>
     </row>
     <row r="954">
       <c r="A954" s="2" t="n"/>
@@ -15964,6 +17900,8 @@
       <c r="L954" s="2" t="n"/>
       <c r="M954" s="2" t="n"/>
       <c r="N954" s="2" t="n"/>
+      <c r="O954" s="2" t="n"/>
+      <c r="P954" s="2" t="n"/>
     </row>
     <row r="955">
       <c r="A955" s="2" t="n"/>
@@ -15980,6 +17918,8 @@
       <c r="L955" s="2" t="n"/>
       <c r="M955" s="2" t="n"/>
       <c r="N955" s="2" t="n"/>
+      <c r="O955" s="2" t="n"/>
+      <c r="P955" s="2" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="2" t="n"/>
@@ -15996,6 +17936,8 @@
       <c r="L956" s="2" t="n"/>
       <c r="M956" s="2" t="n"/>
       <c r="N956" s="2" t="n"/>
+      <c r="O956" s="2" t="n"/>
+      <c r="P956" s="2" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="2" t="n"/>
@@ -16012,6 +17954,8 @@
       <c r="L957" s="2" t="n"/>
       <c r="M957" s="2" t="n"/>
       <c r="N957" s="2" t="n"/>
+      <c r="O957" s="2" t="n"/>
+      <c r="P957" s="2" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="2" t="n"/>
@@ -16028,6 +17972,8 @@
       <c r="L958" s="2" t="n"/>
       <c r="M958" s="2" t="n"/>
       <c r="N958" s="2" t="n"/>
+      <c r="O958" s="2" t="n"/>
+      <c r="P958" s="2" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="2" t="n"/>
@@ -16044,6 +17990,8 @@
       <c r="L959" s="2" t="n"/>
       <c r="M959" s="2" t="n"/>
       <c r="N959" s="2" t="n"/>
+      <c r="O959" s="2" t="n"/>
+      <c r="P959" s="2" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="2" t="n"/>
@@ -16060,6 +18008,8 @@
       <c r="L960" s="2" t="n"/>
       <c r="M960" s="2" t="n"/>
       <c r="N960" s="2" t="n"/>
+      <c r="O960" s="2" t="n"/>
+      <c r="P960" s="2" t="n"/>
     </row>
     <row r="961">
       <c r="A961" s="2" t="n"/>
@@ -16076,6 +18026,8 @@
       <c r="L961" s="2" t="n"/>
       <c r="M961" s="2" t="n"/>
       <c r="N961" s="2" t="n"/>
+      <c r="O961" s="2" t="n"/>
+      <c r="P961" s="2" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="2" t="n"/>
@@ -16092,6 +18044,8 @@
       <c r="L962" s="2" t="n"/>
       <c r="M962" s="2" t="n"/>
       <c r="N962" s="2" t="n"/>
+      <c r="O962" s="2" t="n"/>
+      <c r="P962" s="2" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="2" t="n"/>
@@ -16108,6 +18062,8 @@
       <c r="L963" s="2" t="n"/>
       <c r="M963" s="2" t="n"/>
       <c r="N963" s="2" t="n"/>
+      <c r="O963" s="2" t="n"/>
+      <c r="P963" s="2" t="n"/>
     </row>
     <row r="964">
       <c r="A964" s="2" t="n"/>
@@ -16124,6 +18080,8 @@
       <c r="L964" s="2" t="n"/>
       <c r="M964" s="2" t="n"/>
       <c r="N964" s="2" t="n"/>
+      <c r="O964" s="2" t="n"/>
+      <c r="P964" s="2" t="n"/>
     </row>
     <row r="965">
       <c r="A965" s="2" t="n"/>
@@ -16140,6 +18098,8 @@
       <c r="L965" s="2" t="n"/>
       <c r="M965" s="2" t="n"/>
       <c r="N965" s="2" t="n"/>
+      <c r="O965" s="2" t="n"/>
+      <c r="P965" s="2" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="2" t="n"/>
@@ -16156,6 +18116,8 @@
       <c r="L966" s="2" t="n"/>
       <c r="M966" s="2" t="n"/>
       <c r="N966" s="2" t="n"/>
+      <c r="O966" s="2" t="n"/>
+      <c r="P966" s="2" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="2" t="n"/>
@@ -16172,6 +18134,8 @@
       <c r="L967" s="2" t="n"/>
       <c r="M967" s="2" t="n"/>
       <c r="N967" s="2" t="n"/>
+      <c r="O967" s="2" t="n"/>
+      <c r="P967" s="2" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="2" t="n"/>
@@ -16188,6 +18152,8 @@
       <c r="L968" s="2" t="n"/>
       <c r="M968" s="2" t="n"/>
       <c r="N968" s="2" t="n"/>
+      <c r="O968" s="2" t="n"/>
+      <c r="P968" s="2" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="2" t="n"/>
@@ -16204,6 +18170,8 @@
       <c r="L969" s="2" t="n"/>
       <c r="M969" s="2" t="n"/>
       <c r="N969" s="2" t="n"/>
+      <c r="O969" s="2" t="n"/>
+      <c r="P969" s="2" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="2" t="n"/>
@@ -16220,6 +18188,8 @@
       <c r="L970" s="2" t="n"/>
       <c r="M970" s="2" t="n"/>
       <c r="N970" s="2" t="n"/>
+      <c r="O970" s="2" t="n"/>
+      <c r="P970" s="2" t="n"/>
     </row>
     <row r="971">
       <c r="A971" s="2" t="n"/>
@@ -16236,6 +18206,8 @@
       <c r="L971" s="2" t="n"/>
       <c r="M971" s="2" t="n"/>
       <c r="N971" s="2" t="n"/>
+      <c r="O971" s="2" t="n"/>
+      <c r="P971" s="2" t="n"/>
     </row>
     <row r="972">
       <c r="A972" s="2" t="n"/>
@@ -16252,6 +18224,8 @@
       <c r="L972" s="2" t="n"/>
       <c r="M972" s="2" t="n"/>
       <c r="N972" s="2" t="n"/>
+      <c r="O972" s="2" t="n"/>
+      <c r="P972" s="2" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="2" t="n"/>
@@ -16268,6 +18242,8 @@
       <c r="L973" s="2" t="n"/>
       <c r="M973" s="2" t="n"/>
       <c r="N973" s="2" t="n"/>
+      <c r="O973" s="2" t="n"/>
+      <c r="P973" s="2" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="2" t="n"/>
@@ -16284,6 +18260,8 @@
       <c r="L974" s="2" t="n"/>
       <c r="M974" s="2" t="n"/>
       <c r="N974" s="2" t="n"/>
+      <c r="O974" s="2" t="n"/>
+      <c r="P974" s="2" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="2" t="n"/>
@@ -16300,6 +18278,8 @@
       <c r="L975" s="2" t="n"/>
       <c r="M975" s="2" t="n"/>
       <c r="N975" s="2" t="n"/>
+      <c r="O975" s="2" t="n"/>
+      <c r="P975" s="2" t="n"/>
     </row>
     <row r="976">
       <c r="A976" s="2" t="n"/>
@@ -16316,6 +18296,8 @@
       <c r="L976" s="2" t="n"/>
       <c r="M976" s="2" t="n"/>
       <c r="N976" s="2" t="n"/>
+      <c r="O976" s="2" t="n"/>
+      <c r="P976" s="2" t="n"/>
     </row>
     <row r="977">
       <c r="A977" s="2" t="n"/>
@@ -16332,6 +18314,8 @@
       <c r="L977" s="2" t="n"/>
       <c r="M977" s="2" t="n"/>
       <c r="N977" s="2" t="n"/>
+      <c r="O977" s="2" t="n"/>
+      <c r="P977" s="2" t="n"/>
     </row>
     <row r="978">
       <c r="A978" s="2" t="n"/>
@@ -16348,6 +18332,8 @@
       <c r="L978" s="2" t="n"/>
       <c r="M978" s="2" t="n"/>
       <c r="N978" s="2" t="n"/>
+      <c r="O978" s="2" t="n"/>
+      <c r="P978" s="2" t="n"/>
     </row>
     <row r="979">
       <c r="A979" s="2" t="n"/>
@@ -16364,6 +18350,8 @@
       <c r="L979" s="2" t="n"/>
       <c r="M979" s="2" t="n"/>
       <c r="N979" s="2" t="n"/>
+      <c r="O979" s="2" t="n"/>
+      <c r="P979" s="2" t="n"/>
     </row>
     <row r="980">
       <c r="A980" s="2" t="n"/>
@@ -16380,6 +18368,8 @@
       <c r="L980" s="2" t="n"/>
       <c r="M980" s="2" t="n"/>
       <c r="N980" s="2" t="n"/>
+      <c r="O980" s="2" t="n"/>
+      <c r="P980" s="2" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="2" t="n"/>
@@ -16396,6 +18386,8 @@
       <c r="L981" s="2" t="n"/>
       <c r="M981" s="2" t="n"/>
       <c r="N981" s="2" t="n"/>
+      <c r="O981" s="2" t="n"/>
+      <c r="P981" s="2" t="n"/>
     </row>
     <row r="982">
       <c r="A982" s="2" t="n"/>
@@ -16412,6 +18404,8 @@
       <c r="L982" s="2" t="n"/>
       <c r="M982" s="2" t="n"/>
       <c r="N982" s="2" t="n"/>
+      <c r="O982" s="2" t="n"/>
+      <c r="P982" s="2" t="n"/>
     </row>
     <row r="983">
       <c r="A983" s="2" t="n"/>
@@ -16428,6 +18422,8 @@
       <c r="L983" s="2" t="n"/>
       <c r="M983" s="2" t="n"/>
       <c r="N983" s="2" t="n"/>
+      <c r="O983" s="2" t="n"/>
+      <c r="P983" s="2" t="n"/>
     </row>
     <row r="984">
       <c r="A984" s="2" t="n"/>
@@ -16444,6 +18440,8 @@
       <c r="L984" s="2" t="n"/>
       <c r="M984" s="2" t="n"/>
       <c r="N984" s="2" t="n"/>
+      <c r="O984" s="2" t="n"/>
+      <c r="P984" s="2" t="n"/>
     </row>
     <row r="985">
       <c r="A985" s="2" t="n"/>
@@ -16460,6 +18458,8 @@
       <c r="L985" s="2" t="n"/>
       <c r="M985" s="2" t="n"/>
       <c r="N985" s="2" t="n"/>
+      <c r="O985" s="2" t="n"/>
+      <c r="P985" s="2" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="2" t="n"/>
@@ -16476,6 +18476,8 @@
       <c r="L986" s="2" t="n"/>
       <c r="M986" s="2" t="n"/>
       <c r="N986" s="2" t="n"/>
+      <c r="O986" s="2" t="n"/>
+      <c r="P986" s="2" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="2" t="n"/>
@@ -16492,6 +18494,8 @@
       <c r="L987" s="2" t="n"/>
       <c r="M987" s="2" t="n"/>
       <c r="N987" s="2" t="n"/>
+      <c r="O987" s="2" t="n"/>
+      <c r="P987" s="2" t="n"/>
     </row>
     <row r="988">
       <c r="A988" s="2" t="n"/>
@@ -16508,6 +18512,8 @@
       <c r="L988" s="2" t="n"/>
       <c r="M988" s="2" t="n"/>
       <c r="N988" s="2" t="n"/>
+      <c r="O988" s="2" t="n"/>
+      <c r="P988" s="2" t="n"/>
     </row>
     <row r="989">
       <c r="A989" s="2" t="n"/>
@@ -16524,6 +18530,8 @@
       <c r="L989" s="2" t="n"/>
       <c r="M989" s="2" t="n"/>
       <c r="N989" s="2" t="n"/>
+      <c r="O989" s="2" t="n"/>
+      <c r="P989" s="2" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="2" t="n"/>
@@ -16540,6 +18548,8 @@
       <c r="L990" s="2" t="n"/>
       <c r="M990" s="2" t="n"/>
       <c r="N990" s="2" t="n"/>
+      <c r="O990" s="2" t="n"/>
+      <c r="P990" s="2" t="n"/>
     </row>
     <row r="991">
       <c r="A991" s="2" t="n"/>
@@ -16556,6 +18566,8 @@
       <c r="L991" s="2" t="n"/>
       <c r="M991" s="2" t="n"/>
       <c r="N991" s="2" t="n"/>
+      <c r="O991" s="2" t="n"/>
+      <c r="P991" s="2" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="2" t="n"/>
@@ -16572,6 +18584,8 @@
       <c r="L992" s="2" t="n"/>
       <c r="M992" s="2" t="n"/>
       <c r="N992" s="2" t="n"/>
+      <c r="O992" s="2" t="n"/>
+      <c r="P992" s="2" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="2" t="n"/>
@@ -16588,6 +18602,8 @@
       <c r="L993" s="2" t="n"/>
       <c r="M993" s="2" t="n"/>
       <c r="N993" s="2" t="n"/>
+      <c r="O993" s="2" t="n"/>
+      <c r="P993" s="2" t="n"/>
     </row>
     <row r="994">
       <c r="A994" s="2" t="n"/>
@@ -16604,6 +18620,8 @@
       <c r="L994" s="2" t="n"/>
       <c r="M994" s="2" t="n"/>
       <c r="N994" s="2" t="n"/>
+      <c r="O994" s="2" t="n"/>
+      <c r="P994" s="2" t="n"/>
     </row>
     <row r="995">
       <c r="A995" s="2" t="n"/>
@@ -16620,6 +18638,8 @@
       <c r="L995" s="2" t="n"/>
       <c r="M995" s="2" t="n"/>
       <c r="N995" s="2" t="n"/>
+      <c r="O995" s="2" t="n"/>
+      <c r="P995" s="2" t="n"/>
     </row>
     <row r="996">
       <c r="A996" s="2" t="n"/>
@@ -16636,6 +18656,8 @@
       <c r="L996" s="2" t="n"/>
       <c r="M996" s="2" t="n"/>
       <c r="N996" s="2" t="n"/>
+      <c r="O996" s="2" t="n"/>
+      <c r="P996" s="2" t="n"/>
     </row>
     <row r="997">
       <c r="A997" s="2" t="n"/>
@@ -16652,6 +18674,8 @@
       <c r="L997" s="2" t="n"/>
       <c r="M997" s="2" t="n"/>
       <c r="N997" s="2" t="n"/>
+      <c r="O997" s="2" t="n"/>
+      <c r="P997" s="2" t="n"/>
     </row>
     <row r="998">
       <c r="A998" s="2" t="n"/>
@@ -16668,6 +18692,8 @@
       <c r="L998" s="2" t="n"/>
       <c r="M998" s="2" t="n"/>
       <c r="N998" s="2" t="n"/>
+      <c r="O998" s="2" t="n"/>
+      <c r="P998" s="2" t="n"/>
     </row>
     <row r="999">
       <c r="A999" s="2" t="n"/>
@@ -16684,6 +18710,8 @@
       <c r="L999" s="2" t="n"/>
       <c r="M999" s="2" t="n"/>
       <c r="N999" s="2" t="n"/>
+      <c r="O999" s="2" t="n"/>
+      <c r="P999" s="2" t="n"/>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="n"/>
@@ -16700,6 +18728,8 @@
       <c r="L1000" s="2" t="n"/>
       <c r="M1000" s="2" t="n"/>
       <c r="N1000" s="2" t="n"/>
+      <c r="O1000" s="2" t="n"/>
+      <c r="P1000" s="2" t="n"/>
     </row>
     <row r="1001">
       <c r="A1001" s="2" t="n"/>
@@ -16716,13 +18746,15 @@
       <c r="L1001" s="2" t="n"/>
       <c r="M1001" s="2" t="n"/>
       <c r="N1001" s="2" t="n"/>
+      <c r="O1001" s="2" t="n"/>
+      <c r="P1001" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Menina,Menino"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16737,7 +18769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16749,11 +18781,13 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -16804,25 +18838,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Responsável</t>
+          <t>Sonho</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Contato do responsável</t>
+          <t>Sobre a criança</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Autoriza imagem</t>
+          <t>Responsável</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Contato do responsável</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Autoriza imagem</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Observações</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Código no sistema antigo</t>
         </is>
@@ -16870,21 +18914,31 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Maria Souza</t>
+          <t>ser professora</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>(11) 91234-5678</t>
+          <t>Dá aula para as bonecas todo dia depois da escola.</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>Maria Souza</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>(11) 91234-5678</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>A-001</t>
         </is>
@@ -16936,25 +18990,31 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
+          <t>jogador de futebol</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
           <t>Joana Lima</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>(11) 98765-4321</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Prefere tênis a sandália</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>A-002</t>
         </is>
@@ -17000,23 +19060,25 @@
           <t>música</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Carlos Alves</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>(11) 99876-5432</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -17030,7 +19092,7 @@
     <dataValidation sqref="D2:D4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Menina,Menino"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17045,7 +19107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -17319,7 +19381,7 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Responsável</t>
+          <t>Sonho</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -17329,19 +19391,19 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Nome do responsável. Nunca aparece no site.</t>
+          <t>Opcional. Aparece no site. Complete a frase "sonha em...". Ex.: ser professora</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Contato do responsável</t>
+          <t>Sobre a criança</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -17351,19 +19413,19 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Telefone ou WhatsApp. Nunca aparece no site.</t>
+          <t>Opcional. Aparece no site. O jeitinho dela, contado por ela ou pelos pais (até 400 letras). Sem escola, rua ou sobrenome.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Autoriza imagem</t>
+          <t>Responsável</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -17378,14 +19440,14 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Sim só com o termo de autorização assinado pelo responsável. Sem ele, Não (a criança aparece com avatar).</t>
+          <t>Nome do responsável. Nunca aparece no site.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Observações</t>
+          <t>Contato do responsável</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -17400,14 +19462,14 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Uso interno da equipe. Nunca aparece no site.</t>
+          <t>Telefone ou WhatsApp. Nunca aparece no site.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Código no sistema antigo</t>
+          <t>Autoriza imagem</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -17422,12 +19484,56 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
+          <t>Sim só com o termo de autorização assinado pelo responsável. Sem ele, Não (a criança aparece com avatar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Observações</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Uso interno da equipe. Nunca aparece no site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Código no sistema antigo</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
           <t>Opcional. Se a criança já tinha um código, ele evita duplicar ao importar de novo.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Privacidade: responsável, contato e observações ficam só no painel. A foto da criança só vai para o site com o termo de autorização assinado.</t>
         </is>
